--- a/research/自治体営業リスト_統合版_2026-10.xlsx
+++ b/research/自治体営業リスト_統合版_2026-10.xlsx
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'福島県'!$A$3:$T$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'茨城県'!$A$3:$T$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'栃木県'!$A$3:$T$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'営業メモ'!$A$4:$M$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'営業メモ'!$A$4:$M$41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'営業メモ'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'ファクトチェック結果'!$A$4:$L$50</definedName>
   </definedNames>
@@ -1361,7 +1361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1956,57 +1956,137 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
+          <t>宮城県</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>栗原市</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>第2次栗原市環境基本計画（H30〜R9／2018〜2027年度、10年間）</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>第2次栗原市環境基本計画（H30〜R9の10年間、確認済）。市民生活部環境課が環境政策の総合企画・調整、環境基本計画、環境保全型地域づくり（エコタウン計画）を所管。計画本編・概要版は市サイトで公開。望ましい環境像・基本目標の具体文言は検索で確認できず（要確認）。参考：栗原市地域公共交通計画はR6〜R10（2024〜2028年度）、前身の網形成計画はR5年度で終了（確認済）。</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>市民生活部 環境課 環境政策・施設係（本庁舎1階）。電話 0228-22-3350（直通）、FAX 0228-22-0350、〒987-2293 栗原市築館薬師一丁目7番1号（組織概要ページで確認）。交通計画は企画部 市民協働課（パブコメ問合せ先として確認）。</t>
+        </is>
+      </c>
+      <c r="H12" s="28" t="inlineStr">
+        <is>
+          <t>【次期計画は着手済・業者決定済の可能性大】『第3次栗原市環境基本計画策定支援業務』が市の「2026年6月の入札結果」ページ（2026年6月3日執行分PDF、2.7MB）に掲載（確認済）。→R8.6.3に入札執行。入札結果として公表されていることから競争入札（栗原市の業務委託では指名競争入札が通例のため指名競争入札と推定）。公告日・予定価格・落札者・落札金額・履行期間（R8〜R9の2か年か否か）は、市サイトがWebFetch不可（egress遮断）でPDF本文を確認できず「不明」。計画期間からみて第3次計画はR10（2028）年度開始、R8〜R9の2か年でアンケート・審議会を経て策定と推定。環境審議会の開催日程・諮問日は検索で確認できず。並行して第3次栗原市総合計画（R9〜、推定）を策定中：2026年2月に市民アンケート結果公表、2026年9月28日に基本構想（案）の意見募集開始（確認済）。</t>
+        </is>
+      </c>
+      <c r="I12" s="25" t="inlineStr">
+        <is>
+          <t>次期（第3次）：R8.6.3執行の入札（方式・落札者・金額は不明、上記PDF要確認）。現行（第2次、H29年度策定支援）：発注方式・受託者・金額とも不明。試行クエリ：「第3次栗原市環境基本計画策定支援業務」「栗原市 入札結果 令和8年6月 環境基本計画策定支援業務 落札」「栗原市 2026年6月の入札結果 … 指名競争入札 落札者」（extended）「"環境基本計画策定支援業務" 栗原市 落札金額 予定価格 2026年6月3日執行」（extended）「栗原市 環境基本計画 策定支援業務 平成29年度 入札結果 落札」「栗原市 環境基本計画 策定 業務委託 株式会社 第2次 平成29年 受託」「栗原市 令和8年度 当初予算 環境基本計画策定事業 債務負担行為」。いずれも他市の仕様書等のみヒット。</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>・栗原市ゼロカーボンシティ宣言（2024年2月表明、検索要約ベース＝推定）。栗原市オーガニックビレッジ宣言もあり。・第2次総合計画はH29〜R8で今年度終了、第3次総合計画（基本構想案パブコメ2026.9.28〜）と環境基本計画の改定が連動。・交通：栗原市地域公共交通計画（R6〜R10、R5.7.11〜7.30パブコメ、意見2人4件）。乗合デマンド交通を花山地区を除き2024年3月29日で終了し、2024年4月1日からタクシー利用助成事業へ転換。市民バスは毎年4月にダイヤ・ルート見直し（R7年度版利用ガイド）。交通計画の次期改定はR10年度策定作業（R11開始）と推定。</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>・第3次環境基本計画策定支援はR8.6.3に入札執行済で受託者決定済。落札者・金額を環境課に確認（または6月3日執行分PDFで確認）し、R9年度に関連業務（地球温暖化対策実行計画（区域施策編）の同時改定、再エネ導入目標・促進区域の検討、市民アンケート等）が別発注されるかをヒアリングする
+・ゼロカーボンシティ宣言（2024年2月、推定）・オーガニックビレッジ宣言を受け、第3次計画に脱炭素・地域循環共生圏の施策を盛り込む際の補助事業（環境省の脱炭素関連補助）活用提案を切り口にする
+・交通計画（R6〜R10）は中間評価・タクシー助成への転換効果検証の時期に入るため、市民協働課に毎年度の評価・モニタリング支援や次期（R10年度策定）計画の準備状況をヒアリング</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="inlineStr">
+        <is>
+          <t>https://www.kuriharacity.jp/w004/030/010/030/20260114/202606/PAGE000000000000015506.html
+https://www.kuriharacity.jp/li/030/190/020/020/index.html
+https://www.kuriharacity.jp/w012/010/010/020/120/51193.html
+https://www.kuriharacity.jp/soshiki/gaiyo/20180607155533.html
+https://www.kuriharacity.jp/w010/020/030/51329.html
+https://www.kuriharacity.jp/w007/020/050/010/050/44337.html
+https://kuriharacity.jp/w007/020/050/010/R8.2shiminanke-to.pdf?3251049=
+https://www.kuriharacity.jp/li/030/news.html
+https://www.kuriharacity.jp/li/010/020/080/index.html
+https://www.kuriharacity.jp/w001/030/010/200/2025/20250210/PAGE000000000000008625.html
+https://www.kuriharacity.jp/w018/020/010/150/PAGE000000000000014198.html
+https://www.kuriharacity.jp/w010/010/010/020/070/PAGE000000000000012678.html
+https://www.kuriharacity.jp/w010/010/010/020/001/PAGE000000000000014277.html
+https://www.kuriharacity.jp/li/010/020/120/index.html</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t>期間確認：環境基本計画 H30〜R9 確認済（検索結果『2018年度から2027年度までの10年間』）。交通計画 R6〜R10 確認済（パブコメページ要約『令和6年度から令和10年度』）。次期環境計画の入札はR8.6.3執行で確認済だが、落札者・金額・方式・履行期間はPDF未読のため不明（kuriharacity.jpはWebFetchがegress遮断）。WebSearch使用14回（うちextended 2回）。ゼロカーボン宣言日は単一要約のため推定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
           <t>秋田県</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>秋田市</t>
         </is>
       </c>
-      <c r="D12" s="27" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>秋田市環境基本計画（H30〜R9）</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>秋田市環境基本条例（H11.3制定）に基づく計画。現行計画はH30年度〜R9年度（2018〜2027年度）の10年計画で、策定後5年経過を受けR4年度に中間見直し（パブコメR4.12.16〜R5.1.16、R5.3中間見直し版公表）。主な施策（基本目標）は計画PDF本文未確認のため要確認。</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>環境部 環境総務課（秋田市山王一丁目1-1 本庁舎3階、電話018-888-5702）。同課の所掌に環境政策の企画、地球温暖化対策、環境教育、自然環境保全、新エネルギーが含まれる（検索結果本文で確認）。係名は未確認。</t>
         </is>
       </c>
-      <c r="H12" s="28" t="inlineStr">
+      <c r="H13" s="28" t="inlineStr">
         <is>
           <t>着手済：第45回秋田市環境審議会（令和8年3月24日）の議題に「秋田市環境基本計画の改定について」（資料1あり）があり、R8年度から改定作業が始まっていると見られる。具体的な改定スケジュール（諮問・答申時期、パブコメ時期）は検索で確認できず。現行計画がR9末で終わるため、R8〜R9の2か年で改定しR10.4に新計画を開始する見込み（推定）。改定支援業務の委託（プロポーザル・入札）の有無は環境部入札結果ページの検索要約で確認できず（R8年度当初に発注済の可能性、または市直営の可能性。いずれも未確認）。</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>不明。現行計画（H29年度策定）、R4年度の中間見直しとも、策定支援業務の発注方式・受託者・金額は検索で確認できず。市HPには「環境部入札結果」ページ（R7年12月まで分・R8分）が存在するが、該当業務の記載は検索要約上見当たらなかった（ページ本文は未確認）。</t>
         </is>
       </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>ゼロカーボンシティ宣言済（市HPに宣言ページあり、宣言日は未確認）。地球温暖化対策実行計画（区域施策編）はR4年度に見直し。秋田市新エネルギービジョン、第14次秋田市総合計画「県都『あきた』創生プラン」あり。審議会では市内地下水のPFOS・PFOA指針値超過も報告（第45回）。交通分野では第4次秋田市公共交通政策ビジョン（地域公共交通計画、R8〜R12）をR8.3策定済。</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr">
         <is>
           <t>・第45回環境審議会（R8.3.24）で改定議題が出ており改定作業は進行中。審議会運営支援・市民/事業者アンケート・計画書作成の外部委託の有無と、R9年度の追加業務（パブコメ対応、概要版作成等）の余地を確認する。
 ・ゼロカーボンシティ宣言と区域施策編（R4見直し）の目標を新環境基本計画にどう統合するか（温対計画・新エネビジョンとの一体化）を提案軸にする。
 ・PFOS・PFOA等の新たな環境課題を新計画の生活環境分野にどう位置付けるかを話題にする。</t>
         </is>
       </c>
-      <c r="L12" s="26" t="inlineStr">
+      <c r="L13" s="26" t="inlineStr">
         <is>
           <t>https://www.city.akita.lg.jp/kurashi/recycle/1016631/1006116.html
 https://www.city.akita.lg.jp/shisei/hoshin-keikaku/1009930/1006108.html
@@ -2019,65 +2099,65 @@
 https://www.city.akita.lg.jp/kurashi/recycle/1006076/1006141.html</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M13" s="22" t="inlineStr">
         <is>
           <t>調査日 2026-10-02。第45回審議会資料1（改定について、PDF 76.1KB）の中身（スケジュール・委託の記載）は未確認のため、直接閲覧を推奨。検索結果に https://www.city.akita.lg.jp/_res/projects/default_project/_page_/001/051/322/setumeisyo.pdf （説明書、内容不明）が出たが、本計画の改定支援業務と関係があるかは未確認（新しいページ番号帯のためR8年度の公募の可能性あり＝要確認、推定）。過去の受託者・金額は不明。</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>秋田県</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>能代市</t>
         </is>
       </c>
-      <c r="D13" s="24" t="inlineStr"/>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr"/>
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>第2次能代市環境基本計画（H30〜R9）</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>能代市環境基本条例に基づく計画（第1次はH20.3策定）。第2次はH30.3策定、計画期間H30年度〜R9年度の10年間、環境像「みんなでつくり 次世代へつなぐ 環境のまち のしろ」。重点環境施策6本（自然環境への意識高揚・自然との共生、温室効果ガス排出量の抑制等）を置き、R4年度までの実績を踏まえR5.3に指標目標を中間見直し。風力・太陽光・木質バイオマス等の再エネ導入、能代港（洋上風力の拠点港湾）の活用を掲げ、再エネ導入量をR3年度76,803kWからR9年度250,000kWへ拡大する目標。</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>環境産業部 環境衛生課 環境衛生係（電話0185-89-2173、FAX0185-89-1769）が計画の問い合わせ窓口（検索結果本文で確認）。同課に環境保全係もあり。</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>R9年度末で計画期間終了のため、第3次計画はR8〜R9年度に策定作業が必要（推定）。次期計画の策定委託・懇談会開催・パブコメは検索で確認できず。既存の「環境のまちづくり市民懇談会」資料（1st/3rdフォルダ、後期目標検討シート等）は中間見直し時のものと見られ（推定）、第3次策定でも同懇談会を活用する可能性が高い（推定）。市の「発注予定及び結果」（R8年度分ページの存在は検索要約による）に該当業務があるかは未確認。R9当初予算で策定業務を計上する場合、R9年度前半に発注見込み（推定）。</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>不明。第2次計画（H29年度策定）、R4年度の中間見直しとも、策定支援業務の発注方式・受託者・金額は検索で確認できず。市にはプロポーザル方式等による業者選定実施要綱あり。</t>
         </is>
       </c>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>2025年7月1日の定例記者会見で「能代市カーボンニュートラル宣言」（2050年度CO2実質ゼロ）。秋田洋上風力発電による能代港洋上風力の運転、「エネルギーのまち 能代」の取組。市役所の地球温暖化対策実行計画（事務事業編、環境マネジメントシステム運用書）をR6.3改訂。区域施策編の有無は未確認。第3次能代山本定住自立圏共生ビジョン（R8.3）、第3期のしろ創生総合戦略（R7.3）策定済。</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr">
         <is>
           <t>・現行計画はR9年度末で終期。R7.7のカーボンニュートラル宣言を受け、第3次環境基本計画に区域施策編（温対法の地方公共団体実行計画）を統合・一体策定する提案が有効（区域施策編の策定状況は要確認）。
 ・再エネ導入目標（R9に250,000kW）の達成状況評価と洋上風力の拡大を踏まえた次期目標設定・指標設計を支援メニューとして示す。
 ・市民懇談会を活用した中間見直しの実績があるため、懇談会運営・市民アンケート・指標点検をパッケージにした策定支援を提案する。</t>
         </is>
       </c>
-      <c r="L13" s="26" t="inlineStr">
+      <c r="L14" s="26" t="inlineStr">
         <is>
           <t>https://www.city.noshiro.lg.jp/sangyo/kankyo/keikaku/22091
 https://www.city.noshiro.lg.jp/up/files/www/sangyo/kankyo/keikaku/keikaku_minaoshi_2nd.pdf
@@ -2090,65 +2170,65 @@
 https://wa.city.noshiro.lg.jp/energy/</t>
         </is>
       </c>
-      <c r="M13" s="22" t="inlineStr">
+      <c r="M14" s="22" t="inlineStr">
         <is>
           <t>調査日 2026-10-02。計画期間H30〜R9は検索結果本文で確認。第3次計画の着手（委託・懇談会・予算）は検索8回で確認できず。過去の受託者・金額は不明。懇談会資料の開催時期は未確認（中間見直し時と推定）。市サイトへのWebFetchは未試行（久慈市でブロックされたため、今回はWebSearchのみ）。</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>秋田県</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>大館市</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr"/>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr"/>
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>大館市地域公共交通計画（H30〜R9）</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>H30.3策定の大館市地域公共交通網形成計画（H30〜R9、2018〜2027年度）を、R6年度の見直し業務を経てR7（R7.3版・R7.8改定版）に「大館市地域公共交通計画」として改定。公共交通不便地域やバス路線再編で減便・廃止が見込まれる地域でのデマンド方式等の新しい交通システム導入の検証、比内地域・田代地域のバス路線再編とコミュニティバス（ほほえみひない号、たしろたけのこ号）運行など。R7.9に大館市地域公共交通利便増進実施計画（R7〜R9）も策定し「コンパクトシティ・プラス・ネットワーク」を推進。</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>建設部 都市計画課 交通政策係（電話0186-43-7146、koutsu@city.odate.lg.jp、〒018-5792 大館市比内町扇田字新大堤下93番地6）（検索結果本文で確認）</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>計画終期R9（2027年度）。改定版・利便増進実施計画とも計画期間がR9まで（検索要約では改定計画の期間をR7〜R9と表記、元の計画期間H30〜R9の残期間と見られる＝推定）。次期計画の策定業務・活性化協議会での審議は検索で確認できず。R6年度の見直しが入札（5月公告・6月開札）で発注された例から、次期計画はR9当初予算化・R9年度5〜6月頃発注、またはR8〜R9の2か年発注の見込み（推定）。</t>
         </is>
       </c>
-      <c r="I14" s="25" t="inlineStr">
+      <c r="I15" s="25" t="inlineStr">
         <is>
           <t>R6年度「大館市地域公共交通網形成計画見直し業務ほか」（案件番号06-52TI-04、公告2024/05/21、開札2024/06/06）：落札者 (株)協和コンサルタンツ、落札金額7,633,000円、予定価格9,490,000円。参加6社＝ランドブレイン(株)、(株)福山コンサルタント、(株)協和コンサルタンツ、(株)オリエンタルコンサルタンツ、八千代エンジニヤリング(株)、(株)復建技術コンサルタント（nsearch.jpの検索結果本文で確認）。発注方式は入札（指名競争入札と推定）。業務名に「ほか」とあり利便増進実施計画策定等を含む可能性（推定）。H29年度の網形成計画当初策定業務の受託者・金額は検索で確認できず。</t>
         </is>
       </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>R7.10.1から比内地域のバス路線を変更（運行効率化）、比内地域コミュニティバス「ほほえみひない号」運行開始、田代地域でコミュニティバス「たしろたけのこ号」運行開始。大館市都市再興基本計画（立地適正化計画）策定済。R4年度に大館市総合計画策定支援等業務の公募型プロポーザル（R4.4.28公告）実施。環境分野は第3次大館市環境基本計画（R3〜R12、推定）。</t>
         </is>
       </c>
-      <c r="K14" s="22" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>・R6見直し業務は指名6社の価格競争で協和コンサルタンツが763.3万円で落札。次期計画（R9終期）でも同規模・同方式が想定されるため、R9当初予算要求（R8秋）に向けた業務内容・積算の情報提供を早めに行う。
 ・利便増進実施計画（R7〜R9）とコミュニティバス導入・比内地域路線再編の効果検証を、次期計画の評価・目標設定に繋げる支援を提案する。
 ・立地適正化計画（都市再興基本計画）との連動（コンパクトシティ・プラス・ネットワーク）を次期計画の柱として提示する。</t>
         </is>
       </c>
-      <c r="L14" s="26" t="inlineStr">
+      <c r="L15" s="26" t="inlineStr">
         <is>
           <t>https://www.city.odate.lg.jp/city/soshiki/koutsu/p11901
 https://www.city.odate.lg.jp/uploads/public/pages_0000011901_00/R7.08%E6%94%B9%E6%AD%A3_%E5%A4%A7%E9%A4%A8%E5%B8%82%E5%9C%B0%E5%9F%9F%E5%85%AC%E5%85%B1%E4%BA%A4%E9%80%9A%E8%A8%88%E7%94%BB.pdf
@@ -2161,65 +2241,65 @@
 https://nsearch.jp/nyusatsu_ankens/627d514f1acc1a11c5649e9f</t>
         </is>
       </c>
-      <c r="M14" s="22" t="inlineStr">
+      <c r="M15" s="22" t="inlineStr">
         <is>
           <t>調査日 2026-10-02。R6見直し業務の受託者・金額はnsearch.jp（民間の入札情報サイト）の検索結果本文によるもので、市の入札結果ページ原本では未確認。発注方式（指名競争）は推定。改定版計画の期間表記（H30〜R9かR7〜R9か）は資料により異なる可能性あり要確認。次期計画の着手は未確認。H29当初策定の受託者は不明。</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>秋田県</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>鹿角市</t>
         </is>
       </c>
-      <c r="D15" s="24" t="inlineStr"/>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr"/>
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>鹿角市地域公共交通計画（令和7年6月改訂版）</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>鹿角市地域公共交通活性化協議会が策定した地域公共交通のマスタープラン。計画期間は令和5年度〜令和9年度（検索結果の要約で確認、本文PDFは未閲覧）。素案パブコメはR5.1.23〜R5.2.22、R5.3.6のR4年度第5回協議会を経て策定。市民・交通事業者・行政が一体となった持続可能な交通体系の構築が目的。R7.6に秋北バス一部路線廃止・八幡平地区再編（R7.10.1対応）に合わせ改訂（既存調査メモより）。前計画は鹿角市地域公共交通網形成計画（H28〜H32）。</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>市民共動部 環境生活課（交通担当）（推定：計画ページのURLが soshiki/shiminkyodo/kankyoseikatsu 配下）。係名・電話番号は未確認。</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>終期R9（令和9年度末）。次期計画策定の着手情報（業務公告・協議会での審議）は検索で確認できず。通例ではR8年度後半〜R9年度当初予算で策定支援業務を計上し、R9年度に1年で策定（推定）。R8年度予算書・協議会資料の確認が必要。</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>不明。現行計画（R4年度策定作業）・前回網形成計画（H27〜H28頃策定）の策定支援業務の発注方式・受託者・金額は検索で見つからず。R4年度予算の概要ページは存在するが金額の記載は検索結果で確認できず。なお市はR5年度に別途「鹿角市総合都市交通体系調査」（都市計画道路の見直し等、国交省街路交通調査として公表）を実施しているが受託者は未確認。</t>
         </is>
       </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>・R7.6改訂の契機：秋北バスの一部路線廃止・八幡平地区の路線再編（R7.10.1）（既存調査メモ、検索結果での再確認はできず）。・R5年度鹿角市総合都市交通体系調査（都市計画道路35,270m中17,992m整備・整備率51.0%、未着手路線の見直し）。・第7次鹿角市総合計画（基本構想・前期基本計画）が進行中（期間は未確認）。・環境面：第3次鹿角市環境基本計画（R3〜R12）、エネルギービジョン（R4.2）。</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr">
         <is>
           <t>・R5〜R9計画はR7.6に路線廃止対応で改訂済み。次期計画では秋北バス路線縮小後の八幡平地区等の代替交通（デマンド・乗合タクシー等）の効果検証と再設計が論点になる点を切り口に、R9年度策定に向けたR8年度中のデータ収集（乗降調査・住民アンケート）の前倒しを提案。
 ・R5年度に総合都市交通体系調査（都市計画道路見直し）を実施済みのため、都市計画（道路・立地）と公共交通計画の整合を取った次期計画づくりを提案できる。
 ・協議会運営（年5回程度開催実績あり）と利便増進・補助金（地域公共交通確保維持事業）申請支援を一体で受けられる体制をアピール。</t>
         </is>
       </c>
-      <c r="L15" s="26" t="inlineStr">
+      <c r="L16" s="26" t="inlineStr">
         <is>
           <t>https://www.city.kazuno.lg.jp/soshiki/shiminkyodo/kankyoseikatsu/gyomu/2/3/10092.html
 https://www.city.kazuno.lg.jp/soshiki/shiminkyodo/kankyoseikatsu/gyomu/2/3/9297.html
@@ -2230,65 +2310,65 @@
 https://www.city.kazuno.lg.jp/soshiki/seisakukikaku/sogosenryaku/gyomu/2/4/07/7563.html</t>
         </is>
       </c>
-      <c r="M15" s="22" t="inlineStr">
+      <c r="M16" s="22" t="inlineStr">
         <is>
           <t>調査日2026-10-02。市サイト（city.kazuno.lg.jp）はWebFetchでブロックされ本文未閲覧。計画期間R5〜R9は検索結果の要約での確認（本文引用なし）。担当課は URL 構造からの推定。受託者・金額は不明。R7.6改訂の具体内容は既存データ注釈に依拠し今回再確認できず。</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>秋田県</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>北秋田市</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr"/>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr"/>
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>北秋田市地域公共交通計画（令和5年度〜令和9年度）</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>北秋田市地域公共交通網形成計画（H30〜R4）の後継として策定（市ニュースでは2024年3月29日策定と掲載、計画書の完成は2023年3月との記載もあり）。期間R5〜R9（市ニュースで確認）。市の交通政策の最上位計画（マスタープラン）として交通の将来像と公共交通の役割・取組の方向性を定め、計画に基づき交通再編を実施し利便向上・維持確保を図る。別途、利便増進実施計画あり。</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>総合政策課（推定：検索結果の要約に総務部総合政策課の言及があるが、交通計画の所管として本文では未確認）。係名・電話番号は未確認。</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>終期R9。次期交通計画の策定業務公告は検索で見つからず。現行計画はR4年度に応募型プロポーザルで策定支援業務を発注し1年で策定した実績があるため、次期もR9年度当初予算計上→R9年度春にプロポーザル公告→R9年度内策定の流れ（推定）。R8年度県北地域部会（秋田県地域公共交通活性化協議会）資料あり。</t>
         </is>
       </c>
-      <c r="I16" s="25" t="inlineStr">
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t>現行計画：『北秋田市地域公共交通計画策定支援業務』を公募（応募型）プロポーザルで発注（R4年度、網形成計画がR4年度で終了するためR5年度からの計画を策定する目的）。参加資格は市資格者名簿登載・東北地区内に本社または営業所・過去5年以内の地域公共交通計画/再編実施計画の実績。仕様書PDFは検索結果に存在。受託者・契約金額・上限額は検索結果本文で確認できず＝不明。前回網形成計画（H30〜R4）の受託者も不明。（参考：同市はR7年度に『第３次北秋田市総合計画等策定支援業務』を応募型プロポーザルで発注、上限15,279,000円（税込）、履行期限R8.3.31。受託者は未確認）</t>
         </is>
       </c>
-      <c r="J16" s="22" t="inlineStr">
+      <c r="J17" s="22" t="inlineStr">
         <is>
           <t>・環境基本計画（R3改正版）は「平成28年度から令和8年度までの10年間」とされ（検索要約）、R8＝今年度終期。次期環境基本計画の策定業務公告・審議会開催は今回の検索でも確認できず（策定が遅れている/内製の可能性、要確認）。・地球温暖化対策実行計画（区域施策編）を令和7年7月に策定（市PDF）。ゼロカーボン宣言R6.2.15（既存調査メモ）。・第3次北秋田市総合計画をR7年度に策定支援委託（R8年度始期と推定）—上位計画が新しくなったため、交通・環境計画とも新総合計画との整合が次期改定の論点。・R5〜R9交通計画に基づく交通再編を実施中。</t>
         </is>
       </c>
-      <c r="K16" s="22" t="inlineStr">
+      <c r="K17" s="22" t="inlineStr">
         <is>
           <t>・環境基本計画がR8年度末で終期を迎えるが、次期計画の策定公告が見当たらない。R7.7策定の区域施策編と統合した『環境基本計画＋区域施策編』一体型の次期計画（R9〜）を提案する好機（スケジュールが厳しければ1年延長・中間見直しの支援も）。
 ・現行交通計画は応募型プロポーザル（東北に拠点・過去5年の計画実績が要件）で発注された実績。次期（R9年度策定見込み）も同方式が想定されるため、東北拠点と交通計画実績を早めに担当課に示し、R8年度中の評価・検証（再編効果、乗降データ分析）支援で関係構築。
 ・第3次総合計画（R7年度策定支援）との整合を軸に、交通・環境・脱炭素（公用車EV、デマンド交通）を横断した施策体系を提案。</t>
         </is>
       </c>
-      <c r="L16" s="26" t="inlineStr">
+      <c r="L17" s="26" t="inlineStr">
         <is>
           <t>https://www.city.kitaakita.akita.jp/news/p15700
 https://www.city.kitaakita.akita.jp/uploads/public/news_0000015700_00/koukyoukoutsukeikaku.pdf
@@ -2301,65 +2381,65 @@
 https://www.pref.akita.lg.jp/uploads/public/archive_0000098833_00/R8活性化協議会①/令和８年度第１回秋田県地域公共交通活性化協議会県北地域部会_会議概要.pdf</t>
         </is>
       </c>
-      <c r="M16" s="22" t="inlineStr">
+      <c r="M17" s="22" t="inlineStr">
         <is>
           <t>調査日2026-10-02。市サイトはWebFetchブロックのため本文未閲覧（検索結果要約に依拠）。交通計画の策定日は市ニュース要約では2024.3.29、検索要約では2023年3月完成と食い違い（計画期間R5始期からR5.3策定が妥当（推定））。策定支援業務がプロポーザルであったことは仕様書の要約で確認、受託者・金額は不明。担当課（総合政策課）は推定。環境基本計画の期間はH28〜R8（要約）とH30.4始期説が混在、要確認。</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>秋田県</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>五城目町・八郎潟町・大潟村（南秋地域）</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr"/>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr"/>
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>南秋地域公共交通計画（令和5年度〜令和9年度、南秋地域公共交通活性化協議会）</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>五城目町・八郎潟町・大潟村の3町村全域を対象とする広域計画。期間R5〜R9（五城目町サイトで確認）、R5.6策定（東北運輸局資料、既存調査）。前計画は南秋地域公共交通網形成計画（H30.3策定、H30〜H34）。基本方針は3町村広域連携公共交通軸の形成・再編、地域間幹線交通の導入、地域内交通の見直し、各主要拠点の連携強化、わかりやすく安心な公共交通、3町村連携による持続可能な運営・仕組みづくり等（網形成計画からの継承を含む、検索要約）。主要施策として「南秋地域広域マイタウンバス」を運行。</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>南秋地域公共交通活性化協議会 事務局：五城目町 まちづくり課（検索要約で確認）。係名・電話番号は未確認。八郎潟町・大潟村の担当課は未確認。</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>終期R9。次期計画の策定業務公告・協議会での審議は検索で確認できず。前回はR4年度に作業→R5.4頃に八郎潟町でも素案の意見募集→R5.6策定の流れ（八郎潟町パブコメ記事 2023.4.20付と推定）。次期もR9年度に策定作業→R10年度当初策定の可能性（推定）。また五城目町単独計画（R4〜R8）がR8年度で終期のため、R8年度中に単独計画の扱い（延長・南秋計画への統合等）が論点になっている可能性（推定、検索では未確認）。</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>不明。南秋地域公共交通計画（R4〜R5作業）・前回網形成計画（H29年度作業）とも、策定支援業務の発注方式・受託者・金額は検索で確認できず。協議会発注（国の計画策定事業補助活用）の可能性（推定）。</t>
         </is>
       </c>
-      <c r="J17" s="22" t="inlineStr">
+      <c r="J18" s="22" t="inlineStr">
         <is>
           <t>・秋田県地域公共交通計画（R4〜R8）の次期計画策定：県がR8年度に『秋田県地域公共交通計画策定業務委託』をプロポーザルで発注（質問への回答 R8.4.16公開、業務委託仕様書あり。計画検討部会・地域部会の開催を含む）。受託者は未確認。R8.6.23第1回県活性化協議会で次期計画策定を議論（既存調査）。次期県計画（R9〜）と南秋計画次期版の整合が論点。・五城目町単独の五城目町地域公共交通計画（R4〜R8、R4.5策定）：次期動向は未確認。・大潟村は環境省脱炭素先行地域（既存調査）。・JR奥羽本線八郎潟駅が3町村の結節点（推定）。</t>
         </is>
       </c>
-      <c r="K17" s="22" t="inlineStr">
+      <c r="K18" s="22" t="inlineStr">
         <is>
           <t>・県計画（R4〜R8）の次期版をR8年度に策定中。県計画の新しい地域区分・幹線ネットワーク方針を南秋計画次期版（R9終期）にどう反映するか、R8〜R9年度にかけた先行的な検討支援（県計画とのすり合わせ資料作成）を提案。
 ・五城目町単独計画がR8年度で終期のため、南秋計画との統合・一本化（計画の重複解消、協議会運営の効率化）を町まちづくり課（協議会事務局）に提案。
 ・広域マイタウンバスの利用実績評価と、大潟村の脱炭素先行地域の取組（EV・再エネ）と連携した交通施策（EVバス・デマンド）を次期計画の目玉として提示。</t>
         </is>
       </c>
-      <c r="L17" s="26" t="inlineStr">
+      <c r="L18" s="26" t="inlineStr">
         <is>
           <t>https://www.town.gojome.akita.jp/kurashi/koukyoukoutsu/2085
 https://www.town.gojome.akita.jp/up/files/town/machikeikaku/koutuukeikaku.pdf
@@ -2375,65 +2455,65 @@
 https://www.env.go.jp/content/900512579.pdf</t>
         </is>
       </c>
-      <c r="M17" s="22" t="inlineStr">
+      <c r="M18" s="22" t="inlineStr">
         <is>
           <t>調査日2026-10-02。WebFetchは試行せず（他の自治体サイトでブロック多発のため）。期間R5〜R9は既存調査で本文確認済。事務局=五城目町まちづくり課は検索要約で確認。南秋計画のR5.6策定は既存調査（東北運輸局資料）に依拠。ある検索要約では『2022年6月に計画完成』とあったが期間R5始期と矛盾するため採用せず。受託者・金額は不明。県次期計画プロポーザルの受託者・金額も未確認。</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="22" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>山形県</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>村山市</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr"/>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr"/>
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>村山市環境基本計画（第２次）（平成30年度〜令和9年度）</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>平成30年3月策定の第2次計画。期間H30〜R9（10年、既存調査で本文確認済「平成30年度〜平成39年度」）。望ましい環境像「豊かな自然環境と共生する 循環のまち 村山市」、基本目標は①安心で良好な生活環境を大切にするまちづくり②多様な自然を承継するまちづくり③地球環境保全に積極的に取り組むまちづくり④持続的に発展していくまちづくり。再エネ導入（太陽光・木質バイオマス等）促進を含む。</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>市民環境課（電話 0237-55-2111、FAX 0237-55-6443）※市の環境基本計画ページの問い合わせ先として検索結果で確認。係名は未確認。</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>終期R9（令和9年度末）。第3次計画の策定着手（業務公告・環境審議会での審議・市民アンケート）は検索で確認できず。R9年度中に策定するには、R9年度当初予算での策定支援業務計上→R9年度春〜初夏に発注、あるいはR8年度後半からアンケート等の先行実施（推定）。R8年度秋〜冬の予算要求期が営業のタイミング（推定）。</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>不明。第2次計画（H29年度策定作業）の策定支援業務の発注方式・受託者・金額は検索で確認できず。市の入札結果ページ（年度別PDF、H29年度分あり）に掲載の可能性があるが、市サイトはWebFetchブロックのため未確認。参考：市は第6次村山市総合計画等策定支援業務を公募型プロポーザルで発注（受託者・金額は未確認）しており、計画策定支援はプロポーザル方式の実績あり。</t>
         </is>
       </c>
-      <c r="J18" s="22" t="inlineStr">
+      <c r="J19" s="22" t="inlineStr">
         <is>
           <t>・第6次村山市総合計画：第5次総合計画とまち・ひと・しごと創生総合戦略がR6年度で終期を迎えるため、総合戦略を包含して策定。R7.3.6第5回策定審議会で前期基本計画（案）答申（R7年度始期と推定、計画期間は検索要約で『令和6年度から概ね10年間』とも記載あり要確認）。次期環境基本計画は新総合計画との整合が必要。・村山市立地適正化計画の作成（パブコメ実施ページあり、時期未確認）。・新「道の駅むらやま」整備（R6.3基本計画、R7.10建築設計プロポーザル審査講評）。・地球温暖化対策実行計画は事務事業編のみ確認、区域施策編・ゼロカーボンシティ宣言は確認できず（未策定の可能性、推定）。・交通：市単独の地域公共交通計画は見当たらず、山形県地域公共交通計画（R8.3.27策定の次期計画）が県全域を対象（既存調査）。</t>
         </is>
       </c>
-      <c r="K18" s="22" t="inlineStr">
+      <c r="K19" s="22" t="inlineStr">
         <is>
           <t>・第2次環境基本計画がR9年度末で終期。区域施策編（温対法の努力義務）が未確認のため、第3次環境基本計画と区域施策編（＋ゼロカーボンシティ宣言）を一体策定する提案で、事業規模と国補助（地域脱炭素関連）活用の両面から訴求。
 ・第6次総合計画（R7年度〜）・立地適正化計画・新道の駅整備と整合した環境施策（再エネ導入、道の駅のEV充電・防災拠点化等）を次期計画の柱として提案。
 ・R9年度策定に向け、R8年度内の市民・事業者アンケートや現行計画の進捗評価を先行支援する『準備業務』を市民環境課に打診（予算要求期前の情報提供）。</t>
         </is>
       </c>
-      <c r="L18" s="26" t="inlineStr">
+      <c r="L19" s="26" t="inlineStr">
         <is>
           <t>https://www.city.murayama.lg.jp/kurashi/shizen/kankyohozen/kankyoukihon.html
 https://www.city.murayama.lg.jp/kurashi/shizen/kankyohozen/kankyoukihon.files/kankyou-2.pdf
@@ -2446,65 +2526,65 @@
 https://www.pref.yamagata.jp/020057/kurashi/kendo/kotsuseisaku/ykotsu_kasseikakyougikai.html</t>
         </is>
       </c>
-      <c r="M18" s="22" t="inlineStr">
+      <c r="M19" s="22" t="inlineStr">
         <is>
           <t>調査日2026-10-02。東京都武蔵村山市（第三次環境基本計画R8〜R17策定済）の情報が検索で大量に混入したため、city.murayama.lg.jp にドメイン限定して確認。市サイトはWebFetchブロック。受託者・金額は不明。区域施策編・ゼロカーボン宣言は『見つからない』だけで、不存在は未確定。第6次総合計画の期間は要約間で表現が揺れ（R6年度から概ね10年／R7年度以降）、要確認。</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="22" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>山形県</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>朝日町</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr"/>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr"/>
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>第2次朝日町環境基本計画（H30〜R9）</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>第2次朝日町環境基本計画はH30年度に策定され、約6年後に環境情勢の変化を踏まえて見直し版を策定（町HPで確認）。町の環境行政の総合計画であり、町民・事業者・行政の行動指針を定める。目指す環境像は「みんなで守る青い空、きれいな水と緑の町」と「ゼロカーボンシティ」（検索結果要約で確認）。計画期間H30〜R9は第6次総合発展計画（H30〜R9）と同期間とみられる（期間の本文記載は既存ファクトチェックで確認済とされる）。</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>総務課 防災係（計画掲載ページのURLが somuka/bosaigakari 配下であることからの推定。係名・電話番号は未確認）</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>次期（第3次）計画の着手（審議会・委託公告・アンケート）は検索で確認できず。現行計画がR9年度末で満了し、上位計画の第6次朝日町総合発展計画もH30〜R9で、R10年度から第7次総合発展計画が始まることを町HPで確認。第7次総合発展計画と第3次環境基本計画がR8〜R9に並行して策定される見込み（推定）。予算化はR9当初予算で策定業務を発注する形が想定される（推定）。</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>不明（第2次計画H30策定時・見直し版策定時のいずれも策定支援業務の発注方式・受託者・金額は検索で見当たらず）</t>
         </is>
       </c>
-      <c r="J19" s="22" t="inlineStr">
+      <c r="J20" s="22" t="inlineStr">
         <is>
           <t>第6次朝日町総合発展計画（H30〜R9）の見直しを実施済、第7次総合発展計画はR10開始。朝日町人口ビジョン（R7.3）、朝日町観光振興計画（R6.3）、朝日町地球温暖化対策実行計画（事務事業編）、朝日町地域循環型経済構想（みどりの食料システム戦略推進交付金活用）など関連計画あり。環境基本計画見直し版で「ゼロカーボンシティ」を環境像に掲げている。過疎地域持続的発展計画（R3〜R7）は期間満了。交通は町単独の法定計画は見当たらず、山形県地域公共交通計画（R8.3策定）が県全域をカバー。</t>
         </is>
       </c>
-      <c r="K19" s="22" t="inlineStr">
+      <c r="K20" s="22" t="inlineStr">
         <is>
           <t>・第6次総合発展計画（H30〜R9）と環境基本計画が同時にR9で終わるため、第7次総合発展計画との一体的な策定・整合スケジュールを提案できる
 ・見直し版で掲げた「ゼロカーボンシティ」を受け、区域施策編（地球温暖化対策実行計画）を環境基本計画に内包する形での第3次計画策定を提案（現在確認できるのは事務事業編のみ）
 ・地域循環型経済構想・みどりの食料システムなど農業・資源循環の取組を環境基本計画の重点施策に取り込む切り口</t>
         </is>
       </c>
-      <c r="L19" s="26" t="inlineStr">
+      <c r="L20" s="26" t="inlineStr">
         <is>
           <t>https://www.town.asahi.yamagata.jp/portal/soshikinogoannai/somuka/bosaigakari/3_1/3/2438.html
 https://www.town.asahi.yamagata.jp/portal/soshikinogoannai/seisakusuishinka/sogoseisakukakari/3/2/1542.html
@@ -2514,65 +2594,65 @@
 https://www.town.asahi.yamagata.jp/material/files/group/3/jinkouvision.pdf</t>
         </is>
       </c>
-      <c r="M19" s="22" t="inlineStr">
+      <c r="M20" s="22" t="inlineStr">
         <is>
           <t>調査日 2026-10-02。山形県西村山郡朝日町（富山県・三重県の朝日町とは別。検索結果に富山県朝日町の資料が多数混在するため注意）。町HPはWebFetchがブロックされ本文未確認、内容は検索結果の要約に基づく。見直し版の策定年（R5〜R6頃、推定）・担当係名・電話番号・ゼロカーボンシティ宣言の有無と日付は未確認。区域施策編の有無も未確認。</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>福島県</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>いわき市</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr"/>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="D21" s="24" t="inlineStr"/>
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>いわき市地域公共交通計画（R5〜R9）</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>いわき市地域公共交通計画はR5.3策定、計画期間は概ね5年間（R5.3〜R10.3、既存ファクトチェックで確認済）。第二次いわき都市圏都市交通マスタープラン（R4.8策定）を上位に、いわき都市圏総合交通戦略と同時にR5.3策定。R7.1.20の第15回いわき都市圏総合都市交通推進協議会で計画の一部改定と、いわき市地域公共交通利便増進実施計画の決定（意見聴取）を承認。</t>
         </is>
       </c>
-      <c r="G20" s="22" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>いわき市 都市建設部 都市計画課 総合交通対策担当（電話0246-22-1120、sogokotsutaisaku@city.iwaki.lg.jp ※R5利便増進実施計画プロポーザル実施要領の記載）。法定協議会は「いわき都市圏総合都市交通推進協議会」（事務局：同課）。</t>
         </is>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>次期計画（R10〜）の策定業務公告・協議会審議は検索で確認できず。R5年度の利便増進実施計画策定業務が協議会発注の公募型プロポーザル（上限950万円）だったことから、次期計画も協議会による公募型プロポーザルでR9年度当初に発注される可能性が高い（推定）。R8当初予算概要では、鉄道・バスの改善による公共交通ネットワーク構築、小川地区の定額タクシー、泉・勿来・川部・山田・渡辺等での地域協議を推進と記載（R8当初予算概要で確認）。並行して市は市制60周年（R8.10）を目途に「未来ビジョン」を策定予定、（仮称）中期戦略策定支援業務（履行期限R9.3.19、次期いわき創生総合戦略を兼ねる）をプロポーザルで発注済。</t>
         </is>
       </c>
-      <c r="I20" s="25" t="inlineStr">
+      <c r="I21" s="25" t="inlineStr">
         <is>
           <t>現行計画（R5.3策定）の策定支援業務の発注方式・受託者・金額は不明（検索で見当たらず）。参考：「いわき市地域公共交通利便増進実施計画策定等業務委託」はR5年度にいわき都市圏総合都市交通推進協議会が公募型プロポーザルで発注（委託期間：契約締結日〜R6.3.15、委託料上限額9,500,000円税込、R5.7.24〜8.1書面開催の第9回協議会で発注方法を協議）。同業務の受託者名は検索結果本文で確認できず。</t>
         </is>
       </c>
-      <c r="J20" s="22" t="inlineStr">
+      <c r="J21" s="22" t="inlineStr">
         <is>
           <t>R7.1に計画一部改定・利便増進実施計画を決定。R8年度は小川地区で定額タクシー実施、泉・勿来・川部・山田・渡辺地区で公共交通確保に向けた地域協議を実施（R8当初予算概要）。いわき都市圏総合交通戦略（R5.3）、第二次都市交通マスタープラン（R4.8）、いわき市道路事業基本方針（R8.1策定、R7〜概ね10年）。市制60周年「未来ビジョン」（R8.10目途）・（仮称）中期戦略策定中。環境基本計画（第三次）中間改定版R8〜R12。</t>
         </is>
       </c>
-      <c r="K20" s="22" t="inlineStr">
+      <c r="K21" s="22" t="inlineStr">
         <is>
           <t>・現行計画はR10.3で満了。R8〜R9の未来ビジョン・（仮称）中期戦略策定と並行して、次期地域公共交通計画の評価・検討スケジュールを前倒しで組む提案
 ・小川地区の定額タクシーや泉・勿来・川部・山田・渡辺地区での地域協議の成果を、次期計画の地区別交通サービス体系として整理する支援
 ・R5年度の利便増進実施計画（協議会発注・プロポーザル）の実績を踏まえ、R7.1改定版・利便増進実施計画の評価（PDCA）から次期計画策定まで一貫支援を提案</t>
         </is>
       </c>
-      <c r="L20" s="26" t="inlineStr">
+      <c r="L21" s="26" t="inlineStr">
         <is>
           <t>https://www.city.iwaki.lg.jp/www/contents/1679296597893/simple/koukyoukoutuukeikaku1.pdf
 https://www.city.iwaki.lg.jp/www/contents/1679296597893/simple/gaiyouban.pdf
@@ -2585,65 +2665,65 @@
 https://www.city.iwaki.lg.jp/www/contents/1765350887689/simple/file02.pdf</t>
         </is>
       </c>
-      <c r="M20" s="22" t="inlineStr">
+      <c r="M21" s="22" t="inlineStr">
         <is>
           <t>調査日 2026-10-02。WebFetchは使用せず、検索結果の要約に基づく。現行計画策定業務（R4年度頃）の発注方式・受託者・金額、利便増進実施計画業務の受託者・契約額は未確認（協議会ページ・kyougikekka.pdfの本文確認が必要）。R8年度の協議会開催状況・次期計画策定予算の有無は未確認。担当電話番号はR5時点の資料記載で、現行の組織名は要確認。</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="22" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>福島県</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>鮫川村</t>
         </is>
       </c>
-      <c r="D21" s="24" t="inlineStr"/>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr"/>
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>鮫川村地域公共交通計画（R5〜R9）</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>鮫川村地域公共交通計画（R5〜R9）はR5.2.21の鮫川村地域公共交通協議会で策定（村HPで確認）。村営バス「あおぞら号」の維持とデマンド交通の導入を位置付け。デマンド交通はR5.11.14〜R6.3.31に実証運行を始め、R6.4〜R6.8に実証継続、R6.9.1〜R7.2.28は共創モデル（国の共創モデル実証事業と推定）で実証継続、R7.10から本格運行（村HP検索結果で確認）。</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>鮫川村役場 村づくり推進室（デマンド交通の所管として検索結果に記載。協議会の進行も「室長」）。電話番号・係名は未確認。</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>次期計画（R10〜）に関する協議会審議・策定業務の公告は検索で確認できず。協議会は年数回開催（例：R6年度第3回 R6.9.26）、R7年度会議録が村HPに掲載。R7.10のデマンド本格運行後の評価をR8年度に行い、R9年度に次期計画を策定する流れが見込まれる（推定）。小規模村のため、策定支援業務は随意契約または指名競争の小規模発注になる可能性（推定）。</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>不明（現行計画R5.2策定時の策定支援業務の発注方式・受託者・金額は検索で見当たらず）。デマンド交通の運行事業者も未確認。</t>
         </is>
       </c>
-      <c r="J21" s="22" t="inlineStr">
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>デマンド交通がR7.10に本格運行開始。村営バス「あおぞら号」は利用者減少・燃料費/物価高騰で厳しい運営状況との広報記載あり（R7広報）。R7.11.2に鮫川村オーガニックビレッジ宣言。地域再生計画「『道』から未来を切り拓く里山イノベーション計画」（県・村）、まち・ひと・しごと創生推進計画あり。地域おこし協力隊募集。環境基本計画は確認できず。</t>
         </is>
       </c>
-      <c r="K21" s="22" t="inlineStr">
+      <c r="K22" s="22" t="inlineStr">
         <is>
           <t>・R7.10に本格運行を始めたデマンド交通と村営バス「あおぞら号」の利用データ分析・評価を、次期計画（R10〜）の策定とあわせて受託する提案
 ・共創モデルの実証で得た知見（地域事業者との連携）を次期計画の施策として制度化し、運行経費の抑制につなげる切り口
 ・オーガニックビレッジ宣言や里山イノベーション計画（道の駅等の拠点）と連動した交通結節点の整理・観光二次交通の検討</t>
         </is>
       </c>
-      <c r="L21" s="26" t="inlineStr">
+      <c r="L22" s="26" t="inlineStr">
         <is>
           <t>https://www.vill.samegawa.fukushima.jp/sp/page/page002592.html
 https://www.vill.samegawa.fukushima.jp/sp/page/page002750.html
@@ -2654,65 +2734,65 @@
 https://www.chisou.go.jp/tiiki/tiikisaisei/dai70nintei/plan/a0090.pdf</t>
         </is>
       </c>
-      <c r="M21" s="22" t="inlineStr">
+      <c r="M22" s="22" t="inlineStr">
         <is>
           <t>調査日 2026-10-02。WebFetchは使用せず、検索結果の要約に基づく。山形県の鮭川村（さけがわむら）と検索結果が混在するので注意。計画期間R5〜R9は村HP要約で確認。所管課名（村づくり推進室）は検索要約によるもので要確認。東北運輸局の計画作成・取組事例集に掲載との要約があったが、該当資料は特定できず。オーガニックビレッジ宣言日（R7.11.2）は県SDGsページの要約による。</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="22" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>福島県</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>福島県（避難地域広域公共交通計画／避難12市町村）</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr"/>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="D23" s="24" t="inlineStr"/>
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>福島県避難地域広域公共交通計画（R5.4〜R10.3）</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>避難地域12市町村（田村市・南相馬市・川俣町・広野町・楢葉町・富岡町・川内村・浪江町・葛尾村・飯舘村・大熊町・双葉町）で住民の日常生活に必要な広域公共交通ネットワークを構築するための県計画。前身は福島県避難地域広域公共交通網形成計画（H30.3.28策定）。現行計画はR5.3策定、R5.5・R6.5・R7.3・R8.3に一部改定（直近はR8.3.27改定、計画書表紙で確認）。計画期間R5.4〜R10.3。</t>
         </is>
       </c>
-      <c r="G22" s="22" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>福島県 生活環境部 生活交通課（公共交通担当 電話024-521-7177、交通安全担当 024-521-7158、FAX 024-521-7887、〒960-8670 福島市杉妻町2-16 ※検索結果の要約による）。協議会は「福島県避難地域広域公共交通検討協議会」（ワーキンググループあり）。</t>
         </is>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>県協議会資料で、R8年度に最終評価（及び次期計画の方向性の決定）、R9年度に次期計画（R10.4〜）を策定と明記（確認済）。R8.6.25の福島県地域公共交通活性化協議会で、避難地域広域公共交通検討協議会の今年度スケジュールを報告事項として予定。R8年度はWG会議を重ねて最終評価を進める段階。次期計画策定支援業務はR9年度当初に公募型プロポーザル等で発注される見込み（推定。R9当初予算要求はR8秋〜冬に行われる見込み、推定）。</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>不明（現行計画R5.3策定時、前身の網形成計画H30.3策定時のいずれも、策定支援業務の発注方式・受託者・金額は検索で見当たらず）。参考：生活交通課ページに「福島県地域公共交通計画調査策定業務に係る公募型プロポーザル」の実施記録あり（県全域計画R6.3策定に係るものと推定。受託者・金額は未確認）。</t>
         </is>
       </c>
-      <c r="J22" s="22" t="inlineStr">
+      <c r="J23" s="22" t="inlineStr">
         <is>
           <t>避難12市町村の計画は毎年度のように一部改定されており、評価指標（利用者数・収支等）のモニタリングを毎年度実施。県全域の福島県地域公共交通計画（R6.3策定、R6.3.19に利便増進実施計画関連の一部改定）、会津圏域地域公共交通計画、県北圏域の路線バス改善（系統統合・乗合タクシー導入）など圏域別の計画あり。福島県市町村生活交通対策事業補助金。広野町環境基本計画（R7〜R17）策定済。</t>
         </is>
       </c>
-      <c r="K22" s="22" t="inlineStr">
+      <c r="K23" s="22" t="inlineStr">
         <is>
           <t>・R8年度の最終評価〜R9年度の次期計画策定が県資料で明示されており、R9発注の策定支援業務に向けて、最終評価の論点（帰還・移住人口の動向と需要推計、広域路線と町村内交通の役割分担）を整理した提案を早めに示す
 ・毎年度の一部改定・評価指標モニタリングを踏まえ、データに基づくPDCA（利用実績・収支・乗継データの一元化）を次期計画の柱とする提案
 ・12市町村ごとのデマンド交通・自家用有償・スクールバス等の多様な輸送資源を広域計画にどう位置付けるか、県全域計画・圏域計画との整合の切り口</t>
         </is>
       </c>
-      <c r="L22" s="26" t="inlineStr">
+      <c r="L23" s="26" t="inlineStr">
         <is>
           <t>https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html
 https://www.pref.fukushima.lg.jp/uploaded/attachment/738677.pdf
@@ -2726,65 +2806,370 @@
 https://www.pref.fukushima.lg.jp/uploaded/attachment/622613.pdf</t>
         </is>
       </c>
-      <c r="M22" s="22" t="inlineStr">
+      <c r="M23" s="22" t="inlineStr">
         <is>
           <t>調査日 2026-10-02。WebFetchは使用せず、検索結果の要約に基づく。R8年度最終評価・R9年度次期計画策定は協議会資料（756354.pdf等）の要約で確認。次期計画策定支援業務の公告・予算額は未確認。過去の策定支援業務（H29・R4頃）の受託者・金額は未確認（県の入札・契約情報や議会資料での確認が必要）。電話番号は生活交通課ページ要約によるもので、担当名は要確認。</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="22" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>須賀川市</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr"/>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>第3次須賀川市環境基本計画（中間改定版）（H30〜R9、期間は推定）</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>第3次須賀川市環境基本計画（H30〜R9の10年間、推定）。中間年の令和4年（2022年）に、環境課題をめぐる国際的潮流や国・県の動き、各施策の取組状況を踏まえ取組内容・目標値等を見直し、R4.3に【中間改定】版を公表（検索要約）。関連計画として地球温暖化対策実行計画（区域施策編、R4〜R12）、第3期エコ実行プラン（事務事業編）、R5.5.29カーボンニュートラル宣言。望ましい環境像・基本目標の具体的文言は検索で確認できず（要確認）。参考：須賀川市地域公共交通計画はR6〜R10（R7.1.29一部改定、検索要約）でR9終期ではないため対象外。</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>環境課（〒962-8601 須賀川市八幡町135）。環境保全係 0248-88-9130／環境衛生係 0248-88-9129（検索要約）。環境基本計画の担当は環境保全係と推定。交通計画は別課（公共交通担当、未確認）。</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>次期（第4次）環境基本計画の策定業務・審議会諮問・プロポ公告は検索で見当たらず（R8年度入札結果ページ・発注見通しページは存在するが中身未確認）。現行計画R9終期のため、通常はR8〜R9の2か年で策定（R8年度に基礎調査・市民アンケート、R9年度に計画案・環境審議会諮問・パブコメ）と推定。ただし市の第9次総合計画「まちづくりビジョン2023」もR5〜R9でR9終期のため、次期総合計画（R10〜）と同時並行・整合をとる形で、R9年度単年度策定（R9当初予算計上→R9春プロポ）となる可能性もある（推定）。R8年度当初予算・施政方針での言及は検索で確認できず。</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>不明。現行第3次計画（H29年度策定業務と推定）・中間改定（R3年度業務と推定）とも、発注方式・受託者・金額は検索で確認できず。試行：「須賀川市 環境基本計画 策定支援業務 委託 プロポーザル」「須賀川市 環境基本計画 策定 委託 株式会社 平成29年度 OR 令和3年度 中間見直し 業務」「須賀川市 入札結果 環境基本計画 業務委託」（site限定）等。市サイトはWebFetch/curlともエグレス遮断で計画書PDF巻末・入札結果PDFを直接確認できず。入札結果は年度別・課別に公表（例：令和7年度入札結果ページ）されているため、R3年度分の環境課結果を要確認。</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>・R5.5.29「須賀川市カーボンニュートラル宣言」（2050年CO2排出実質ゼロ）。・地球温暖化対策実行計画（区域施策編）R4〜R12。・第9次総合計画「須賀川市まちづくりビジョン2023」R5〜R9（次期総合計画の策定がR8〜R9に始まる見込み、教育振興基本計画に「次期須賀川市総合計画との整合」記載）。・須賀川市地域公共交通計画R6〜R10（R7.1.29一部改定、基本目標：生活を支え交流を創る公共交通ネットワーク構築／誰もが利用しやすい環境整備／持続可能な公共交通の基盤整備）、市内循環バス運行。・都市計画マスタープラン改定、緑の基本計画、第3期中心市街地活性化基本計画。・年次報告書『須賀川市の環境』（R7.5）を公表。</t>
+        </is>
+      </c>
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>・第3次環境基本計画（中間改定版）はR9終期で、総合計画（まちづくりビジョン2023）もR9終期→次期総合計画と第4次環境基本計画の同時策定スケジュール（R8基礎調査かR9単年度か、予算要求時期）を環境保全係にヒアリング
+・カーボンニュートラル宣言（R5.5）・区域施策編（R4〜R12）を第4次環境基本計画に統合（温対計画・地域気候変動適応計画・生物多様性地域戦略の一体化）する構成案を提案
+・年次報告『須賀川市の環境』の指標進捗を用いた現行計画の評価・市民アンケート設計など、策定前年度の基礎調査業務の切り出し発注を打診</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="inlineStr">
+        <is>
+          <t>https://www.city.sukagawa.fukushima.jp/kurashi/gomi_recycle/kankyo_hozen/1002334/index.html
+https://www.city.sukagawa.fukushima.jp/kurashi/gomi_recycle/kankyo_hozen/1002334/1014545.html
+https://www.city.sukagawa.fukushima.jp/kurashi/gomi_recycle/kankyo_hozen/1002334/1010858.html
+https://www.city.sukagawa.fukushima.jp/material/files/group/47/r05shinokankyo.pdf
+https://www.city.sukagawa.fukushima.jp/kurashi/koutsu/koutsu_keikaku/1015962.html
+https://www.city.sukagawa.fukushima.jp/shisei/keikaku/sogo_keikaku/1010579/index.html
+https://www.city.sukagawa.fukushima.jp/1016863/1017337.html
+https://www.city.sukagawa.fukushima.jp/jigyosya/nyusatsu/1010733/nyusatsu_kekka/index.html
+https://www.city.sukagawa.fukushima.jp/jigyosya/nyusatsu/1010733/nyusatsu_kekka/1/index.html
+https://www.city.sukagawa.fukushima.jp/jigyosya/nyusatsu/1003442.html
+https://www.env.go.jp/policy/local_keikaku/sakutei2/07/07207.html</t>
+        </is>
+      </c>
+      <c r="M24" s="22" t="inlineStr">
+        <is>
+          <t>計画期間：推定（強）。市サイト限定検索3回の要約がいずれも「The Third Environmental Basic Plan spans from fiscal year 2018 to fiscal year 2027」「中間改定は2022年3月」と一致するが、本文の逐語引用は得られず（"平成30年度から令和9年度"の完全一致検索ではヒットせず）。市サイトはWebFetch・curlともエグレス遮断で本文未確認。交通計画はR6〜R10（検索要約）でR9終期ではないため対象外とした。WebSearch使用17回。電話番号は検索要約由来（要確認）。須賀川市は「すかがわ」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>相馬市</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr"/>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>第2次相馬市環境基本計画（見直し版）（H30〜R9、期間は推定）</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>相馬市環境基本計画（第2次）。相馬市環境基本条例に基づき環境保全施策を総合的・計画的に推進する計画で、平成30年3月策定・計画期間10年間（→H30〜R9と算出）。策定から5年以上経過し、社会情勢の変化や科学技術の進展に対応するため見直しを実施（見直し時期はR5〜R6頃と推定、未確認）。計画書は第1章、第2章（分割）、第3章〜第5章のPDFで公開。望ましい環境像・基本目標は検索で確認できず（要確認）。</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>生活環境課 環境係（市役所庁舎1階、〒976-8601 相馬市中村字北町63-3）電話 0244-37-2143（検索要約）。公共交通（おでかけミニバス）は企画政策課 0244-37-2132。</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>第3次環境基本計画の策定業務・審議会・プロポ公告は検索で見当たらず。現行計画R9終期のため、R8〜R9での策定（R9年度単年度策定が有力、R9当初予算計上→R9春発注）と推定。並行して次期総合計画「第6次相馬市長期総合計画」（現行：相馬市マスタープラン2017、10年ぶりの見直し）の策定が進行中：R8.8.5総合計画審議会（委員22人、うち女性10人・公募大学生4人、全4回審議予定、市民アンケート実施）、R8.9.17第1回新長期総合計画策定委員会（市長あいさつ）。次期総合計画はR10開始と推定され、第3次環境基本計画は同計画と整合させる形で策定されると推定。R8年度重点施策実行計画（38施策）での環境基本計画への言及は確認できず。</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>不明。第2次計画（H29年度策定業務と推定）・見直し（R4〜R5年度頃と推定）の発注方式・受託者・金額は検索で確認できず。試行：「相馬市 環境基本計画 策定業務 委託 受託 株式会社」（南相馬市・他市のみヒット）、「相馬市環境基本計画（第2次）見直し版 令和6年3月 OR 令和5年3月 第1章 計画期間」等。市サイトはWebFetchエグレス遮断で計画書PDF巻末を確認できず。見直しは職員直営の可能性もある（推定）。</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>・新市長：2025.12.21市長選で新人のあべ勝弘氏が無投票当選（立谷前市長から交代、go2senkyo）。R8.2.5臨時会で「誰もが安心し、誇りを持って、笑顔で暮らせる相馬市」を掲げる。・公共交通：65歳以上無料の「おでかけミニバス」（R5.1国内初のグリーンメタンバス導入）について、乗車率低迷を踏まえ固定ルート型から「デマンド型予約運行」へ見直し（R8新年あいさつ）。地域公共交通計画は検索で確認できず（未策定の可能性、要確認）。・R8.3議会：生ごみ処理器等設置奨励金を拡充しごみ減量・CO2排出抑制。R8.4からプラスチック分別変更等のごみ減量新施策。・相馬港が「サーキュラーエコノミーポート」に選定（R8.8議会あいさつ）。・そうまIHIグリーンエネルギーセンター（水素活用・CO2フリーの循環型地域社会）。・地球温暖化対策実行計画（区域施策編）策定済（期間未確認）。ゼロカーボンシティ宣言は検索で確認できず。・都市計画マスタープラン・立地適正化計画を策定（R7頃）。</t>
+        </is>
+      </c>
+      <c r="K25" s="22" t="inlineStr">
+        <is>
+          <t>・第6次長期総合計画の策定（R8.8審議会発足、R8.9策定委員会）と同時期に第2次環境基本計画がR9終期→第3次計画の策定時期・予算要求（R9当初かR8補正か）を生活環境課環境係にヒアリング。総合計画の市民アンケート結果を環境計画にも活用する効率的な進め方を提案
+・サーキュラーエコノミーポート選定・IHIグリーンエネルギーセンター・ごみ減量新施策を軸に、第3次計画を「循環経済・脱炭素」中心に再構成し区域施策編も統合する構成案を提示
+・新市長体制下でおでかけミニバスのデマンド化を進めている→地域公共交通計画（法定計画）の策定やデマンド実証の効果検証支援を企画政策課に別途提案</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="inlineStr">
+        <is>
+          <t>https://www.city.soma.fukushima.jp/shinososhiki/seikatsukankyoka/keikaku_shisaku/1622.html
+https://www.city.soma.fukushima.jp/shinososhiki/seikatsukankyoka/index.html
+https://www.city.soma.fukushima.jp/shinososhiki/somuka/shinogaiyo/1517.html
+https://www.city.soma.fukushima.jp/shinososhiki/seikatsukankyoka/kankyo_gomi_recycle/3/1014.html
+https://www.city.soma.fukushima.jp/shinososhiki/kikakuseisakuka/keikaku_shisaku/1634.html
+https://www.city.soma.fukushima.jp/shinososhiki/hishoka/shichoshitsu/shichonoaisatsu/r8/8gatu/20590.html
+https://www.city.soma.fukushima.jp/shinososhiki/kikakuseisakuka/keikaku_shisaku/20579.html
+https://www.city.soma.fukushima.jp/shinososhiki/hishoka/shichoshitsu/shichonoaisatsu/r8/9gatu/20891.html
+https://www.city.soma.fukushima.jp/shinososhiki/hishoka/shichoshitsu/gikaiaisatsu/r8/20739.html
+https://www.city.soma.fukushima.jp/shinososhiki/hishoka/shichoshitsu/gikaiaisatsu/r8/19514.html
+https://www.city.soma.fukushima.jp/shiseijoho/shichoshitsu/shityou_hitokoto/2026/19137.html
+https://www.city.soma.fukushima.jp/shinososhiki/kikakuseisakuka/seikatsu/1/odekake_bus.html
+https://www.city.soma.fukushima.jp/shinososhiki/hishoka/shichoshitsu/hitokoto/2025/17575.html
+https://www.city.soma.fukushima.jp/shinososhiki/shokokankoka/keikaku_shisaku/1644.html
+https://www.city.soma.fukushima.jp/shinososhiki/kikakuseisakuka/keikaku_shisaku/3220.html
+https://go2senkyo.com/local/jichitai/639</t>
+        </is>
+      </c>
+      <c r="M25" s="22" t="inlineStr">
+        <is>
+          <t>計画期間：推定（強）。検索要約に計画ページ本文の引用と見られる文言「平成30年3月に相馬市環境基本計画（第二次）を策定し、10年間を計画期間としておりますが、当計画は策定より5年以上経過しているため…計画の見直しを行いました」が複数回出現。H30〜R9は「10年間」からの算出で、終期年度の明記は未確認。見直し版の公表年月も未確認。市サイトはWebFetchエグレス遮断。WebSearch使用15回（全体32回）。南相馬市（第3次南相馬市環境基本計画・ゼロカーボン推進計画等）の結果が多数混入したが除外済。新市長名は選挙情報サイト要約由来（要確認）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>川俣町</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr"/>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>福島県避難地域広域公共交通計画（県・避難12市町村の広域計画、R5.4〜R10.3＝R5〜R9）</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>福島県避難地域広域公共交通計画（福島県生活交通課所管、令和5年3月30日策定、R5.5・R6.5・R7.3・R8.3（R8.3.27）一部改定）。計画期間は令和5年4月〜令和10年3月の5年間。前身は福島県避難地域広域公共交通網形成計画（H30.3.28策定、H30〜R4）で、改正活性化再生法に対応して移行。対象は田村市・南相馬市・川俣町・広野町・楢葉町・富岡町・川内村・大熊町・双葉町・浪江町・葛尾村・飯舘村の12市町村。避難地域住民の日常生活維持・帰還促進に必要な広域公共交通ネットワーク構築が目的。協議体は福島県避難地域広域公共交通検討協議会。なお町単独の現行地域公共交通計画は確認できず（川俣町地域公共交通会議がH21.3に旧法の地域公共交通総合連携計画を策定したのみ）。</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>【県計画】福島県 生活環境部 生活交通課（https://www.pref.fukushima.lg.jp/sec/16005d/）。電話は検索で未確認。【町】川俣町 政策推進課 政策調整係（生活交通担当、電話024-566-2111＝代表と推定）。川俣町地域公共交通会議の事務局も同課と推定。</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>【県広域計画】R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画策定（R10.4開始）予定（県資料の検索要約で確認、R8.6.25福島県地域公共交通活性化協議会資料756354.pdfに避難地域広域公共交通検討協議会の今年度スケジュール）。次期計画策定支援業務の公告・プロポーザルは検索で確認できず（R9年度当初予算で発注の可能性＝推定、公告はR9春〜夏と推定）。発注主体は県（生活交通課）であり町ではない点に注意。【町】ふれあいタクシー（デマンド）の見直しについてR8.7.17〜7.31にパブリックコメント実施（乗降場所の廃止・追加、地区別ダイヤ見直し）→R8年度下期〜R9に運行変更見込み（推定）。川俣町地域公共交通会議は直近でR7.2.17（令和6年度第1回）開催を確認。町単独の地域公共交通計画策定の動きは検索で確認できず。</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>不明。県のH29年度（網形成計画、H30.3策定）・R4年度（現行計画、R5.3策定）とも策定支援業務の受託者・発注方式・金額は検索で確認できず。試行クエリ：「避難地域広域公共交通計画 策定 業務委託 福島県 受託」「"避難地域広域公共交通" 業務 委託 契約 落札 OR 受注 OR 随意契約」「避難地域 広域公共交通 計画策定 業務 プロポーザル 生活交通課」「福島県避難地域広域公共交通網形成計画 策定 調査 業務 平成29年度 委託 コンサルタント」「福島県避難地域広域公共交通計画 令和4年度 策定 業務 委託料 契約 生活交通課 入札結果」。県サイトPDFはcurlでも403（プロキシ拒否）で計画書巻末を確認できず。計画書738677.pdf巻末・県の契約公表（生活交通課の随意契約結果）を要確認。</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>・町の公共交通：福島交通路線（南相馬福島線、月舘経由川俣線）、JRバス福浪線（川高前〜福島駅）、自治体バス川俣松川線・川俣飯野線（福島市と共同運行、カネハチタクシー委託）、デマンドタクシー山木屋・小綱木線（ゴリラタクシー）、ふれあいタクシー（地区別デマンド）。・福沢地区は路線バス福沢循環線を廃止しデマンド乗合タクシー＋スクールバスで代替（国交省資料）。・ふれあいタクシー見直しパブコメ（R8.7、乗降場所にオリナスかわまた等を追加）。・環境：川俣町地域まるごと脱炭素計画（地球温暖化対策実行計画 区域施策編）、循環型社会形成推進地域計画（R3〜R7）あり。環境基本計画は確認できず。ゼロカーボン宣言・総合計画の改定時期は検索で確認できず。</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>・県の避難地域広域計画はR8最終評価→R9次期策定（R10開始）。発注者は県生活交通課のため、県のR9当初予算・R9公告を本命として追跡し、12市町村の個別データ収集（川俣町分含む）の協力体制を提案材料にする（受託者・前回金額は要確認）
+・川俣町は現行の町単独法定計画が見当たらない（H21旧法連携計画のみ）一方、ふれあいタクシー見直し（R8.7パブコメ）・福島市との共同自治体バスなど再編が進行中→町単独の地域公共交通計画（利便増進・デマンド最適化）策定の必要性を政策推進課政策調整係にヒアリング
+・地域まるごと脱炭素計画と交通（EV化・デマンド効率化）の連携余地。環境基本計画が無いため、環境分野計画の統合・策定ニーズも確認（推定）</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="inlineStr">
+        <is>
+          <t>https://www.pref.fukushima.lg.jp/sec/16005d/hinankeikaku.html
+https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html
+https://www.pref.fukushima.lg.jp/uploaded/attachment/738677.pdf
+https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-kyougikai.html
+https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-public.html
+https://www.pref.fukushima.lg.jp/uploaded/attachment/756354.pdf
+https://www.pref.fukushima.lg.jp/sec/16005d/chiikikoukyoukasseikakyougikai.html
+https://www.pref.fukushima.lg.jp/sec/16005d/
+https://www.town.kawamata.lg.jp/site/kurashi-tetsuzuki/kawamatakoukyokotsu.html
+https://www.town.kawamata.lg.jp/site/kurashi-tetsuzuki/bus-koukyoukoutsuu.html
+https://www.town.kawamata.lg.jp/site/kurashi-tetsuzuki/bus-matsukawa-iino3.html
+https://www.town.kawamata.lg.jp/site/kurashi-tetsuzuki/fureaitakusi.html
+https://www.town.kawamata.lg.jp/site/chosei-shisetsu/demando-pabu.html
+https://www.town.kawamata.lg.jp/soshiki/2/
+https://www.mlit.go.jp/common/000045923.pdf
+https://www.town.kawamata.lg.jp/site/chosei-shisetsu/chiikimarugotodathutansokeikaku.html</t>
+        </is>
+      </c>
+      <c r="M26" s="22" t="inlineStr">
+        <is>
+          <t>期間：確認済（県サイト検索本文「令和5年4月から令和10年3月までの計画期間」、計画書表題「令和５年３月（令和５年５月、令和６年５月、令和７年３月、令和８年３月一部改定）」）。次期スケジュール（R8最終評価・R9策定）は県資料の検索要約ベースで推定寄り（前回調査では本文確認）。WebSearch使用15回（川俣町分）。県サイト・町サイトへの直接取得はプロキシ403で不可。電話024-566-2111は検索要約で確認（代表番号と推定）。宮城県川崎町・山形県川西町等とは別。目標計画の発注者は県であり町単独の営業案件ではない点に留意。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>三春町</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr"/>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>三春町地域公共交通計画（R5〜R9）</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>三春町地域公共交通計画（町単独、三春町地域公共交通活性化協議会、計画期間 令和5年度〜令和9年度の5年間）。R6.6・R7.8（令和7年度第2回協議会）に一部改定。基本理念「町民の日常の移動を支える利便性の高い持続可能な地域公共交通の実現」。基本方針は(1)町内の利用しやすい公共交通ネットワークの実現（買物・通院・通学を支える、既存サービス見直しと新たな公共交通導入検討）、(2)近隣市町村と連携した広域移動ニーズへの対応 等。町営バス（特別会計）・福島交通路線バスが軸。</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>住民課 生活環境グループ（バス事業担当、電話0247-62-2147）。三春町バス管理センター（0247-62-2020）。※検索要約では「まちづくり推進課」が公共交通対策・町営バス事業を担当との記載もあり、R8年度以降の組織改編で移管の可能性（要確認）。</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>次期計画（R10〜）の策定委託・プロポーザル・パブコメは検索で確認できず。終期R9のため、R8年度に評価・検討（R8.3にユニ・トランドと交通・人流データ活用の包括連携協定）、R9年度当初予算で策定支援を発注しR9中に策定と推定。R8年度当初予算：町営バス事業特別会計1億1,234万円（前年度9,971万円から12.7%増）、総額144億1,456万円（R8予算説明書で確認）。R8予算説明書（17.5MB）内の計画策定費計上有無は未確認。町営バスはR7.10・R8.4に運行見直し（時刻表R8.4.1改正）。</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>不明。R4年度の策定支援業務の受託者・発注方式・金額は検索で確認できず。試行：「三春町地域公共交通計画 策定業務 委託 令和4年度」「三春町 入札結果 令和4年度 公共交通計画 策定 業務」（町HP内、入札情報ページ https://www.town.miharu.fukushima.jp/life/2/17/62/ に令和4年度入札等結果あり、詳細未確認）「三春町 地域公共交通計画 策定 委託料 議会 一般会計予算」。参考：R6年度補正予算（第8号、R7.3）で地域公共交通費の委託料△740万円（三春町公共交通実証プロジェクト事業＝共創モデル実証運行業務関連）。町HPは直接取得不可（プロキシ403）。</t>
+        </is>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
+        <is>
+          <t>・町営バスR7.10・R8.4運行見直し、福島交通路線バスもR7.10再編。・県中・県南圏域地域公共交通利便増進実施計画（R7.10〜R13.3）に含まれる。・R8.3.30ユニ・トランド（ユニリタグループ）と地方創生の包括連携協定（交通・人流・物流データの収集・可視化・分析、システム構築、人的支援）。・国交省共創モデル実証プロジェクト活用（R6年度）。・第8次三春町長期計画（R7年度開始、まちづくり推進課所管）。・三春町環境条例（H12）はあるが環境基本計画・ゼロカーボン宣言は検索で確認できず。</t>
+        </is>
+      </c>
+      <c r="K27" s="22" t="inlineStr">
+        <is>
+          <t>・現行計画はR9終期・R6/R7と毎年改定し町営バス見直し（R7.10・R8.4）を回している→次期計画はR9策定が濃厚。R9当初予算要求（R8秋〜冬）前の今が提案タイミング（推定）
+・ユニ・トランドとのデータ連携協定（R8.3）があり、次期計画のデータ分析部分は同社が担う可能性→当社はアンケート・協議会運営・計画書とりまとめ、利便増進実施計画（県中・県南圏域）との整合で差別化
+・所管課が住民課生活環境グループかまちづくり推進課かが曖昧→組織改編有無を確認し、担当窓口を特定（要確認）</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="inlineStr">
+        <is>
+          <t>https://www.town.miharu.fukushima.jp/soshiki/4/kokyoukotsu.html
+https://www.town.miharu.fukushima.jp/life/1/9/44/
+https://www.town.miharu.fukushima.jp/soshiki/4/tyoueibasu.html
+https://www.town.miharu.fukushima.jp/soshiki/4/miharubus_jikoku.html
+https://www.town.miharu.fukushima.jp/soshiki/4/
+https://www.town.miharu.fukushima.jp/soshiki/27/
+https://www.town.miharu.fukushima.jp/soshiki/3/8yosan_1_1_1.html
+https://www.town.miharu.fukushima.jp/soshiki/3/uploads/%EF%BC%B28%E4%BA%88%E7%AE%97%E8%AA%AC%E6%98%8E%E6%9B%B8%EF%BC%88%E5%85%AC%E8%A1%A8%EF%BC%89.pdf
+https://www.town.miharu.fukushima.jp/soshiki/3/uploads/01_R7.3%E8%A3%9C%E6%AD%A3%EF%BC%88%E4%B8%80%E8%88%AC%EF%BC%89%20(1).pdf
+https://www.town.miharu.fukushima.jp/life/2/17/62/
+https://www.town.miharu.fukushima.jp/soshiki/27/dai8zityoukei.html
+https://www.logi-today.com/930374
+https://www.town.miharu.fukushima.jp/soshiki/4/fukushimakotsubus.html
+https://www.mlit.go.jp/sogoseisaku/transport/content/001895410.pdf</t>
+        </is>
+      </c>
+      <c r="M27" s="22" t="inlineStr">
+        <is>
+          <t>期間：確認済（町HP検索本文「計画期間は令和5年度から令和9年度までの5年間」）。改定R6.6・R7.8も町HP検索結果で確認。WebSearch使用16回（三春町分、両町計31回）。所管課は住民課生活環境グループ（電話0247-62-2147）だが、まちづくり推進課担当との要約もあり要確認。第8次長期計画の期間は要約で「R7〜R11の5年」とあるが10年構想との記載もあり推定扱い。fukushimakotsubus.html・001895410.pdfは前回調査で検索に出たURL。他県に同名自治体なし（田村郡三春町）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>常陸大宮市</t>
         </is>
       </c>
-      <c r="D23" s="24" t="inlineStr"/>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="D28" s="24" t="inlineStr"/>
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>常陸大宮市地域公共交通計画（R5〜R9）／第2次常陸大宮市環境基本計画 後期計画（R5〜R9）</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>【交通】常陸大宮市地域公共交通計画（R5.2策定、R5〜R9の5年間、前身は網形成計画H30.3策定・R4終了）。基本理念「住みたいまちを支える、持続可能で便利な地域公共交通」。JR水郡線・高速バス・広域路線バスは事業者へ利用促進を働きかけ、路線バス利用困難区域の移動手段として乗合タクシーを位置づけ、バス停のベンチ・上屋設置等の待合環境改善を検討。【環境】第2次環境基本計画（H30〜R9の10年）の後期計画（R5〜R9）。中間見直しに合わせ地球温暖化対策実行計画（区域施策編、2050年ゼロカーボンシティ実現に向けて）と地域気候変動適応計画を包含し一体化。→交通・環境とも同時にR9終期。</t>
         </is>
       </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>【交通】地域創生課 地域創生グループ（本庁1階、〒319-2292 常陸大宮市中富町3135-6、電話0295-52-1111（代表））。協議体：常陸大宮市地域公共交通会議。【環境】担当課は検索で確認できず（環境審議会あり、要確認）。</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>交通・環境とも次期計画（策定支援委託・アンケート・プロポ）の情報は検索で見つからず（R8.10時点）。前回の交通計画はR4年度単年度で公募型プロポーザル→R5.2策定のパターン。同様ならR9年度当初予算に次期交通計画策定支援委託を計上（R8秋〜冬に予算要求）、R9春〜夏にプロポ公告の見込み（推定）。環境（第3次環境基本計画、R10〜）も同時期に策定業務が発生、温対実行計画（区域施策編）・適応計画の一体改定となる見込み（推定）。総合計画の改定時期との連動も要確認。</t>
         </is>
       </c>
-      <c r="I23" s="25" t="inlineStr">
+      <c r="I28" s="25" t="inlineStr">
         <is>
           <t>【交通・前回】「常陸大宮市地域公共交通計画策定支援業務」を公募型プロポーザルで発注（R4年度、履行期間：契約締結日〜R5.3.31、提案上限額8,459,000円（税込））（市サイト page007375 の検索要約より）。受託者・契約金額は検索で確認できず（候補者選定結果の公表ページ見当たらず）→計画書巻末（1685520960_doc_100_0.pdf）またはプロポーザル情報ページで要確認。【参考】網形成計画（H29年度）・観光振興基本計画も公募型プロポで発注実績あり（観光は実施要領のみ確認）。AIデマンド交通システム導入業務委託も候補者選定委員会方式（page008456、結果内容は未確認）。【環境・後期計画】策定支援業者は不明（未調査に近い、検索で見つからず）。</t>
         </is>
       </c>
-      <c r="J23" s="22" t="inlineStr">
+      <c r="J28" s="22" t="inlineStr">
         <is>
           <t>・R5.12.1から予約制乗合タクシー「のるーと常陸大宮」にAIデマンド交通システムを導入（市内全域、ドアtoドア、運行は常陸大宮市社会福祉協議会）。R7.6予約方法変更、R7.7からLINE予約対応。・公共ライドシェア「ノッカル常陸大宮」の実証運行を開始（時期は要確認）。・JR水郡線沿線（存続・利用促進が論点）。・常陸大宮駅周辺整備事業・駅西交流拠点整備（実施設計R7.3完了）で交通結節点整備進行中。・ゼロカーボンシティ宣言済（宣言年は資料表記が「2022（令和2）年7月」と不整合、要確認）。・公共交通ガイドブック発行。</t>
         </is>
       </c>
-      <c r="K23" s="22" t="inlineStr">
+      <c r="K28" s="22" t="inlineStr">
         <is>
           <t>・交通計画と環境基本計画が同じR9終期→次期策定（R9年度発注見込み、推定）に向け、交通の脱炭素（EV乗合タクシー等）を両計画で整合させる一体的な支援を提案。予算要求前のR8秋〜冬に地域創生課・環境担当課を訪問
 ・のるーと常陸大宮（AIデマンド）とノッカル常陸大宮（公共ライドシェア）の実績データ評価・役割分担整理、水郡線・駅周辺整備との結節を次期計画の論点として提示
 ・前回は公募型プロポ・上限約846万円の単年度策定→同規模・同方式を想定した提案準備（受託者は要確認、競合把握のため計画書巻末を確認）</t>
         </is>
       </c>
-      <c r="L23" s="26" t="inlineStr">
+      <c r="L28" s="26" t="inlineStr">
         <is>
           <t>https://www.city.hitachiomiya.lg.jp/kurashi_gyousei/gyousei/plan/r0/page003126.html
 https://www.city.hitachiomiya.lg.jp/page/page007375.html
@@ -2802,65 +3187,65 @@
 https://www.city.hitachiomiya.lg.jp/kakoiba/progress/kouryu/jissesekkei/page010868.html</t>
         </is>
       </c>
-      <c r="M23" s="22" t="inlineStr">
+      <c r="M28" s="22" t="inlineStr">
         <is>
           <t>交通・環境ともR9終期で両方狙える最有望先。次期発注情報は未公表。前回交通は公募型プロポ（R4、上限8,459,000円）、受託者未確認。</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="22" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="22" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>阿見町</t>
         </is>
       </c>
-      <c r="D24" s="24" t="inlineStr"/>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="D29" s="24" t="inlineStr"/>
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>阿見町地域公共交通計画（R5〜R9）</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>阿見町地域公共交通計画：令和5年2月、阿見町地域公共交通活性化協議会が策定（R5〜R9年度）。章構成は背景・目的／地域の現況／関連計画／課題／基本方針／目標・施策。デマンドタクシー「あみまるくん」の運行・利便性向上と路線バスの確保維持が中心施策（施策詳細は計画本文で要確認）。前身はH21〜H22の地域公共交通総合連携計画策定調査事業。※環境基本計画（第2次、R3〜R12）はR9終了ではないため対象外。</t>
         </is>
       </c>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>産業建設部 都市計画課（阿見町地域公共交通活性化協議会事務局）TEL 029-888-1111（内線234）（検索要約で確認、内線は要確認）</t>
         </is>
       </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="H29" s="22" t="inlineStr">
         <is>
           <t>現計画はR9年度末で終了→次期計画はR8〜R9年度で策定作業が必要。前回は協議会がR3〜R4の2か年事業として策定しており、同様ならR8年度着手・R9年度末策定が想定されるが、令和8年6月1日のR8第1回協議会ではアンケート調査結果報告とR9確保維持事業計画の審議が確認できるのみで、次期計画策定業務の発注は未確認（要確認）。前回同様に協議会予算で委託する場合、R8年度協議会予算または補正・R9年度当初予算での計上が見込まれる（推定）。</t>
         </is>
       </c>
-      <c r="I24" s="25" t="inlineStr">
+      <c r="I29" s="25" t="inlineStr">
         <is>
           <t>現行計画（R5.2策定）：協議会がR3〜R4年度の2か年で「阿見町地域公共交通計画策定事業」を実施。R4年度協議会予算で計画策定委託料 6,600,000円（検索要約で確認、kyougisiryo.pdf／SHIDAI.pdf系資料、要確認）。発注方式・受託者は不明。試行：「プロポーザル」「受託者」「入札結果」「落札」「委託契約 締結」「協議会予算」等で計12件検索したが受託者名は出ず。計画本文PDF巻末・協議会資料の直接取得はアクセス不可（403）。※R5年度に茨城大学への委託研究の報告あり（計画策定とは別件）。</t>
         </is>
       </c>
-      <c r="J24" s="22" t="inlineStr">
+      <c r="J29" s="22" t="inlineStr">
         <is>
           <t>デマンドタクシー「あみまるくん」の利用者満足度アンケート実施（R5年度）、R7年度に効率化に向けた実証実験の記述あり（要確認）。茨城大学への委託研究（R5年度報告）。ゼロカーボンシティ宣言（令和4年6月1日、町民生活部生活環境課）。第2次環境基本計画（R3〜R12）は第6次阿見町総合計画の環境施策を担う位置づけ。R8.6.1協議会で公共交通に関するアンケート調査結果を報告＝次期計画の基礎調査の可能性（推定）。</t>
         </is>
       </c>
-      <c r="K24" s="22" t="inlineStr">
+      <c r="K29" s="22" t="inlineStr">
         <is>
           <t>・現計画R9年度末終了。前回はR3〜R4の2か年・R4委託料660万円規模で策定しており、次期計画も2か年で進める場合はR8年度中の発注準備が必要——スケジュール・予算化状況を都市計画課に確認
 ・R8.6の協議会で報告したアンケート結果やR7実証実験の成果を次期計画の評価・目標設定にどう繋ぐか（あみまるくん効率化、路線バス維持）を切り口に提案
 ・ゼロカーボンシティ宣言（R4.6）と交通計画の連携（公共交通利用転換・EV等）を、環境部局との横断テーマとして提示</t>
         </is>
       </c>
-      <c r="L24" s="26" t="inlineStr">
+      <c r="L29" s="26" t="inlineStr">
         <is>
           <t>https://www.town.ami.lg.jp/cmsfiles/contents/0000009/9640/keikaku.pdf
 https://www.town.ami.lg.jp/cmsfiles/contents/0000009/9640/gaiyo.pdf
@@ -2875,65 +3260,65 @@
 https://www.town.ami.lg.jp/cmsfiles/contents/0000012/12659/1syou.pdf</t>
         </is>
       </c>
-      <c r="M24" s="22" t="inlineStr">
+      <c r="M29" s="22" t="inlineStr">
         <is>
           <t>WebSearch12回使用。町サイトへの直接取得は403でブロック。受託者は計画書巻末か協議会R3年度資料で確認できる可能性大。</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="22" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>五霞町</t>
         </is>
       </c>
-      <c r="D25" s="24" t="inlineStr"/>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="D30" s="24" t="inlineStr"/>
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>五霞町地域公共交通計画（R5.3策定・R6.5変更、R5〜R9と推定）</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>五霞町地域公共交通計画：令和5年3月、五霞町地域公共交通会議が策定、令和6年5月変更。計画期間は目次に「1.3 地域公共交通計画の期間」があるが年数は検索結果で未確認（R5〜R9の5年間と推定・要確認）。高齢化を踏まえ町の実情に合った利便性が高く持続可能な公共交通網の形成が目的。運行体系は①ごかりん号（朝晩定時運行）②ごかりん号（日中オンデマンド運行、アプリ・電話予約）③五霞町役場前〜幸手駅線（代替バス）の3系統。※環境基本計画（改定版、R5〜R14）はR9終了ではないため対象外。</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G30" s="22" t="inlineStr">
         <is>
           <t>生活安全課（ごかりん号・公共交通の窓口、検索要約で確認）。電話番号は未確認（町代表は0280-84-1111と推定・要確認）</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H30" s="22" t="inlineStr">
         <is>
           <t>現計画がR9年度末終了なら、次期計画はR8〜R9年度に策定作業が必要（推定）。次期計画策定業務の公告・予算計上・公共交通会議での策定議題はいずれも検索で確認できず（未着手または非公開の可能性）。R9年度単年での策定ならR9当初予算要求（R8秋〜冬）が判断時期（推定）。</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
+      <c r="I30" s="22" t="inlineStr">
         <is>
           <t>不明。現行計画（R5.3策定、R4年度作業と推定）の策定支援業務の発注方式・受託者・金額は検索で確認できず。前々計画はH27.3「五霞町地域公共交通網形成計画」（H26年度）、R4.6「地域内フィーダー系統確保維持改善計画」。試行：「策定支援業務 委託」「入札結果 指名競争入札」「当初予算 委託料」「議会会議録 委託 コンサル」「網形成計画 株式会社」「生活安全課 業務委託 契約」等13件検索。町サイトはWebFetch/curlとも遮断され計画書巻末の確認不可。</t>
         </is>
       </c>
-      <c r="J25" s="22" t="inlineStr">
+      <c r="J30" s="22" t="inlineStr">
         <is>
           <t>コミュニティ交通「ごかりん号」：H25に五霞町コミュニティ交通運営協議会設立、H25.10試行運行、H28.10本格運行。日中はオンデマンド運行化。幸手駅（埼玉県）への代替バスを運行＝町内に鉄道駅なく近隣駅アクセスが課題（推定）。隣接の境町は自動運転バスを定常運行（2020.11〜）しており比較材料。環境基本計画はH25.3改定版を脱炭素対応で再改定（R5〜R14）。ゼロカーボンシティ宣言の有無は未確認。</t>
         </is>
       </c>
-      <c r="K25" s="22" t="inlineStr">
+      <c r="K30" s="22" t="inlineStr">
         <is>
           <t>・計画期間（R9終了見込み）と次期改定の進め方・予算化時期を生活安全課に確認。小規模町のため、指名競争入札か随意契約か等、前回の発注形態のヒアリングも兼ねる
 ・ごかりん号の定時＋オンデマンド併用・幸手駅線代替バスの評価（利用実績・収支）を次期計画のKPI再設計に繋ぐ提案
 ・隣接境町の自動運転バスや広域（埼玉県側幸手市等）との連携を次期計画の論点として提示（推定ベース）</t>
         </is>
       </c>
-      <c r="L25" s="26" t="inlineStr">
+      <c r="L30" s="26" t="inlineStr">
         <is>
           <t>https://www.town.goka.lg.jp/data/doc/1690350530_doc_20_0.pdf
 https://www.town.goka.lg.jp/data/doc/1737593680_doc_20_0.pdf
@@ -2944,69 +3329,317 @@
 https://trafficnews.jp/post/111210</t>
         </is>
       </c>
-      <c r="M25" s="22" t="inlineStr">
+      <c r="M30" s="22" t="inlineStr">
         <is>
           <t>WebSearch13回、WebFetch1回（EGRESS_BLOCKED）。茨城県猿島郡五霞町。</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="22" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="22" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="22" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>つくばみらい市</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr"/>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>つくばみらい市地域公共交通計画（R5〜R9）</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>つくばみらい市地域公共交通計画（令和5年3月策定、計画期間2023〜2027年度＝R5〜R9の5年間、確認済）。前計画のつくばみらい市地域公共交通網形成計画（H30.3策定）を継承し、地域特性やニーズにきめ細かく対応し「誰もが移動できる交通体系」の持続を目指す。上位計画は市総合計画・都市計画マスタープラン・立地適正化計画と整合。コミュニティバス（H19.10導入）とデマンド乗合タクシー（H26.4導入）が軸で、R6.4.1にコミュニティバスのルート・時刻改正（「きぬ医師会病院・みらい平駅ルート」「伊奈庁舎・みらい平駅ルート」新設）。基本方針・数値目標の詳細は検索で取得できず。参考：つくばみらい市環境基本計画（H19.3策定、H28年度に見直し・H29.3改訂版、R8年度に目標年度到達）。</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>交通：都市建設部 都市計画課 公共交通係（地域公共交通、TX沿線のまちづくり、いばらきの公共交通を所管）。〒300-2492 つくばみらい市加藤237 谷和原庁舎1階、電話0297-58-2111（代表）、FAX 0297-52-6024（市「都市計画課（業務内容）」ページ）。法定協議会は「つくばみらい市地域公共交通会議」（事務局同課と推定）。環境基本計画：生活環境課（電話は代表0297-58-2111経由、直通は未確認）。</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>【交通】計画書に「計画期間の満了時に本計画の更新を予定」。現行がR9末で満了するため、次期計画はR8〜R9年度に策定作業（R9当初予算で策定業務委託→R10開始）が標準的と推定。R8年度当初予算ページ・予算資料の検索では交通計画策定の委託料は確認できず（R8着手は無しと推定、R9予算計上の可能性）。地域公共交通会議はR7年度に3回開催（第3回 R8.1.28 谷和原庁舎）、R8年度開催情報は検索で未確認。
+【環境（有力リード）】R8年度予算資料に「環境基本計画が策定から10年を経過し、目標年度を迎えることから、計画の見直しを行う」として環境基本計画策定業務委託料7,381千円、環境保全審議会委員報酬（6,000円×10人×4日）を計上（確認済、予算資料PDF）。R8年度第2回環境保全審議会の開催予定情報も検索要約に出現。R8年度中に次期（第2次相当）環境基本計画の策定支援業務を発注済または発注予定と推定（発注方式・受託者・時期は未確認、2026-10-02時点）。</t>
+        </is>
+      </c>
+      <c r="I31" s="22" t="inlineStr">
+        <is>
+          <t>不明。R4年度の地域公共交通計画策定支援、H29年度の網形成計画策定支援とも、受託者・金額・方式を検索で確認できず。試行：「つくばみらい市 地域公共交通計画 策定支援業務 委託 プロポーザル」「…網形成計画 策定業務 委託 落札」「…令和4年度 業務委託 受託者」「令和4年度 指名競争入札結果 地域公共交通計画策定 落札者 金額」（site:city.tsukubamirai.lg.jp）「復建調査設計 つくばみらい市 公共交通」。市はR4年度指名競争入札結果を第1〜11回分PDFで公開（page003982.html）しており、該当業務が指名競争なら同PDFに掲載の可能性（市サイトはプロキシで接続拒否、PDF未確認）。計画書巻末の作成協力者欄も要確認。</t>
+        </is>
+      </c>
+      <c r="J31" s="22" t="inlineStr">
+        <is>
+          <t>・コミュニティバス：R6.4.1ルート・時刻改正（2ルート新設）。デマンド乗合タクシー運行中。
+・つくばエクスプレス（みらい平駅・みどりの駅）沿線開発が進む人口増加都市で、TX沿線まちづくりも都市計画課公共交通係が所管。
+・茨城県地域公共交通計画（R5〜R9）が県全域の地域間幹線を対象。
+・地球温暖化対策実行計画（区域施策編）：R8.3策定・R8〜R12（既存情報）。
+・環境基本計画：H29.3改訂版、R8年度に見直し予算計上（7,381千円）。
+・総合計画：第2次つくばみらい市総合計画（後期基本計画）運用中、次期改定時期は未確認。</t>
+        </is>
+      </c>
+      <c r="K31" s="22" t="inlineStr">
+        <is>
+          <t>・環境基本計画の見直し予算（R8、策定業務委託料7,381千円、審議会4回想定）が計上済み→生活環境課に発注状況（プロポ/指名の時期、R8単年かR9までの2か年か）を至急確認。既に契約済なら、区域施策編（R8.3策定）との整合・進捗管理などの周辺業務を狙う
+・地域公共交通計画はR9末満了で「満了時に更新予定」と明記→R9当初予算での策定業務発注を見込み、R8秋〜冬の予算要求時期に都市計画課公共交通係へ評価データ整理・利用実態調査の先行提案（R6.4のバス改正効果検証）を行う
+・TX沿線の人口増加とコミュニティバス・デマンドの再編が続く都市→立地適正化計画・都市計画マスタープランと連動した交通計画の更新支援を、他のTX沿線・郊外市の事例を添えて訴求</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="inlineStr">
+        <is>
+          <t>https://www.city.tsukubamirai.lg.jp/jyumin/shisetu-koutsu/koukyoukoutsu/page004893.html
+https://www.city.tsukubamirai.lg.jp/data/doc/1683698412_doc_39_0.pdf
+https://www.city.tsukubamirai.lg.jp/gyousei/public-comment/r04/page004683.html
+https://www.city.tsukubamirai.lg.jp/gyousei/gikai/r04/page004754.html
+https://www.city.tsukubamirai.lg.jp/gyousei/gikai/r07/page007275.html
+https://www.city.tsukubamirai.lg.jp/jyumin/shisetu-koutsu/koukyoukoutsu/page005822.html
+https://www.city.tsukubamirai.lg.jp/data/doc/1610452423_doc_3_0.pdf
+https://www.city.tsukubamirai.lg.jp/gyousei/soshiki/page002665.html
+https://www.city.tsukubamirai.lg.jp/jyumin/gomi-kankyou-doubutsu/kankyouhozen/page000080.html
+https://www.city.tsukubamirai.lg.jp/data/doc/1706234238_doc_25_0.pdf
+https://www.city.tsukubamirai.lg.jp/data/doc/1772426110_doc_14_0.pdf
+https://www.city.tsukubamirai.lg.jp/gyousei/zaisei/yosan/r08/page007397.html
+https://www.city.tsukubamirai.lg.jp/business/bid/bid-kekka/bid-result/page003982.html
+https://www.city.tsukubamirai.lg.jp/data/doc/1772670871_doc_25_0.pdf</t>
+        </is>
+      </c>
+      <c r="M31" s="22" t="inlineStr">
+        <is>
+          <t>交通計画期間は確認済（根拠：計画書「計画期間は2023年度から2027年度までの5年間」）。環境基本計画は改訂版（H29.3）の期間が明示されていないが、R8予算資料に「策定から10年を経過し、目標年度を迎えることから、計画の見直しを行う」「環境基本計画策定業務委託料 7,381千円」とあり見直し着手は確認済（ただし検索要約の一つは単位を「万円」と誤表示、別検索で「7,381千円」と確認）。WebSearch使用15回。市サイトはcurl/WebFetchとも接続拒否で入札結果PDF・計画書巻末は未確認。つくば市（別自治体）の網形成計画・協議会情報と混同しないよう注意。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>大子町</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr"/>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>大子町環境基本計画（H30.3策定、期間H30〜R9は推定）</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>大子町環境基本計画（平成30年3月策定）。H28.9制定の大子町環境基本条例に基づく初の環境基本計画。施策体系は(1)自然環境の保全・創造（森林管理・里山・生物多様性）、(2)生活環境の保全（公害防止・廃棄物）、(3)地球環境の保全（温暖化対策・省エネ）、(4)環境意識の向上（環境教育）の4分野で、町・町民・事業者の役割を規定（検索要約）。計画期間は本文で確認できず、10年計画と推定（H30〜R9）。交通は「大子町地域公共交通計画」（マスタープラン）と「大子町地域公共交通再編計画」（アクションプラン）を作成（町HP掲載2023/3/27、期間未確認）。</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>環境基本計画：生活環境課 生活環境担当（庁舎1階、〒319-3521 大子町大字北田気662番地、電話0295-76-8802、FAX 0295-72-3550）。交通（AI乗合タクシー・地域公共交通会議）：まちづくり課 まちづくり担当（本庁2階、電話0295-72-1131、FAX 0295-72-1167）。総合計画もまちづくり課所管（第7次総合計画の発行者）。</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>【環境】第2次環境基本計画の策定委託・審議会・パブコメ等は検索で見当たらず（2026-10-02時点、未確認）。現行がH30〜R9の10年計画であれば、R8〜R9年度に見直し作業→R9当初予算で策定支援業務発注が想定される（推定）。地域脱炭素ビジョン（区域施策編を兼ねる、2024年4月公表）が既にあるため、次期計画はビジョンとの統合・整合が論点になる可能性（推定）。
+【交通】地域公共交通計画・再編計画はR5.3頃公表（町HP日付2023/3/27）。期間不明だが5年ならR5〜R9で満了が環境と同時期となる可能性（推定、要確認）。</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="inlineStr">
+        <is>
+          <t>不明。H29年度の環境基本計画策定支援業務、R4年度頃の地域公共交通計画策定支援業務とも受託者・金額・方式を検索で確認できず。試行：「大子町 環境基本計画策定業務 委託 平成29年度 入札 結果」「大子町 環境基本計画 策定 委託 環境審議会 第2次」（site:town.daigo.ibaraki.jp）「大子町地域脱炭素ビジョン 策定 委託」「大子町地域公共交通再編実施計画 国土交通大臣 認定」。町サイトは接続拒否でPDF（素案・計画書巻末）未確認。NJSSに大子町役場の調達ページあり（未確認）。</t>
+        </is>
+      </c>
+      <c r="J32" s="22" t="inlineStr">
+        <is>
+          <t>・ゼロカーボンシティ宣言（R4.8）、大子町地域脱炭素ビジョン（地球温暖化対策実行計画（区域施策編）を兼ねる、2024年4月公表）、ゼロカーボン推進事業補助金、太陽光発電設備等設置工事の公募型プロポーザル実施（審査結果ページあり）。
+・AI乗合タクシー「たくまる」：R3.10.1本格運行開始、愛称決定・運行車両増車のお知らせあり。運賃日中300円・夜間500円。
+・JR水郡線：茨城県水郡線利用促進会議（県・沿線市町、大子町含む）が「水郡線 里山物語2026」等の利用促進ツアーを実施。
+・第7次大子町総合計画「だいご未来ビジョン2027」（R6.2発行、目標年2027＝R9と推定）、第3期大子町総合戦略（R7.3）、立地適正化計画策定済。過疎地域持続的発展計画（R3〜R7）。</t>
+        </is>
+      </c>
+      <c r="K32" s="22" t="inlineStr">
+        <is>
+          <t>・環境基本計画（H30.3策定）・総合計画「だいご未来ビジョン2027」がともにR9前後で目標年を迎える見込み→生活環境課に第2次環境基本計画の策定時期・予算化（R9当初）を確認し、地域脱炭素ビジョン（区域施策編）との統合型計画を提案
+・たくまる増車・本格運行の実績と水郡線の利用促進を踏まえ、まちづくり課に地域公共交通計画の期間・評価状況をヒアリング→期間満了が近ければ、AIデマンドのデータ分析と水郡線・路線バスとの結節を軸にした次期計画策定支援を提案
+・小規模町で環境・交通・総合計画の改定時期が重なる可能性→業務の一括・連携発注（調査の共通化、住民アンケート共用）によるコスト削減を訴求</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="inlineStr">
+        <is>
+          <t>https://www.town.daigo.ibaraki.jp/page/page003178.html
+https://www.town.daigo.ibaraki.jp/data/doc/1525765232_doc_99_1.pdf
+https://www.town.daigo.ibaraki.jp/page/page007352.html
+https://www.town.daigo.ibaraki.jp/page/page006483.html
+https://www.town.daigo.ibaraki.jp/page/page007344.html
+https://www.town.daigo.ibaraki.jp/page/page008115.html
+https://www.town.daigo.ibaraki.jp/page/page002515.html
+https://www.town.daigo.ibaraki.jp/page/page000713.html
+https://www.town.daigo.ibaraki.jp/page/page001206.html
+https://www.town.daigo.ibaraki.jp/page/page005024.html
+https://www.town.daigo.ibaraki.jp/page/page007622.html
+https://www.town.daigo.ibaraki.jp/page/page005766.html
+https://www.town.daigo.ibaraki.jp/page/page007319.html
+https://www.town.daigo.ibaraki.jp/data/doc/1709885186_doc_14_0.pdf
+https://www.town.daigo.ibaraki.jp/page/page002107.html
+https://www.pref.ibaraki.jp/kikaku/kotsuseisaku/tetsudo/suigunsentour-information2026.html
+https://www.env.go.jp/recycle/waste/3r_network/5_region/project_list/08_ibaraki/10_daigo_h29.pdf</t>
+        </is>
+      </c>
+      <c r="M32" s="22" t="inlineStr">
+        <is>
+          <t>環境基本計画の期間は未確認（推定H30〜R9）。根拠は「大子町環境基本計画 素案 平成30年3月 大子町」「『大子町環境基本条例』の規定に基づき…策定しました」のみで、目次に「計画の期間」項目はあるが本文の年度は検索で取得できず。なお「平成30年度から令和9年度までの10年間」でヒットしたのは常陸大宮市環境基本計画であり大子町ではない（混同注意）。交通計画の期間も不明。WebSearch使用15回（両市町合計30回）。町サイトはcurl/WebFetch接続拒否。生活環境課の電話0295-76-8802は町HP検索要約で確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>守谷市</t>
+        </is>
+      </c>
+      <c r="D33" s="27" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>守谷市地域公共交通計画（R5〜R9／2023〜2027年度、5年間）</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>守谷市地域公共交通計画（R5.3策定、R7.5変更、計画期間R5〜R9の5年間、確認済）。前身は守谷市地域公共交通網形成計画（H30.7）。コミュニティバス「モコバス」（市役所・板戸井ルート、みずき野・松並青葉ルートの2ルート1日17便）とデマンド乗合交通で交通空白地域をカバー、つくばエクスプレス・関東鉄道常総線の守谷駅を結節点とする体系。参考：第3次守谷市環境基本計画（R8〜R17）を生活環境課が策定中（前回調査）。</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr">
+        <is>
+          <t>都市整備部 都市計画課 交通政策・景観グループ（守谷市地域公共交通活性化協議会事務局）。電話 0297-45-1111（代表）内線244／都市計画課直通 0297-45-1963。環境基本計画は生活環境課。</t>
+        </is>
+      </c>
+      <c r="H33" s="28" t="inlineStr">
+        <is>
+          <t>【次期（第2次）計画は着手済・受託者決定済】『守谷市地域公共交通再構築調査・検討等業務委託』公募型プロポーザル（確認済）：趣旨＝R4年度策定の守谷市地域公共交通計画（第1次計画）を国交省「地域公共交通計画のアップデートガイダンス」に基づきアップデートし、地域の多様な輸送資源を活用した新たな移動手段の導入等を含め地域公共交通の再構築を調査・検討。公告 R7(2025).10.17、企画提案書等提出 R7.10.29〜11.11 17時、審査結果通知・公表 R7.12.4、契約締結 R7.12上旬予定。提案上限額 14,943,500円（税込）、履行期間 契約締結日の翌日〜R8.11.30。企画提案者6者→プレゼン4者、最優秀＝株式会社長大（124.5点/150点、次点116.8点・114.8点・111.9点）。発注主体は守谷市地域公共交通活性化協議会と推定（検索要約）。R8施政方針で『第1次計画のアップデートとなる第2次守谷市地域公共交通計画を策定』と明記。→R8.11末で調査完了、協議会審議・パブコメを経てR8年度末（R9.3）頃に第2次計画策定と推定（第1次計画R9までを前倒し更新）。R8年度の協議会開催日・パブコメ日程は検索で確認できず。</t>
+        </is>
+      </c>
+      <c r="I33" s="25" t="inlineStr">
+        <is>
+          <t>次期：上記プロポ（R7年度、公募型プロポーザル、受託＝株式会社長大、上限額14,943,500円、契約額は未確認）。現行計画（R4年度策定）：協議会はR4.6.17、11.28、12.23、R5.1.30、3.27の計5回、パブコメR5.2.10〜3.12（計画ページで確認）。受託者選定は公募型プロポーザルで契約者は協議会会長との検索要約あり（単一要約のため推定、R7プロポとの混同の可能性）。受託者・金額は不明。網形成計画（H29〜30年度）：受託者・金額不明。試行クエリ：「守谷市地域公共交通網形成計画 策定 業務委託 受託 株式会社 平成29年度」「守谷市 地域公共交通計画 策定業務 令和4年度 委託 受託者 協議会 議事録」。第3次守谷市環境基本計画（R8〜R17）の策定支援受託者も不明（「第3次守谷市環境基本計画 策定支援業務委託 プロポーザル 受託」「守谷市 環境基本計画 策定 業務委託 入札結果 生活環境課 第3次」「第3次守谷市環境基本計画 パブリックコメント 環境審議会 策定 2026」で未ヒット。R5/R6年度入札結果PDFに含まれる可能性）。</t>
+        </is>
+      </c>
+      <c r="J33" s="22" t="inlineStr">
+        <is>
+          <t>・ゼロカーボンシティ表明（2020年7月28日）、ゼロカーボンシティもりや事業者ネットワーク設立、市内一斉ノーマイカーウィーク、公用車EV導入。・モコバス「高野・同地・赤法花循環ルート」実証運行（R7.11.25〜、R8年度も継続）＝再編の材料。新規コミュニティバス実証運行の運賃について意見募集実施。・デマンド乗合交通運行中。・第三次守谷市総合計画後期基本計画及び第3期総合戦略の策定支援業務も公募プロポで実施（総合計画改定と交通・環境計画が同時期）。・新モビリティサービスと一体となった防災総合公園整備の官民連携手法調査（R7.3、三井住友トラスト基礎研究所）あり。</t>
+        </is>
+      </c>
+      <c r="K33" s="22" t="inlineStr">
+        <is>
+          <t>・第2次交通計画の調査・検討は長大がR7.12〜R8.11.30で受託済のため本体参入は困難。計画策定後のR9年度以降の実証運行評価・モニタリング、利用促進、新たな移動手段（多様な輸送資源活用＝ライドシェア・スクールバス等の混乗）の導入支援が別発注されるかを交通政策・景観グループにヒアリング
+・長大の受託範囲が『調査・検討』（R8.11末まで）である点に着目し、計画本文取りまとめ・パブコメ・協議会運営がR8年度後半に別途発注されるか確認（要確認）
+・環境分野：第3次環境基本計画（R8〜R17）策定後の地球温暖化対策実行計画・ゼロカーボン推進（事業者ネットワーク運営支援等）の案件化を生活環境課に打診。競合情報として第3次環境基本計画の受託者を入札結果で確認しておく</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="inlineStr">
+        <is>
+          <t>https://www.city.moriya.ibaraki.jp/sangyo_business/nyusatsu/1004161/1011200.html
+https://www.city.moriya.ibaraki.jp/_res/projects/default_project/_page_/001/011/200/jissiyouryou.pdf
+https://www.city.moriya.ibaraki.jp/sangyo_business/nyusatsu/1004161/index.html
+https://www.city.moriya.ibaraki.jp/kurashi_tetsuzuki/koutsu/1002163/1002204.html
+https://www.city.moriya.ibaraki.jp/kurashi_tetsuzuki/koutsu/1002163/1002205.html
+https://www.city.moriya.ibaraki.jp/shisei/profile/1004324/1004328/1004359/1004360.html
+https://www.city.moriya.ibaraki.jp/shisetsu/g_sisetu/gyousei/tosisei/0410.html
+https://www.city.moriya.ibaraki.jp/_res/projects/default_project/_page_/001/002/191/r4_4_03_gian1.pdf
+https://www.city.moriya.ibaraki.jp/shisei/mayor/1005682/1011702.html
+https://www.city.moriya.ibaraki.jp/sangyo_business/nyusatsu/1004161/1010425.html
+https://www.city.moriya.ibaraki.jp/sangyo_business/nyusatsu/1004168/index.html
+https://www.city.moriya.ibaraki.jp/shisei/profile/1004324/1004328/1004339/1004340.html
+https://www.city.moriya.ibaraki.jp/kurashi_tetsuzuki/kankyo_gomi/1009763/1010741.html
+https://www.city.moriya.ibaraki.jp/kurashi_tetsuzuki/kankyo_gomi/1009763/1011607.html
+https://www.city.moriya.ibaraki.jp/kurashi_tetsuzuki/koutsu/1002163/1002164/1002166/1011157.html
+https://www.city.moriya.ibaraki.jp/kurashi_tetsuzuki/koutsu/1002163/1002164/1002166/1002175.html
+https://www.mlit.go.jp/sogoseisaku/kanminrenkei/content/001764340.pdf</t>
+        </is>
+      </c>
+      <c r="M33" s="22" t="inlineStr">
+        <is>
+          <t>期間確認：交通計画 R5〜R9 確認済（『計画期間は令和5年度から令和9年度までの5年間』）。次期関連プロポ（再構築調査・検討等業務、長大、上限14,943,500円、履行〜R8.11.30）は市サイト・実施要領PDFの検索結果本文で確認済。公告日R7.10.17はextended検索の要約のみ＝推定寄り。契約額・R8協議会日程・パブコメは未確認。WebSearch使用13回（うちextended 2回）。第3次環境基本計画の受託者は不明。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>栃木県</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>栃木市</t>
         </is>
       </c>
-      <c r="D26" s="27" t="inlineStr">
+      <c r="D34" s="27" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>栃木市地域公共交通計画（H30.10策定の網形成計画をR6.6改訂、〜R9年度末）</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>栃木市地域公共交通計画：H30.10「栃木市地域公共交通網形成計画」（H30〜R9の10年計画）として策定、法改正を受けR6.6に地域公共交通計画へ改訂（期間はR6.7〜R9年度末）。JR両毛線・東武日光線/宇都宮線を軸に路線バス、コミュニティバス「ふれあいバス」、デマンド交通「蔵タク」、タクシー、福祉有償運送で公共交通網を構成。ふれあいバス・蔵タクの詳細は別途「栃木市地域公共交通運行実施計画」で定める。デマンド交通の目標は収支率20.0%・利用者255人/日（R7年度）（検索要約で確認）。※第2次環境基本計画（R5〜R14）はR9終了ではないため対象外。</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G34" s="22" t="inlineStr">
         <is>
           <t>交通防犯課（ふれあいバス問合せ先、TEL 0282-21-2153）（検索要約で確認。資料が古い可能性あり、現行の組織名は要確認）</t>
         </is>
       </c>
-      <c r="H26" s="28" t="inlineStr">
+      <c r="H34" s="28" t="inlineStr">
         <is>
           <t>着手済（事実）：第2次栃木市地域公共交通計画（計画期間R10〜R14の5年間予定）をR7年度から策定中。令和7年5月に入札で特定非営利活動法人まちづくり支援センターに策定業務を委託、同者から公共交通再編のコンサル・指導を受けつつ策定。R7年度第4回栃木市地域公共交通会議で進捗報告（63013.pdf）。現計画終了（R9末）まで約2年あるため、R8〜R9は公共交通再編・実証・計画素案〜パブコメの段階と推定（具体スケジュールは未確認）。→次期交通計画の新規受注余地は小さい。</t>
         </is>
       </c>
-      <c r="I26" s="25" t="inlineStr">
+      <c r="I34" s="25" t="inlineStr">
         <is>
           <t>次期（第2次）計画：R7年5月、入札（方式は一般/指名か未確認）により特定非営利活動法人まちづくり支援センター（公共交通関係コンサルタント）が受託（事実、63013.pdf等）。契約金額は不明（「契約金額」「落札 円」「当初予算 事業費」「契約締結状況」で検索したが出ず）。単年度か複数年契約かも未確認。前計画（H30.10網形成計画、H29〜H30年度作業と推定）：受託者・方式・金額は不明。1件の検索要約で『H30策定もまちづくり支援センターが協力』とする記述があったが、R7受託記事との混同の可能性が高く（要確認）。試行：プロポーザル/指名競争入札/入札結果/計画書協力者等で計5件検索。</t>
         </is>
       </c>
-      <c r="J26" s="22" t="inlineStr">
+      <c r="J34" s="22" t="inlineStr">
         <is>
           <t>市塙・赤羽工業団地線（路線バス）がR8(2026)年4月1日廃止予定（県資料）。デマンド交通「蔵タク」（平日8〜16時、事前登録・電話予約）とふれあいバス5路線（運賃100〜300円）。公共交通の再編をまちづくり支援センターの指導で検討中＝路線再編・廃止代替が当面の論点。第2次環境基本計画（R5〜R14）。ゼロカーボンシティ宣言の有無は今回未確認。</t>
         </is>
       </c>
-      <c r="K26" s="22" t="inlineStr">
+      <c r="K34" s="22" t="inlineStr">
         <is>
           <t>・交通計画は第2次の策定が既にまちづくり支援センター受託で進行中のため、直接の策定支援提案は困難。代わりに再編に伴う実証運行・利用実態調査・データ分析・評価（モニタリング）業務、または交通計画と環境基本計画（脱炭素・移動のCO2削減）の連携をテーマに情報提供
 ・路線バス廃止（市塙・赤羽工業団地線、R8.4）後の代替交通・工業団地通勤輸送の検討支援を切り口に
 ・第2次環境基本計画の中間見直し時期（R9〜R10頃と推定）や地球温暖化対策実行計画の改定予定を環境部局にヒアリングし、次の案件を探る</t>
         </is>
       </c>
-      <c r="L26" s="26" t="inlineStr">
+      <c r="L34" s="26" t="inlineStr">
         <is>
           <t>https://www.city.tochigi.lg.jp/uploaded/attachment/63013.pdf
 https://www.city.tochigi.lg.jp/uploaded/attachment/56361.pdf
@@ -3020,55 +3653,55 @@
 https://www.city.tochigi.lg.jp/uploaded/attachment/60576.pdf</t>
         </is>
       </c>
-      <c r="M26" s="22" t="inlineStr">
+      <c r="M34" s="22" t="inlineStr">
         <is>
           <t>WebSearch13回。契約金額は市の入札結果公表ページ（電子入札システム）で直接確認が必要。</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="22" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="22" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="22" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>栃木県</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>鹿沼市</t>
         </is>
       </c>
-      <c r="D27" s="24" t="inlineStr"/>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="D35" s="24" t="inlineStr"/>
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>鹿沼市地域公共交通計画（R4〜R9）／第5次鹿沼市環境基本計画（R4〜R8）</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>【交通】鹿沼市地域公共交通計画：R4年度〜R9年度の6年間（R6.10・R8.6に一部改定）。地域公共交通活性化再生法（R2.11改正）に基づく法定計画として位置づけ。R4.1.24の令和3年度第3回地域公共交通活性化協議会で計画案承認。市営バス「リーバス」・予約バス（デマンド）等の路線網維持・再編が柱（主要施策詳細は計画書本文要確認）。
 【環境】第5次鹿沼市環境基本計画：R4年度〜R8年度の5か年（R4.3策定、目標年次R8）。基本目標は①ゼロカーボンのまちをつくる、②持続可能なまちをつくる、③自然と寄り添うまちをつくる、④自ら行動するまちをつくる。気候変動適応策を含む。</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>【交通】生活課 交通政策係 ☎0289-63-2163（市の交通ガイドPDF記載・検索要約より）。【環境】環境課（係・電話は検索で確認できず、要確認）。</t>
         </is>
       </c>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>【環境】現計画は今年度（R8）で終了だが、第6次計画の策定支援業務の公告・環境審議会への諮問・市民アンケート・パブコメは検索で見当たらず。前回（第5次）はR2年度第3回環境審議会（R3.2.5）で策定を協議開始→R3年度第3回（R3.12.2）→第4回（R4.3.8）で答申という約1年強の工程だったため、今回同様なら既にR7年度中に着手しているはずであり、①庁内直営で策定中、②計画期間の延長、③R9年度策定へ後ろ倒し、のいずれか（推定・環境課に要確認）。
 【交通】R9年度末で終了。次期計画策定支援業務の公告・協議会での次期計画審議は検索で見当たらず。前回はR3年度中に協議会で審議・R4.1承認のため、次期（R10〜）も同様ならR9年度に策定業務、R8年度秋（今期）に予算要求となる見込み（推定）。R9〜R11の予約バス運行事業者選定プロポは実施済（既存note）。</t>
         </is>
       </c>
-      <c r="I27" s="22" t="inlineStr">
+      <c r="I35" s="22" t="inlineStr">
         <is>
           <t>不明。交通計画（R3年度策定）・第5次環境基本計画（R2〜R3年度策定）とも、策定支援業務の発注方式・受託者・契約金額は検索で確認できず。試行：「鹿沼市 地域公共交通計画 策定 業務 プロポーザル 結果」「〜策定支援 委託 株式会社」「鹿沼市 入札結果 令和3年度 地域公共交通計画策定業務」「〜落札者 契約金額」「鹿沼市 環境基本計画 策定支援業務 委託 プロポーザル」「〜契約 落札」「環境審議会 コンサルタント」等。計画書PDFの直接取得は403でブロック。計画書巻末・環境審議会会議録（R3.12.2、R4.3.8）に事務局補助としてコンサル名が出ている可能性あり（要確認）。</t>
         </is>
       </c>
-      <c r="J27" s="22" t="inlineStr">
+      <c r="J35" s="22" t="inlineStr">
         <is>
           <t>・市営バス「リーバス」と予約バス（デマンド型）を運行。予約バスはR9〜R11の運行事業者選定プロポを実施済（既存note）。
 ・地域間幹線系統確保維持費国庫補助金の事業評価をR7.1.24に協議会で実施（国庫補助路線あり）。
@@ -3076,14 +3709,14 @@
 ・総合計画は第9次「鹿沼みらいビジョン（基本構想）」＋5か年の「鹿沼2030プラン（基本計画）」（期間は要確認）。</t>
         </is>
       </c>
-      <c r="K27" s="22" t="inlineStr">
+      <c r="K35" s="22" t="inlineStr">
         <is>
           <t>・環境基本計画がR8年度で満了するのに次期策定の公表情報が無い点を切り口に、延長か後継策定かの方針・R9予算要求の有無を環境課にヒアリング。地球温暖化対策実行計画（区域施策編）との統合策定やコスモ石油との連携協定を踏まえたゼロカーボン施策の具体化を提案。
 ・交通計画はR9年度末満了。R8秋の予算要求に向け、リーバス・予約バス（R9〜R11新運行契約）の利用実績評価を次期計画（R10〜）に反映するスケジュール感と、計画のR6・R8一部改定の経緯を生活課交通政策係に確認。
 ・交通・環境の両計画を同時期に見直すタイミングであることから、脱炭素型交通（公共交通利用転換・EVバス等）を共通テーマとした連携した調査提案が可能。</t>
         </is>
       </c>
-      <c r="L27" s="26" t="inlineStr">
+      <c r="L35" s="26" t="inlineStr">
         <is>
           <t>https://www.city.kanuma.tochigi.jp/manage/contents/upload/623824c0af645.pdf
 https://www.city.kanuma.tochigi.jp/manage/contents/upload/6a3b627349ac7.pdf
@@ -3098,54 +3731,54 @@
 https://www.city.kanuma.tochigi.jp/manage/contents/upload/69e749094fd8e.pdf</t>
         </is>
       </c>
-      <c r="M27" s="22" t="inlineStr">
+      <c r="M35" s="22" t="inlineStr">
         <is>
           <t>WebSearch 12回。過去契約は検索で特定できず（市の入札結果ページ・会議録の個別確認が必要）。電話番号は交通のみ検索要約で確認。</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="22" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="22" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>栃木県</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
         <is>
           <t>日光市</t>
         </is>
       </c>
-      <c r="D28" s="24" t="inlineStr"/>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="D36" s="24" t="inlineStr"/>
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>日光市地域公共交通計画（R5.4〜R10.3＝R9年度末終了）</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>日光市地域公共交通計画：R5.4〜R10.3の5か年（期間は検索要約1回のみ・要確認）。地域公共交通活性化再生法に基づく法定計画・マスタープランで、第2次日光市総合計画に即し、都市計画マスタープラン・立地適正化計画と整合。市民・交通事業者・行政の連携による持続可能な移動サービスの確保が目的。対象は民間路線バス（東武バス日光・日光交通）、日光市営バス、市営デマンド型交通のほか関東自動車・鹿沼市・那須塩原市・塩谷町のバス。原案パブコメはR5.1.16〜2.15（2名14件）。前身はH22「生活交通再構築計画」→H30.3「地域公共交通網形成計画」。
 （参考）第2次日光市環境基本計画（R1.12策定、R2〜R11推定）はR9終了対象外。</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G36" s="22" t="inlineStr">
         <is>
           <t>建設部 都市計画課 交通政策係 ☎0288-21-5151（市営バス問合せ先として市資料に記載・検索要約より。代表番号の可能性あり、要確認）。</t>
         </is>
       </c>
-      <c r="H28" s="22" t="inlineStr">
+      <c r="H36" s="22" t="inlineStr">
         <is>
           <t>次期計画（R10〜）の策定支援業務公告・協議会での次期計画審議は検索で見当たらず（既存noteどおりR8施政方針は現計画の継続のみ）。前回は原案パブコメがR5.1（R4年度）で、R4年度に策定作業→R5.4施行。同様の工程ならR9年度に策定業務を発注、R8年度秋〜冬の当初予算要求で業務委託料計上（推定・要確認）。</t>
         </is>
       </c>
-      <c r="I28" s="22" t="inlineStr">
+      <c r="I36" s="22" t="inlineStr">
         <is>
           <t>不明。現計画（R4年度策定と推定）・前計画（H30.3網形成計画）とも、策定支援業務の発注方式・受託者・契約金額は検索で確認できず。試行：「日光市 地域公共交通計画 策定 業務 プロポーザル 結果」「〜策定支援業務 委託 受託 令和4年度」「〜策定業務 仕様書」「日光市 入札結果 公共交通 計画 業務委託」「日光市議会 地域公共交通計画 策定 委託料」「地域公共交通網形成計画 委託 コンサルタント」「都市計画課 プロポーザル 審査結果」。計画書PDFはWebFetch/curlとも403ブロックで巻末確認不可。都市計画課ではR6年度に「日光市営デマンド交通システム導入業務委託」を公募型プロポで発注しており（審査結果は未確認）、計画策定業務もプロポ方式の可能性あり（推定）。</t>
         </is>
       </c>
-      <c r="J28" s="22" t="inlineStr">
+      <c r="J36" s="22" t="inlineStr">
         <is>
           <t>・R6年度に「日光市営デマンド交通システム導入業務委託」を公募型プロポーザルで実施（担当：建設部都市計画課交通政策係）→デマンド交通の再編・システム化が進行中。
 ・市営バス・市営デマンド交通に加え、東武バス日光・日光交通・関東自動車等の民間路線が混在、近隣市町（鹿沼市・那須塩原市・塩谷町）の路線も乗り入れ。
@@ -3154,14 +3787,14 @@
 ・都市計画マスタープラン（H21.3策定、20年計画）。</t>
         </is>
       </c>
-      <c r="K28" s="22" t="inlineStr">
+      <c r="K36" s="22" t="inlineStr">
         <is>
           <t>・R9年度末で計画満了→R8秋のR9当初予算要求タイミング。網形成計画（H30）→地域公共交通計画（R5）と計画を継承してきた経緯を踏まえ、次期計画の策定方針（直営かコンサル委託か、発注方式）と協議会スケジュールを交通政策係にヒアリング。
 ・R6年度に導入したデマンド交通システムの運行データ・利用実績の評価や、鬼怒川温泉駅前再整備との連携（交通結節点）、観光客と生活交通の両立を次期計画の論点として提示。
 ・ゼロカーボンシティ宣言（R3.12）のEVのまちづくり施策と公共交通（EVバス・グリーンスローモビリティ等）を一体で扱う提案が可能。</t>
         </is>
       </c>
-      <c r="L28" s="26" t="inlineStr">
+      <c r="L36" s="26" t="inlineStr">
         <is>
           <t>https://www.city.nikko.lg.jp/material/files/group/33/tiikikoukyoukoutuukeikaku.pdf
 https://www.city.nikko.lg.jp/material/files/group/3/tiikikoukyoukoutuu_kekka.pdf
@@ -3175,58 +3808,58 @@
 https://www.city.nikko.lg.jp/soshiki/6/1031/5/1/1/125.html</t>
         </is>
       </c>
-      <c r="M28" s="22" t="inlineStr">
+      <c r="M36" s="22" t="inlineStr">
         <is>
           <t>WebSearch 12回、WebFetch 1回（市サイトEGRESS_BLOCKED）。過去契約は特定できず。group/33/bosyuyoukou.pdf＝R6デマンド交通システム導入業務の募集要項（検索要約による、要確認）。</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="22" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="22" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="22" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>栃木県</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C37" s="23" t="inlineStr">
         <is>
           <t>大田原市</t>
         </is>
       </c>
-      <c r="D29" s="27" t="inlineStr">
+      <c r="D37" s="27" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>大田原市地域公共交通計画（R4〜R9）※次期計画（R10〜R14）策定業務は発注済</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>大田原市地域公共交通計画：R4.3策定、R4(2022)〜R9(2027)年度の6か年（R6.12改訂版PDFあり）。前身はH29.3「地域公共交通網形成計画」で、同計画に基づき市営バス・民間路線バス（関東自動車）・デマンド交通を改善。基本方針は①「住みたいまち」になる公共交通網の形成、②地域で互いに支えあう公共交通の推進、③未来を見据えた、時代に即した、人や環境にやさしい新たな交通施策の導入。デマンド交通「らくらく与一号」（親園・野崎・佐久山・湯津上・黒羽・川西・両郷・須賀川地区）を運行。関連計画に那須地域定住自立圏共生ビジョン。</t>
         </is>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>生活環境課（地域公共交通担当）☎0287-23-8832（プロポ公告ページ関連の検索要約より。係名は未確認）。</t>
         </is>
       </c>
-      <c r="H29" s="28" t="inlineStr">
+      <c r="H37" s="28" t="inlineStr">
         <is>
           <t>【着手済】現計画がR9年度末で終了するため、R10年度から5年間の次期計画策定に向け「大田原市地域公共交通計画策定調査業務委託」の公募型プロポーザルを実施。公告ページ（docs/2026073100056、ID上2026-07-31、募集開始は2026-08-05との要約あり・要確認）。業務内容：基礎調査、分析、資料作成、計画案作成等の支援。契約期間：契約日〜令和9年3月19日（R8年度単年度。R9年度に計画案取りまとめの別契約がある可能性あり・推定）。審査：令和8年9月17日（木）実施、審査結果公表ページ docs/2026091600026 → 契約候補者『バイタルリード・サーベイリサーチセンター共同企業体』（代表：株式会社バイタルリード、島根県出雲市荻杼町274番地2）を特定。提案上限額・契約金額・参加者数は検索結果に表示されず不明（市サイトはWebFetch不可、要確認）。</t>
         </is>
       </c>
-      <c r="I29" s="25" t="inlineStr">
+      <c r="I37" s="25" t="inlineStr">
         <is>
           <t>【次期計画（R8年度発注）】公募型プロポーザル、R8年度、契約候補者＝バイタルリード・サーベイリサーチセンター共同企業体（2026-09-17審査）、金額・上限額は不明（要確認）。
 【現計画（R3年度策定）】発注方式・受託者・契約金額は不明。試行：「大田原市 地域公共交通計画 策定 業務委託 受託 令和3年度」「〜落札 入札結果」「市政年報 委託」「議会 委託料」、バイタルリード等社名との組合せ、kkj/labid/NJSS等。R3市政年報・R3補正予算書（第7号）がヒットしたが本文確認できず（同資料に委託料記載の可能性・要確認）。</t>
         </is>
       </c>
-      <c r="J29" s="22" t="inlineStr">
+      <c r="J37" s="22" t="inlineStr">
         <is>
           <t>・デマンド交通「らくらく与一号」を市内8地区で運行、市営バス・関東自動車路線バスと組み合わせた交通網。
 ・那須地域定住自立圏（那須塩原市等）で「那須地域定住自立圏地域公共交通計画」があり広域連携あり。
@@ -3235,14 +3868,14 @@
 ・環境：第三次環境基本計画をR8策定済（R8〜）。公共施設へのPPAモデル太陽光導入（R4年度プロポ）等脱炭素施策あり。</t>
         </is>
       </c>
-      <c r="K29" s="22" t="inlineStr">
+      <c r="K37" s="22" t="inlineStr">
         <is>
           <t>・次期交通計画はバイタルリード・SRC JVが受託候補に特定済のため、計画策定本体の営業機会は今期なし。むしろR9年度の計画策定2年目業務（契約期間がR9.3.19までのため、R9に追加発注の有無）や、計画策定後の実証運行・利用促進・評価（PDCA）支援、デマンド交通運行改善の調査業務を狙う。
 ・今回のプロポの提案上限額・参加者数・評価点を情報公開／聞き取りで把握し、近隣（鹿沼市・日光市）R9〜R10発注案件の価格・提案水準の参考にする。
 ・環境基本計画はR8策定済で当面機会なし。都市MP・立地適正化計画見直し（R6〜）との整合、次期総合計画（R9〜推定）策定動向を確認しつつ、地球温暖化対策実行計画の改定時期をヒアリング。</t>
         </is>
       </c>
-      <c r="L29" s="26" t="inlineStr">
+      <c r="L37" s="26" t="inlineStr">
         <is>
           <t>https://www.city.ohtawara.tochigi.jp/docs/2026073100056
 https://www.city.ohtawara.tochigi.jp/docs/2026091600026
@@ -3261,53 +3894,53 @@
 https://www.city.ohtawara.tochigi.jp/docs/2026013000019</t>
         </is>
       </c>
-      <c r="M29" s="22" t="inlineStr">
+      <c r="M37" s="22" t="inlineStr">
         <is>
           <t>WebSearch 14回、WebFetch 1回（市サイトEGRESS_BLOCKED）。審査結果（2026-09-17、バイタルリード・SRC JV）は検索要約2回で一致、契約期間R9.3.19は要約1回のみ（要確認）。上限額・契約額は不明。</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="22" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="22" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="22" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>栃木県</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C38" s="23" t="inlineStr">
         <is>
           <t>那須塩原市</t>
         </is>
       </c>
-      <c r="D30" s="24" t="inlineStr"/>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="D38" s="24" t="inlineStr"/>
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>第2次那須塩原市地域公共交通計画（R5〜R9）／那須地域定住自立圏地域公共交通計画（第2次、R5.4〜R10.3）。※環境基本計画は改定版で終期R12へ延長のためR9ターゲットは交通計画</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>第2次那須塩原市地域公共交通計画（R5.3策定、R5〜R9）：まちづくりと整合した持続可能な地域公共交通ネットワーク構築を目的とし、市全体の公共交通の基本計画として利便性向上・移動手段の確保維持の各事業を推進。市内は路線バス（関東自動車〔旧東野バス〕・JRバス関東）、市営ゆーバス、予約制デマンド（ゆータク／予約ワゴンバス）で構成（推定：構成は県資料要約ベース）。上位の那須地域定住自立圏地域公共交通計画（2市2町共同、第1次網形成計画H30〜R4→第2次R5.4〜R10.3）は広域幹線・圏域連携を担う。</t>
         </is>
       </c>
-      <c r="G30" s="22" t="inlineStr">
+      <c r="G38" s="22" t="inlineStr">
         <is>
           <t>市民生活部 生活課（公共交通担当／那須地域定住自立圏公共交通部会事務局。国交省資料に「事務局 那須塩原市生活課」と記載）。電話番号は未確認（要確認）。※組織名は「kb」ディレクトリ配下のページで公開。環境基本計画は市民生活部環境課 環境保全係。</t>
         </is>
       </c>
-      <c r="H30" s="22" t="inlineStr">
+      <c r="H38" s="22" t="inlineStr">
         <is>
           <t>市計画・定住自立圏計画ともR9年度末（R10.3）終期のため、第3次計画はR8〜R9年度の2か年で策定作業となる見込み（推定）。第3次策定支援業務の公募は2026-10時点で検索上確認できず。R7年度に「那須地域定住自立圏及び那須塩原市地域公共交通計画推進等支援業務」（企画競争、予定価格6,446,000円・labid要約）が公告されており、この推進支援業務の延長線で次期計画の調査（評価・アンケート）に着手する可能性あり（推定）。協議会（那須地域定住自立圏地域公共交通活性化協議会）はR8.1.21・R8.3.27に開催との要約あり（要確認）。R8.4.1にゆーバス・ゆータクのダイヤ改正実施。R9年度当初予算で策定業務を計上→R9春〜夏に公募型プロポーザルが典型パターン（推定）。</t>
         </is>
       </c>
-      <c r="I30" s="25" t="inlineStr">
+      <c r="I38" s="25" t="inlineStr">
         <is>
           <t>【R5】「令和5年度那須地域定住自立圏及び那須塩原市地域公共交通計画の推進支援業務」企画競争（公募型プロポーザル）— labid掲載。受託者は日本工営株式会社と記載された要約あり（単一要約のみ・要確認）、契約金額不明。【R7】「令和7年度那須地域定住自立圏及び那須塩原市地域公共交通計画推進等支援業務」企画競争、予定価格6,446,000円（labid要約）、受託者不明（要確認）。【R4・第2次計画策定業務】受託者・方式とも不明。市HP「入札結果(令和4年度分)」の四半期PDFに記載がある可能性（未確認、WebFetch不可）。labid.jpはWebFetchブロックのため詳細未取得。</t>
         </is>
       </c>
-      <c r="J30" s="22" t="inlineStr">
+      <c r="J38" s="22" t="inlineStr">
         <is>
           <t>・令和元年に栃木県内初のCO2排出量実質ゼロ宣言、R2に基礎自治体初の地域気候変動適応センター設置。R4.3「気候変動対策計画」（区域施策編＋適応計画統合、R4〜R12）で重点プロジェクトに「運輸部門からのGHG削減対策」→交通×脱炭素の論点あり。
 ・第2期環境基本計画【改定版】：R7年度環境審議会（9/3、11/27）で改定版案・パブコメ結果審議、終期R9→R12に延長。
@@ -3316,14 +3949,14 @@
 ・R8.4.1 ゆーバス・ゆータク ダイヤ改正。</t>
         </is>
       </c>
-      <c r="K30" s="22" t="inlineStr">
+      <c r="K38" s="22" t="inlineStr">
         <is>
           <t>・第2次市計画・定住自立圏計画がともにR9年度末終了：R8〜R9で市計画と圏域計画を同時改定する体制（2市2町協議会）と、推進支援業務（R5・R7）からの評価データ引継ぎの段取りを伺う。
 ・ゼロカーボン（県内初宣言）・気候変動対策計画の『運輸部門削減』重点プロジェクトと次期交通計画の連動（EVバス、デマンド交通の効率化等）を提案切り口に。
 ・那須塩原駅周辺まちづくり・総合計画後期基本計画との整合（駅を核とした交通結節点整備）を、第3次計画の論点として提示。</t>
         </is>
       </c>
-      <c r="L30" s="26" t="inlineStr">
+      <c r="L38" s="26" t="inlineStr">
         <is>
           <t>https://www.city.nasushiobara.tochigi.jp/soshikikarasagasu/kb/shinoseisakutokeikaku/1/5506.html
 https://www.city.nasushiobara.tochigi.jp/soshikikarasagasu/kb/shinoseisakutokeikaku/1/5504.html
@@ -3339,54 +3972,54 @@
 https://www.pref.tochigi.lg.jp/h03/koukyoulrt/documents/nasushiobarakoukyoukotsu2.pdf</t>
         </is>
       </c>
-      <c r="M30" s="22" t="inlineStr">
+      <c r="M38" s="22" t="inlineStr">
         <is>
           <t>labid.jpはWebFetchブロック。R5受託者『日本工営』は検索要約1件のみの情報で要確認。R7受託者未判明。市入札結果PDF（R4・R5・R7）の確認が次の一手。</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="22" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="22" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="22" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
         <is>
           <t>栃木県</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C39" s="23" t="inlineStr">
         <is>
           <t>さくら市</t>
         </is>
       </c>
-      <c r="D31" s="24" t="inlineStr"/>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="D39" s="24" t="inlineStr"/>
+      <c r="E39" s="22" t="inlineStr">
         <is>
           <t>第2次さくら市環境基本計画（H30〜R9）※主ターゲット。参考：さくら市地域公共交通計画はR6〜R10（R10年度末終期）</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F39" s="22" t="inlineStr">
         <is>
           <t>第2次さくら市環境基本計画（H30.3策定、H30〜R9の10年間）：めざす環境像「身近な自然を大切にする環境にやさしいまち」。自然環境・地球環境・生活環境の保全と、それを支える環境教育・環境交流の推進を柱に総合的に推進。市・事業者・市民・滞在者の連携の「道しるべ」と位置付け、年次報告書（さくら市の環境）で進捗管理、SDGsとの対応も整理済。
 交通：さくら市地域公共交通計画（R6.3策定、R6〜R10の5年間、網形成計画の後継）。計画期間はR6〜R10で確定（推定解除）。R4年度に国の地域公共交通調査事業（補助）で実態調査を実施。</t>
         </is>
       </c>
-      <c r="G31" s="22" t="inlineStr">
+      <c r="G39" s="22" t="inlineStr">
         <is>
           <t>市民生活部 生活環境課 環境保全係（〒329-1392 さくら市氏家2771、電話 028-681-1126）。交通計画は「さくら市地域公共交通会議」所管課（総合政策課系と推定・要確認）。</t>
         </is>
       </c>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="H39" s="22" t="inlineStr">
         <is>
           <t>環境基本計画はR9年度末終了のため、第3次計画はR8〜R9年度で策定作業（R8アンケート→R9審議会・パブコメ）の見込み（推定）。2026-10時点で第3次策定支援業務の公募・アンケート実施情報は検索で確認できず→R9単年度策定（R9当初予算計上・R9春発注）の可能性が高い（推定）。進行管理は環境審議会および「さくら市環境基本計画策定委員会」（市民・事業者）が担う。並行してさくら市緑の基本計画（案）がR8.1に公表されており、環境系計画の改定が順次進行中。</t>
         </is>
       </c>
-      <c r="I31" s="22" t="inlineStr">
+      <c r="I39" s="22" t="inlineStr">
         <is>
           <t>不明。第2次環境基本計画（H28〜H29策定）の策定支援業務の方式・受託者・金額は検索で確認できず（試行：『環境基本計画 策定支援業務 入札結果 平成29年度』、『策定委託 株式会社 策定経過』、NJSS等アグリゲータ検索。市HPに平成29年度物品等入札結果一覧の掲載あり→同PDFで確認可能性、WebFetch未実施）。交通計画（R5年度策定）の策定業務も受託者不明。関連調達：R6年度『さくら市AIオンデマンド交通システム導入・運用業務委託』公募型プロポーザル（R6.5.21審査、5.27結果通知、6月上旬契約予定）、受託者名は検索結果に表示されず（要確認）。</t>
         </is>
       </c>
-      <c r="J31" s="22" t="inlineStr">
+      <c r="J39" s="22" t="inlineStr">
         <is>
           <t>・「さくら市地球環境にやさしい小都市（まち）宣言」を表明（ゼロカーボンシティ相当、R6.3表明との要約あり・要確認）。さくら市気候変動対策推進計画、第3次さくら市地球温暖化対策実行計画を策定済（期間は未確認）。温室効果ガス排出量見える化（みんなの算定）、事業者向け脱炭素支援一覧を展開。
 ・バイオマス産業都市構想（R1.7）。
@@ -3395,14 +4028,14 @@
 ・第2次総合計画後期基本計画（R3.3〜）の終期接近→第3次総合計画との整合が次期環境計画の論点（終期は要確認）。</t>
         </is>
       </c>
-      <c r="K31" s="22" t="inlineStr">
+      <c r="K39" s="22" t="inlineStr">
         <is>
           <t>・第2次環境基本計画がR9年度末終了：第3次は総合計画改定・気候変動対策推進計画・温暖化実行計画との統合（区域施策編・適応計画の内包）を提案軸に、R9単年度か2か年かの策定スケジュールと予算要求時期を伺う。
 ・『地球環境にやさしい小都市宣言』と事業者向け脱炭素支援を、次期環境基本計画の重点プロジェクトに格上げする構成案（見える化データの活用）。
 ・交通計画（R10終期）とAIオンデマンド交通の実績評価を環境側（運輸部門CO2）と連動させる切り口。交通計画の次期改定はR9〜R10着手見込みで、環境計画と続けて接点を持てる。</t>
         </is>
       </c>
-      <c r="L31" s="26" t="inlineStr">
+      <c r="L39" s="26" t="inlineStr">
         <is>
           <t>https://www.city.tochigi-sakura.lg.jp/life/000014/000590/p001957.html
 https://www.city.tochigi-sakura.lg.jp/life/000014/000121/000403/p001957.html
@@ -3420,53 +4053,53 @@
 https://www.city.tochigi-sakura.lg.jp/office/000002/000202/index.html</t>
         </is>
       </c>
-      <c r="M31" s="22" t="inlineStr">
+      <c r="M39" s="22" t="inlineStr">
         <is>
           <t>千葉県佐倉市の結果が混在したため除外済。交通計画期間R6〜R10は検索結果本文で確認。過去の環境計画策定業務の受託者は市HPの平成28・29年度入札結果PDFで要確認。</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="22" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="22" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="22" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
         <is>
           <t>栃木県</t>
         </is>
       </c>
-      <c r="C32" s="23" t="inlineStr">
+      <c r="C40" s="23" t="inlineStr">
         <is>
           <t>那須町</t>
         </is>
       </c>
-      <c r="D32" s="24" t="inlineStr"/>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="D40" s="24" t="inlineStr"/>
+      <c r="E40" s="22" t="inlineStr">
         <is>
           <t>那須町地域公共交通計画（R4〜R9、6か年）＋那須地域定住自立圏地域公共交通計画（第2次、R5.4〜R10.3）。※環境は第3次那須町環境基本計画（R8〜R17）策定済のため対象外</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F40" s="22" t="inlineStr">
         <is>
           <t>那須町地域公共交通計画（R4.3策定、R4〜R9の6か年、町全域）：前計画の那須町地域公共交通網形成計画（R3年度末終了）の後継で、『持続可能でまちづくりと一体的な公共交通体系』を目的とする町の公共交通マスタープラン。デマンド型乗合交通（地域内フィーダー系統、運行は那須合同自動車㈱・3年毎選定）による空白地域解消と町民バス路線の維持、バスブック発行等の利用促進が柱。進行管理は法定協議会（那須町地域公共交通活性化協議会）で年2回定期開催、指標評価値を報告。</t>
         </is>
       </c>
-      <c r="G32" s="22" t="inlineStr">
+      <c r="G40" s="22" t="inlineStr">
         <is>
           <t>ふるさと定住課 公共交通係（町HP「公共交通係」office1003ページ、検索要約で課名確認・要確認）。電話番号は未確認（町代表 0287-72-6901 は未検証・要確認）。契約は財政課 契約管理係。</t>
         </is>
       </c>
-      <c r="H32" s="22" t="inlineStr">
+      <c r="H40" s="22" t="inlineStr">
         <is>
           <t>町計画R9年度末終了、定住自立圏計画も同時にR9年度末終了のため、次期計画はR8〜R9年度策定見込み（推定）。2026-10時点で町の次期計画策定業務の公募は検索で確認できず（前回はR3年度単年度で策定→今回もR9単年度策定、R9当初予算計上の可能性・推定）。第7次那須町振興計画後期基本計画がR3〜R7で終了しており、R8以降の新振興計画との整合が必要（新計画の名称・期間は未確認）。関連：栃木県「令和8年度広域公共交通連携検討業務委託」プロポ（県による広域連携検討、inputのファクトチェックより）。</t>
         </is>
       </c>
-      <c r="I32" s="22" t="inlineStr">
+      <c r="I40" s="22" t="inlineStr">
         <is>
           <t>不明。現行計画（R3年度策定）の策定支援業務について方式・受託者・金額とも検索で確認できず（試行：『那須町地域公共交通計画 策定業務 委託 プロポーザル 令和3年度』、『那須町 入札結果 令和3年度 地域公共交通計画策定業務』、『策定支援業務 落札 受託 コンサルタント』、NJSS/nsearchの那須町ページは表示されるが該当案件の本文なし）。協議会発注（補助金活用）の可能性があり町の入札結果に載らないケースも想定（推定）。なお広域分はR5・R7『那須地域定住自立圏及び那須塩原市地域公共交通計画推進(等)支援業務』（那須塩原市発注、R5受託者は日本工営との要約あり・要確認）が圏域4市町をカバー。</t>
         </is>
       </c>
-      <c r="J32" s="22" t="inlineStr">
+      <c r="J40" s="22" t="inlineStr">
         <is>
           <t>・町民バス湯本線・追分・黒磯駅線はR7.4.1から4往復→3往復に減便（運転手不足等の路線維持課題）。
 ・デマンド型乗合交通「当日予約」実証実験（R5.1〜）。
@@ -3476,14 +4109,14 @@
 ・振興計画の改定期（第7次後期R3〜R7終了）。</t>
         </is>
       </c>
-      <c r="K32" s="22" t="inlineStr">
+      <c r="K40" s="22" t="inlineStr">
         <is>
           <t>・町計画と定住自立圏計画がともにR9年度末終了：町単独計画と圏域計画を同時並行で改定する際の役割分担・データ共有（R5・R7推進支援業務の成果活用）の段取りを伺う。
 ・町民バス減便（R7.4）・デマンド当日予約実証の評価を踏まえ、次期計画での路線再編・デマンド拡充・観光二次交通（那須高原）の統合設計を提案。
 ・新振興計画（R8〜）や第3次環境基本計画（R8〜）との整合を図った計画構成（脱炭素・観光MaaS等）を切り口に。</t>
         </is>
       </c>
-      <c r="L32" s="26" t="inlineStr">
+      <c r="L40" s="26" t="inlineStr">
         <is>
           <t>https://www.town.nasu.lg.jp/0242/info-0000002729-1.html
 https://www.town.nasu.lg.jp/manage/contents/upload/6243b2b07f368.pdf
@@ -3499,54 +4132,54 @@
 https://labid.jp/projects/8d260a2f-ed2b-49c9-b300-b380e4a5aee5</t>
         </is>
       </c>
-      <c r="M32" s="22" t="inlineStr">
+      <c r="M40" s="22" t="inlineStr">
         <is>
           <t>過去の策定業務受託者は未判明。計画書PDF巻末（策定体制・協力会社）の目視確認、または協議会資料での確認を推奨。町代表電話番号は未検証。</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="22" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="22" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="22" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
         <is>
           <t>栃木県</t>
         </is>
       </c>
-      <c r="C33" s="23" t="inlineStr">
+      <c r="C41" s="23" t="inlineStr">
         <is>
           <t>那珂川町</t>
         </is>
       </c>
-      <c r="D33" s="24" t="inlineStr"/>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="D41" s="24" t="inlineStr"/>
+      <c r="E41" s="22" t="inlineStr">
         <is>
           <t>那須地域定住自立圏地域公共交通計画（第2次、R5.4〜R10.3）＋那珂川町地域公共交通計画（R5.3策定、期間未確認：圏域計画と同じR5〜R9の可能性・推定）。環境：第2次那珂川町環境基本計画（後期計画）期間不明</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F41" s="22" t="inlineStr">
         <is>
           <t>那珂川町地域公共交通計画（R5.3策定）：町内の公共交通はデマンドタクシー「なかちゃん号」とコミュニティバス「馬頭烏山線」（JR烏山駅〜馬頭高校〜町役場）が軸。R5年度実績：なかちゃん号 運行243日・利用7,697人（日平均31.7人、登録者2,685人）、馬頭烏山線 運行360日・利用20,937人（平日日平均78.9人／休日15.1人）。計画期間は検索で確認できず（圏域計画とセットでR5〜R9と推定・要確認）。上位の那須地域定住自立圏地域公共交通計画（R5.4〜R10.3）が圏域幹線・連携を担う。
 環境：第2次那珂川町環境基本計画（後期計画）は町HPにPDF掲載、所管は生活環境課。期間は未確認（第1次は2009年3月策定との要約あり・要確認）。</t>
         </is>
       </c>
-      <c r="G33" s="22" t="inlineStr">
+      <c r="G41" s="22" t="inlineStr">
         <is>
           <t>生活環境課 生活交通係（地域公共交通の総合調整・推進。町HP office0042）。環境基本計画も生活環境課（環境推進係との要約あり・要確認）。電話番号は未確認。</t>
         </is>
       </c>
-      <c r="H33" s="22" t="inlineStr">
+      <c r="H41" s="22" t="inlineStr">
         <is>
           <t>圏域計画（R9年度末終了）の改定に合わせ、町計画もR8〜R9年度に改定作業となる見込み（推定）。2026-10時点で次期計画の策定業務公募は検索で確認できず。第3次那珂川町総合振興計画（基本構想R8〜R17、前期基本計画R8〜R12）がR8.3策定済のため、次期交通計画・環境計画は新総合振興計画に沿った改定となる。R7.1.30に地域公共交通確保維持事業の事業評価を公表（要約ベース）。</t>
         </is>
       </c>
-      <c r="I33" s="22" t="inlineStr">
+      <c r="I41" s="22" t="inlineStr">
         <is>
           <t>不明。R5.3策定の町計画の策定支援業務について方式・受託者・金額は検索で確認できず（試行：『主要施策の成果 地域公共交通計画策定業務委託』、『公共交通計画 策定業務 入札結果 落札 令和4年』、町HP入札・契約（物品）ページは表示されるが該当案件本文なし）。圏域分はR5・R7『那須地域定住自立圏及び那須塩原市地域公共交通計画推進(等)支援業務』（那須塩原市発注・企画競争、R5受託者は日本工営との要約あり・要確認、R7予定価格6,446,000円）が那珂川町を含む4市町をカバー。環境基本計画の策定業務も不明。</t>
         </is>
       </c>
-      <c r="J33" s="22" t="inlineStr">
+      <c r="J41" s="22" t="inlineStr">
         <is>
           <t>・コミュニティバス馬頭烏山線はR6.10.1に運行会社を変更（関東自動車の告知あり）→運転手不足・事業者確保が課題（推定）。
 ・JR烏山線（隣接那須烏山市の終着駅烏山に接続）の存続議論が地域で取り沙汰（ローカル線解説記事レベル・要確認）。
@@ -3556,14 +4189,14 @@
 ・福岡県那珂川市・茨城県那珂市の結果が混在したため除外済。</t>
         </is>
       </c>
-      <c r="K33" s="22" t="inlineStr">
+      <c r="K41" s="22" t="inlineStr">
         <is>
           <t>・圏域計画・町計画がR9年度末で同時に終期：町単独計画をどこまで圏域計画に統合するか（小規模町の負担軽減）の方針と、改定時期・予算化の見込みを伺う。
 ・なかちゃん号（日平均31.7人）と馬頭烏山線（運行会社変更R6.10）の実績を踏まえた次期の運行形態（AIデマンド化、JR烏山駅接続強化、事業者確保策）を提案軸に。
 ・第3次総合振興計画（R8〜）策定直後のタイミングで、環境基本計画（後期計画）の終期確認と、交通・環境計画の一体的見直し（運輸部門脱炭素・過疎対策）を切り口に。</t>
         </is>
       </c>
-      <c r="L33" s="26" t="inlineStr">
+      <c r="L41" s="26" t="inlineStr">
         <is>
           <t>https://www.town.tochigi-nakagawa.lg.jp/life/kurashi/2023-0331-0958-5.html
 https://www.city.nasushiobara.tochigi.jp/soshikikarasagasu/kb/shinoseisakutokeikaku/1/5504.html
@@ -3581,29 +4214,29 @@
 https://labid.jp/projects/8d260a2f-ed2b-49c9-b300-b380e4a5aee5</t>
         </is>
       </c>
-      <c r="M33" s="22" t="inlineStr">
+      <c r="M41" s="22" t="inlineStr">
         <is>
           <t>町計画・環境基本計画（後期）の計画期間は計画書PDF本文で要確認（WebFetch上限のため未取得）。</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="B35" s="29" t="inlineStr">
+    <row r="42"/>
+    <row r="43">
+      <c r="B43" s="29" t="inlineStr">
         <is>
           <t>凡例</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="30" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="30" t="inlineStr">
         <is>
           <t>黄色＝次期計画に着手済み（策定業務の公告等を確認）／緑＝前回の策定業務の情報あり／根拠URL列は先頭URLのみリンク</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M33"/>
+  <autoFilter ref="A4:M41"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId2"/>
@@ -3634,6 +4267,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
@@ -14229,6 +14870,11 @@
           <t>掲載</t>
         </is>
       </c>
+      <c r="U14" s="20" t="inlineStr">
+        <is>
+          <t>→メモ</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
@@ -16266,6 +16912,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId18"/>
+    <hyperlink ref="U14" location="'営業メモ'!C12" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId21"/>
@@ -18684,20 +19331,20 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId2"/>
-    <hyperlink ref="U4" location="'営業メモ'!C12" display="→メモ"/>
+    <hyperlink ref="U4" location="'営業メモ'!C13" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
-    <hyperlink ref="U5" location="'営業メモ'!C13" display="→メモ"/>
+    <hyperlink ref="U5" location="'営業メモ'!C14" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId8"/>
-    <hyperlink ref="U7" location="'営業メモ'!C14" display="→メモ"/>
+    <hyperlink ref="U7" location="'営業メモ'!C15" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId12"/>
-    <hyperlink ref="U10" location="'営業メモ'!C15" display="→メモ"/>
+    <hyperlink ref="U10" location="'営業メモ'!C16" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId15"/>
@@ -18706,7 +19353,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId20"/>
-    <hyperlink ref="U14" location="'営業メモ'!C16" display="→メモ"/>
+    <hyperlink ref="U14" location="'営業メモ'!C17" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId23"/>
@@ -18715,12 +19362,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId28"/>
-    <hyperlink ref="U22" location="'営業メモ'!C17" display="→メモ"/>
+    <hyperlink ref="U22" location="'営業メモ'!C18" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId29"/>
-    <hyperlink ref="U23" location="'営業メモ'!C17" display="→メモ"/>
+    <hyperlink ref="U23" location="'営業メモ'!C18" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId31"/>
-    <hyperlink ref="U25" location="'営業メモ'!C17" display="→メモ"/>
+    <hyperlink ref="U25" location="'営業メモ'!C18" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId34"/>
@@ -21964,7 +22611,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId16"/>
-    <hyperlink ref="U11" location="'営業メモ'!C18" display="→メモ"/>
+    <hyperlink ref="U11" location="'営業メモ'!C19" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId19"/>
@@ -21980,7 +22627,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId31"/>
-    <hyperlink ref="U21" location="'営業メモ'!C19" display="→メモ"/>
+    <hyperlink ref="U21" location="'営業メモ'!C20" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId34"/>
@@ -22719,6 +23366,11 @@
           <t>掲載</t>
         </is>
       </c>
+      <c r="U9" s="20" t="inlineStr">
+        <is>
+          <t>→メモ</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="n">
@@ -22895,6 +23547,11 @@
           <t>未掲載</t>
         </is>
       </c>
+      <c r="U11" s="20" t="inlineStr">
+        <is>
+          <t>→メモ</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="n">
@@ -26145,6 +26802,11 @@
       <c r="T51" s="12" t="inlineStr">
         <is>
           <t>掲載</t>
+        </is>
+      </c>
+      <c r="U51" s="20" t="inlineStr">
+        <is>
+          <t>→メモ</t>
         </is>
       </c>
     </row>
@@ -27162,14 +27824,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId8"/>
-    <hyperlink ref="U7" location="'営業メモ'!C20" display="→メモ"/>
+    <hyperlink ref="U7" location="'営業メモ'!C21" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId12"/>
+    <hyperlink ref="U9" location="'営業メモ'!C24" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId15"/>
+    <hyperlink ref="U11" location="'営業メモ'!C25" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId18"/>
@@ -27179,7 +27843,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId24"/>
-    <hyperlink ref="U19" location="'営業メモ'!C22" display="→メモ"/>
+    <hyperlink ref="U19" location="'営業メモ'!C26" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId27"/>
@@ -27198,34 +27862,35 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId42"/>
-    <hyperlink ref="U45" location="'営業メモ'!C21" display="→メモ"/>
+    <hyperlink ref="U45" location="'営業メモ'!C22" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId48"/>
+    <hyperlink ref="U51" location="'営業メモ'!C27" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q53" r:id="rId51"/>
-    <hyperlink ref="U53" location="'営業メモ'!C22" display="→メモ"/>
+    <hyperlink ref="U53" location="'営業メモ'!C23" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId52"/>
-    <hyperlink ref="U54" location="'営業メモ'!C22" display="→メモ"/>
+    <hyperlink ref="U54" location="'営業メモ'!C23" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId53"/>
-    <hyperlink ref="U55" location="'営業メモ'!C22" display="→メモ"/>
+    <hyperlink ref="U55" location="'営業メモ'!C23" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId54"/>
-    <hyperlink ref="U56" location="'営業メモ'!C22" display="→メモ"/>
+    <hyperlink ref="U56" location="'営業メモ'!C23" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId55"/>
-    <hyperlink ref="U57" location="'営業メモ'!C22" display="→メモ"/>
+    <hyperlink ref="U57" location="'営業メモ'!C23" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId56"/>
-    <hyperlink ref="U58" location="'営業メモ'!C22" display="→メモ"/>
+    <hyperlink ref="U58" location="'営業メモ'!C23" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId57"/>
-    <hyperlink ref="U59" location="'営業メモ'!C22" display="→メモ"/>
+    <hyperlink ref="U59" location="'営業メモ'!C23" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId58"/>
-    <hyperlink ref="U60" location="'営業メモ'!C22" display="→メモ"/>
+    <hyperlink ref="U60" location="'営業メモ'!C23" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId60"/>
-    <hyperlink ref="U62" location="'営業メモ'!C22" display="→メモ"/>
+    <hyperlink ref="U62" location="'営業メモ'!C23" display="→メモ"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29200,6 +29865,11 @@
           <t>掲載</t>
         </is>
       </c>
+      <c r="U23" s="20" t="inlineStr">
+        <is>
+          <t>→メモ</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
@@ -30212,6 +30882,11 @@
           <t>掲載</t>
         </is>
       </c>
+      <c r="U34" s="20" t="inlineStr">
+        <is>
+          <t>→メモ</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="n">
@@ -30754,6 +31429,11 @@
       <c r="T40" s="12" t="inlineStr">
         <is>
           <t>掲載</t>
+        </is>
+      </c>
+      <c r="U40" s="20" t="inlineStr">
+        <is>
+          <t>→メモ</t>
         </is>
       </c>
     </row>
@@ -31408,9 +32088,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId34"/>
+    <hyperlink ref="U23" location="'営業メモ'!C33" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId36"/>
-    <hyperlink ref="U24" location="'営業メモ'!C23" display="→メモ"/>
+    <hyperlink ref="U24" location="'営業メモ'!C28" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId39"/>
@@ -31429,6 +32110,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId54"/>
+    <hyperlink ref="U34" location="'営業メモ'!C31" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId57"/>
@@ -31440,12 +32122,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId65"/>
+    <hyperlink ref="U40" location="'営業メモ'!C32" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId67"/>
-    <hyperlink ref="U42" location="'営業メモ'!C24" display="→メモ"/>
+    <hyperlink ref="U42" location="'営業メモ'!C29" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId69"/>
-    <hyperlink ref="U45" location="'営業メモ'!C25" display="→メモ"/>
+    <hyperlink ref="U45" location="'営業メモ'!C30" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -33995,30 +34678,30 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId6"/>
-    <hyperlink ref="U6" location="'営業メモ'!C26" display="→メモ"/>
+    <hyperlink ref="U6" location="'営業メモ'!C34" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId10"/>
-    <hyperlink ref="U8" location="'営業メモ'!C27" display="→メモ"/>
+    <hyperlink ref="U8" location="'営業メモ'!C35" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId12"/>
-    <hyperlink ref="U9" location="'営業メモ'!C28" display="→メモ"/>
+    <hyperlink ref="U9" location="'営業メモ'!C36" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId18"/>
-    <hyperlink ref="U12" location="'営業メモ'!C29" display="→メモ"/>
+    <hyperlink ref="U12" location="'営業メモ'!C37" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId22"/>
-    <hyperlink ref="U14" location="'営業メモ'!C30" display="→メモ"/>
+    <hyperlink ref="U14" location="'営業メモ'!C38" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId24"/>
-    <hyperlink ref="U15" location="'営業メモ'!C31" display="→メモ"/>
+    <hyperlink ref="U15" location="'営業メモ'!C39" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId27"/>
@@ -34043,10 +34726,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId48"/>
-    <hyperlink ref="U27" location="'営業メモ'!C32" display="→メモ"/>
+    <hyperlink ref="U27" location="'営業メモ'!C40" display="→メモ"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId50"/>
-    <hyperlink ref="U28" location="'営業メモ'!C33" display="→メモ"/>
+    <hyperlink ref="U28" location="'営業メモ'!C41" display="→メモ"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/research/自治体営業リスト_統合版_2026-10.xlsx
+++ b/research/自治体営業リスト_統合版_2026-10.xlsx
@@ -13422,7 +13422,7 @@
       </c>
       <c r="T12" s="13" t="n"/>
     </row>
-    <row r="13" ht="69" customHeight="1">
+    <row r="13" ht="134" customHeight="1">
       <c r="A13" s="13" t="n">
         <v>10</v>
       </c>
@@ -13501,7 +13501,7 @@
       </c>
       <c r="R13" s="13" t="inlineStr">
         <is>
-          <t>交通：網形成計画2020〜2024年度で期間満了、後継の地域公共交通計画は検索で確認できず。環境：総合計画後期基本計画の関連計画一覧で期間R4〜R13、R4.3パブコメ結果公表（e_urlは環境政策課ページ）。</t>
+          <t>交通：網形成計画2020〜2024年度で期間満了、後継の地域公共交通計画は検索で確認できず。環境：総合計画後期基本計画の関連計画一覧で期間R4〜R13、R4.3パブコメ結果公表（e_urlは環境政策課ページ）。 【2026.10追記】上信電鉄沿線地域交通リ・デザイン推進協議会（県主導の法定協議会、富岡市・下仁田町・甘楽町・高崎市・南牧村等）が沿線の交通再構築を検討中（R7.6第7回協議会で再構築調査・意見聴取、R8.7.21第3回沿線地域懇談会） https://www.pref.gunma.jp/page/711517.html 。沿線計画の策定は未確認。</t>
         </is>
       </c>
       <c r="S13" s="17" t="inlineStr">
@@ -13600,7 +13600,7 @@
       </c>
       <c r="T14" s="13" t="n"/>
     </row>
-    <row r="15" ht="95" customHeight="1">
+    <row r="15" ht="108" customHeight="1">
       <c r="A15" s="13" t="n">
         <v>12</v>
       </c>
@@ -13679,7 +13679,7 @@
       </c>
       <c r="R15" s="13" t="inlineStr">
         <is>
-          <t>交通：R6〜R7の2か年で策定支援業務（プロポーザル https://www.city.midori.gunma.jp/kurashi/1001625/1006056/1006059.html ）、R8〜R12。環境：後期基本計画2023〜2027年度でR9終期（期間はSDGs未来都市計画の記載で確認、計画書本体URLは未確認）。次期計画の着手は未確認。2050年みどり5つのゼロ宣言。</t>
+          <t>交通：R6〜R7の2か年で策定支援業務（プロポーザル https://www.city.midori.gunma.jp/kurashi/1001625/1006056/1006059.html ）、R8〜R12。環境：後期基本計画2023〜2027年度でR9終期（期間はSDGs未来都市計画の記載で確認、計画書本体URLは未確認）。次期計画の着手は未確認。2050年みどり5つのゼロ宣言。 【2026.10再調査】環境基本計画の改定業務・審議会での審議は引き続き確認できず。</t>
         </is>
       </c>
       <c r="S15" s="17" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="T19" s="13" t="n"/>
     </row>
-    <row r="20" ht="134" customHeight="1">
+    <row r="20" ht="225" customHeight="1">
       <c r="A20" s="13" t="n">
         <v>17</v>
       </c>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="R20" s="13" t="inlineStr">
         <is>
-          <t>交通：町独自計画は確認できず（町営バス5路線、デマンド検討）。群馬県地域公共交通計画（群馬県交通まちづくり戦略の見直し、R5〜R9、県全域を4広域圏で記載） https://www.pref.gunma.jp/page/140624.html が県全域をカバー。県はR8.9.29に4広域圏別の計画改定業務プロポーザルを公告（履行期限R9.3.12） https://www.pref.gunma.jp/site/nyuusatsu/list135-773.html 。環境：H29〜H38（R8）でR8年度終期、次期（第3次）計画の作業は検索で確認できず。要注視。</t>
+          <t>交通：町独自計画は確認できず（町営バス5路線、デマンド検討）。群馬県地域公共交通計画（群馬県交通まちづくり戦略の見直し、R5〜R9、県全域を4広域圏で記載） https://www.pref.gunma.jp/page/140624.html が県全域をカバー。県はR8.9.29に4広域圏別の計画改定業務プロポーザルを公告（履行期限R9.3.12） https://www.pref.gunma.jp/site/nyuusatsu/list135-773.html 。環境：H29〜H38（R8）でR8年度終期、次期（第3次）計画の作業は検索で確認できず。要注視。 【2026.10追記】上信電鉄沿線地域交通リ・デザイン推進協議会（県主導の法定協議会、富岡市・下仁田町・甘楽町・高崎市・南牧村等）が沿線の交通再構築を検討中（R7.6第7回協議会で再構築調査・意見聴取、R8.7.21第3回沿線地域懇談会） https://www.pref.gunma.jp/page/711517.html 。沿線計画の策定は未確認。 環境基本計画の改定委託・入札も2026.10の再調査で確認できず。</t>
         </is>
       </c>
       <c r="S20" s="20" t="inlineStr">
@@ -14044,7 +14044,7 @@
       </c>
       <c r="T20" s="13" t="n"/>
     </row>
-    <row r="21" ht="108" customHeight="1">
+    <row r="21" ht="186" customHeight="1">
       <c r="A21" s="13" t="n">
         <v>18</v>
       </c>
@@ -14103,7 +14103,7 @@
       <c r="Q21" s="13" t="n"/>
       <c r="R21" s="13" t="inlineStr">
         <is>
-          <t>交通：村独自計画は検索で確認できず。群馬県地域公共交通計画（群馬県交通まちづくり戦略の見直し、R5〜R9、県全域を4広域圏で記載） https://www.pref.gunma.jp/page/140624.html が県全域をカバー。県はR8.9.29に4広域圏別の計画改定業務プロポーザルを公告（履行期限R9.3.12） https://www.pref.gunma.jp/site/nyuusatsu/list135-773.html 。環境：環境基本計画は確認できず。</t>
+          <t>交通：村独自計画は検索で確認できず。群馬県地域公共交通計画（群馬県交通まちづくり戦略の見直し、R5〜R9、県全域を4広域圏で記載） https://www.pref.gunma.jp/page/140624.html が県全域をカバー。県はR8.9.29に4広域圏別の計画改定業務プロポーザルを公告（履行期限R9.3.12） https://www.pref.gunma.jp/site/nyuusatsu/list135-773.html 。環境：環境基本計画は確認できず。 【2026.10追記】上信電鉄沿線地域交通リ・デザイン推進協議会（県主導の法定協議会、富岡市・下仁田町・甘楽町・高崎市・南牧村等）が沿線の交通再構築を検討中（R7.6第7回協議会で再構築調査・意見聴取、R8.7.21第3回沿線地域懇談会） https://www.pref.gunma.jp/page/711517.html 。沿線計画の策定は未確認。</t>
         </is>
       </c>
       <c r="S21" s="20" t="inlineStr">
@@ -14113,7 +14113,7 @@
       </c>
       <c r="T21" s="13" t="n"/>
     </row>
-    <row r="22" ht="66" customHeight="1">
+    <row r="22" ht="121" customHeight="1">
       <c r="A22" s="13" t="n">
         <v>19</v>
       </c>
@@ -14182,7 +14182,7 @@
       <c r="Q22" s="13" t="n"/>
       <c r="R22" s="13" t="inlineStr">
         <is>
-          <t>交通：R6.4策定（甘楽町地域公共交通協議会）、2024〜2028年度。環境：環境基本計画は確認できず（総合計画内で環境施策）。</t>
+          <t>交通：R6.4策定（甘楽町地域公共交通協議会）、2024〜2028年度。環境：環境基本計画は確認できず（総合計画内で環境施策）。 【2026.10追記】上信電鉄沿線地域交通リ・デザイン推進協議会（県主導の法定協議会、富岡市・下仁田町・甘楽町・高崎市・南牧村等）が沿線の交通再構築を検討中（R7.6第7回協議会で再構築調査・意見聴取、R8.7.21第3回沿線地域懇談会） https://www.pref.gunma.jp/page/711517.html 。沿線計画の策定は未確認。</t>
         </is>
       </c>
       <c r="S22" s="17" t="inlineStr">

--- a/research/自治体営業リスト_統合版_2026-10.xlsx
+++ b/research/自治体営業リスト_統合版_2026-10.xlsx
@@ -17,8 +17,9 @@
     <sheet name="茨城県" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="栃木県" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="群馬県" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="営業メモ" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="ファクトチェック結果" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="宮崎県" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="営業メモ" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ファクトチェック結果" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="TGT_MIN">'集計・設定'!$C$4</definedName>
@@ -32,9 +33,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'茨城県'!$A$3:$T$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'栃木県'!$A$3:$T$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'群馬県'!$A$3:$T$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'営業メモ'!$A$4:$N$41</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'営業メモ'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'ファクトチェック結果'!$A$4:$L$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'宮崎県'!$A$3:$T$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'営業メモ'!$A$4:$N$41</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'営業メモ'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'ファクトチェック結果'!$A$4:$L$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1628,6 +1630,791 @@
 </file>
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>3</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>3</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>4</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>4</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>5</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>5</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>6</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>6</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>7</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>7</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>8</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>8</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>9</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>9</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>10</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>10</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>11</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>11</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>12</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>12</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>13</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>13</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>14</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>14</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>15</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>15</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>16</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>16</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>17</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>17</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>18</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>18</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>19</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>19</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>20</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>20</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>21</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>21</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>22</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>22</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>23</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>23</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>24</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>24</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>25</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>25</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>26</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>26</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>27</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>27</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
+    <from>
+      <col>21</col>
+      <colOff>28575</colOff>
+      <row>28</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>828675</colOff>
+      <row>28</row>
+      <rowOff>828675</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="twoCell">
     <from>
@@ -11801,7 +12588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12224,247 +13011,289 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>宮崎県</t>
+        </is>
+      </c>
+      <c r="C18" s="3">
+        <f>COUNTA('宮崎県'!$C$4:$C$29)</f>
+        <v/>
+      </c>
+      <c r="D18" s="3">
+        <f>COUNTIF('宮崎県'!$C$4:$C$29,"◎ 営業")</f>
+        <v/>
+      </c>
+      <c r="E18" s="3">
+        <f>COUNTIF('宮崎県'!$C$4:$C$29,"△ 着手済・要確認")</f>
+        <v/>
+      </c>
+      <c r="F18" s="3">
+        <f>COUNTIF('宮崎県'!$C$4:$C$29,"？ 期間要確認")</f>
+        <v/>
+      </c>
+      <c r="G18" s="3">
+        <f>COUNTIF('宮崎県'!$C$4:$C$29,"✕ 対象外")</f>
+        <v/>
+      </c>
+      <c r="H18" s="3">
+        <f>COUNTIF('宮崎県'!$S$4:$S$29,"未調査")</f>
+        <v/>
+      </c>
+      <c r="I18" s="3">
+        <f>COUNTIF('宮崎県'!$S$4:$S$29,"交通のみ調査")+COUNTIF('宮崎県'!$S$4:$S$29,"環境のみ調査")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C18" s="2">
-        <f>SUM(C9:C17)</f>
-        <v/>
-      </c>
-      <c r="D18" s="2">
-        <f>SUM(D9:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="2">
-        <f>SUM(E9:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="2">
-        <f>SUM(F9:F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="2">
-        <f>SUM(G9:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="2">
-        <f>SUM(H9:H17)</f>
-        <v/>
-      </c>
-      <c r="I18" s="2">
-        <f>SUM(I9:I17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="C19" s="2">
+        <f>SUM(C9:C18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="2">
+        <f>SUM(D9:D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="2">
+        <f>SUM(E9:E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="2">
+        <f>SUM(F9:F18)</f>
+        <v/>
+      </c>
+      <c r="G19" s="2">
+        <f>SUM(G9:G18)</f>
+        <v/>
+      </c>
+      <c r="H19" s="2">
+        <f>SUM(H9:H18)</f>
+        <v/>
+      </c>
+      <c r="I19" s="2">
+        <f>SUM(I9:I18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>■ 判定の見方</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>◎ 営業：どちらかの計画の終期が対象年度（初期値R9）で、次の計画の作業は見つかっていない</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>△ 着手済・要確認：終期は対象年度だが、次期計画の策定業務委託やパブコメをすでに確認済。委託先が決まっている可能性が高い</t>
+          <t>◎ 営業：どちらかの計画の終期が対象年度（初期値R9）で、次の計画の作業は見つかっていない</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>？ 期間要確認：終期がわからないため判定できない</t>
+          <t>△ 着手済・要確認：終期は対象年度だが、次期計画の策定業務委託やパブコメをすでに確認済。委託先が決まっている可能性が高い</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>✕ 対象外：終期が対象年度の外（R8以前は作成中または終了、R10以降は先）、または新計画を策定済</t>
+          <t>？ 期間要確認：終期がわからないため判定できない</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
+          <t>✕ 対象外：終期が対象年度の外（R8以前は作成中または終了、R10以降は先）、または新計画を策定済</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
           <t>－：その計画がない（環境基本計画を作っていない町村など）</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr"/>
-    </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>■ 入力する列</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>各県シートの「終期(令和年度)」と「改定状況」（未確認／着手済／策定済／計画なし）を直すと、判定が自動で変わります。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>「未確認」は、改定の動きが検索で見つからなかったという意味です。動きがないと確かめたわけではありません。</t>
+          <t>各県シートの「終期(令和年度)」と「改定状況」（未確認／着手済／策定済／計画なし）を直すと、判定が自動で変わります。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
+          <t>「未確認」は、改定の動きが検索で見つからなかったという意味です。動きがないと確かめたわけではありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
           <t>確度：確認済＝検索結果の本文に期間が書かれていた／推定＝策定時期などから推測（終期のセルは茶色の斜体）／不明＝確認できなかった</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr"/>
-    </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>■ 国交省一覧との照合（T列）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>国土交通省「地域公共交通計画の作成状況一覧」（令和8年5月末時点）と照合。掲載＝計画作成済み、期間満了＝一覧で灰色（計画期間が満了）。一覧には計画期間の記載がないため、終期は各計画書で確認。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
+          <t>国土交通省「地域公共交通計画の作成状況一覧」（令和8年5月末時点）と照合。掲載＝計画作成済み、期間満了＝一覧で灰色（計画期間が満了）。一覧には計画期間の記載がないため、終期は各計画書で確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
           <t>【当方未把握】＝一覧には計画があるが本調査で計画書を特定できていない／【当方は計画あり】＝本調査では計画を把握したが一覧に未掲載（旧法計画・最近の策定・名称違いの可能性）。</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr"/>
-    </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>■ 調査の方法と限界</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>【重要】検索回数に上限（1セッション200回）があるため、県によっては一部の市町村・計画を調べきれていません。「調査状況」列が「未調査」「交通のみ調査」の行は空欄・？になっていますが、計画がないという意味ではありません。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>2026年9月30日時点でWeb検索して調べました。自治体サイトやPDFを直接開けない環境だったため、期間は検索結果の本文・要約から取っています。</t>
+          <t>【重要】検索回数に上限（1セッション200回）があるため、県によっては一部の市町村・計画を調べきれていません。「調査状況」列が「未調査」「交通のみ調査」の行は空欄・？になっていますが、計画がないという意味ではありません。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
+          <t>2026年9月30日時点でWeb検索して調べました。自治体サイトやPDFを直接開けない環境だったため、期間は検索結果の本文・要約から取っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
           <t>計画リンクはエビデンスとして検索結果に出たURLを載せています。営業に行く前に、リンク先の計画書で計画期間を確かめてください。特に「推定」「不明」の行は必ず確認してください。</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>■ シート一覧（クリックで移動）</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>青森県</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>岩手県</t>
+          <t>青森県</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>宮城県</t>
+          <t>岩手県</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>秋田県</t>
+          <t>宮城県</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>山形県</t>
+          <t>秋田県</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>山形県</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>茨城県</t>
+          <t>福島県</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>栃木県</t>
+          <t>茨城県</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>群馬県</t>
+          <t>栃木県</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>営業メモ</t>
+          <t>群馬県</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>宮崎県</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>営業メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>ファクトチェック結果</t>
         </is>
@@ -12477,17 +13306,18 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B42" location="'青森県'!A1" display="青森県"/>
-    <hyperlink ref="B43" location="'岩手県'!A1" display="岩手県"/>
-    <hyperlink ref="B44" location="'宮城県'!A1" display="宮城県"/>
-    <hyperlink ref="B45" location="'秋田県'!A1" display="秋田県"/>
-    <hyperlink ref="B46" location="'山形県'!A1" display="山形県"/>
-    <hyperlink ref="B47" location="'福島県'!A1" display="福島県"/>
-    <hyperlink ref="B48" location="'茨城県'!A1" display="茨城県"/>
-    <hyperlink ref="B49" location="'栃木県'!A1" display="栃木県"/>
-    <hyperlink ref="B50" location="'群馬県'!A1" display="群馬県"/>
-    <hyperlink ref="B51" location="'営業メモ'!A1" display="営業メモ"/>
-    <hyperlink ref="B52" location="'ファクトチェック結果'!A1" display="ファクトチェック結果"/>
+    <hyperlink ref="B43" location="'青森県'!A1" display="青森県"/>
+    <hyperlink ref="B44" location="'岩手県'!A1" display="岩手県"/>
+    <hyperlink ref="B45" location="'宮城県'!A1" display="宮城県"/>
+    <hyperlink ref="B46" location="'秋田県'!A1" display="秋田県"/>
+    <hyperlink ref="B47" location="'山形県'!A1" display="山形県"/>
+    <hyperlink ref="B48" location="'福島県'!A1" display="福島県"/>
+    <hyperlink ref="B49" location="'茨城県'!A1" display="茨城県"/>
+    <hyperlink ref="B50" location="'栃木県'!A1" display="栃木県"/>
+    <hyperlink ref="B51" location="'群馬県'!A1" display="群馬県"/>
+    <hyperlink ref="B52" location="'宮崎県'!A1" display="宮崎県"/>
+    <hyperlink ref="B53" location="'営業メモ'!A1" display="営業メモ"/>
+    <hyperlink ref="B54" location="'ファクトチェック結果'!A1" display="ファクトチェック結果"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15488,6 +16318,2416 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="55" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>宮崎県　地域公共交通計画・環境基本計画の終期一覧（2026年9月30日時点の調査）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10">
+        <f>"営業判定の対象：終期 R"&amp;TGT_MIN&amp;"〜R"&amp;TGT_MAX&amp;"年度 →◎（着手済は△、期間不明は？）。終期セルの色：緑＝対象年度／橙＝その翌年度（次の候補）。対象年度は「集計・設定」シートのC4・C5のプルダウンで切替。"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>市町村</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>営業判定</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>交通判定</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>環境判定</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>地域公共交通計画</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>交通 計画期間</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>交通 終期(令和年度)</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>交通 確度</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>交通 改定状況</t>
+        </is>
+      </c>
+      <c r="K3" s="11" t="inlineStr">
+        <is>
+          <t>交通 計画リンク（エビデンス）</t>
+        </is>
+      </c>
+      <c r="L3" s="11" t="inlineStr">
+        <is>
+          <t>環境基本計画</t>
+        </is>
+      </c>
+      <c r="M3" s="11" t="inlineStr">
+        <is>
+          <t>環境 計画期間</t>
+        </is>
+      </c>
+      <c r="N3" s="11" t="inlineStr">
+        <is>
+          <t>環境 終期(令和年度)</t>
+        </is>
+      </c>
+      <c r="O3" s="11" t="inlineStr">
+        <is>
+          <t>環境 確度</t>
+        </is>
+      </c>
+      <c r="P3" s="11" t="inlineStr">
+        <is>
+          <t>環境 改定状況</t>
+        </is>
+      </c>
+      <c r="Q3" s="11" t="inlineStr">
+        <is>
+          <t>環境 計画リンク（エビデンス）</t>
+        </is>
+      </c>
+      <c r="R3" s="11" t="inlineStr">
+        <is>
+          <t>注釈（改定作業の状況など）</t>
+        </is>
+      </c>
+      <c r="S3" s="11" t="inlineStr">
+        <is>
+          <t>調査状況</t>
+        </is>
+      </c>
+      <c r="T3" s="11" t="inlineStr">
+        <is>
+          <t>国交省一覧(R8.5末)</t>
+        </is>
+      </c>
+      <c r="U3" s="11" t="inlineStr">
+        <is>
+          <t>営業メモ</t>
+        </is>
+      </c>
+      <c r="V3" s="12" t="inlineStr">
+        <is>
+          <t>位置図</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="409" customHeight="1">
+      <c r="A4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>宮崎市</t>
+        </is>
+      </c>
+      <c r="C4" s="14">
+        <f>IF(OR(D4="◎",E4="◎"),"◎ 営業",IF(OR(D4="△",E4="△"),"△ 着手済・要確認",IF(OR(D4="？",E4="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D4" s="15">
+        <f>IF(J4="計画なし","－",IF(J4="策定済","✕",IF(H4="","？",IF(AND(H4&gt;=TGT_MIN,H4&lt;=TGT_MAX),IF(J4="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E4" s="15">
+        <f>IF(P4="計画なし","－",IF(P4="策定済","✕",IF(N4="","？",IF(AND(N4&gt;=TGT_MIN,N4&lt;=TGT_MAX),IF(P4="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>宮崎市地域公共交通網形成計画（R2.3策定、期間延長中）※後継の宮崎市地域公共交通計画は策定中</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>R2〜R8（当初R2〜R6、R8.2再延長でR9.2まで）</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>着手済</t>
+        </is>
+      </c>
+      <c r="K4" s="16" t="inlineStr">
+        <is>
+          <t>https://www.city.miyazaki.miyazaki.jp/city/policy/transportation/223591.html</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>第四次宮崎市環境基本計画</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>R7〜R16</t>
+        </is>
+      </c>
+      <c r="N4" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="O4" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="P4" s="15" t="inlineStr">
+        <is>
+          <t>策定済</t>
+        </is>
+      </c>
+      <c r="Q4" s="16" t="inlineStr">
+        <is>
+          <t>https://www.city.miyazaki.miyazaki.jp/fs/8/3/8/2/2/9/_/838229.pdf</t>
+        </is>
+      </c>
+      <c r="R4" s="13" t="inlineStr">
+        <is>
+          <t>交通：網形成計画（R2〜R6の5年）を延長、R6.8地域公共交通会議で新計画（宮崎市地域公共交通計画）策定方針を承認。R8.2.6の令和7年度第2回宮崎市地域公共交通会議で議題『「宮崎市地域公共交通計画」策定スケジュールの見直し及び現計画期間の再延長について』（資料 https://www.city.miyazaki.miyazaki.jp/fs/8/7/2/3/1/6/_/__2___________________.pdf ）→次期計画策定作業中だが遅延。網形成計画ページに『計画期間を再延長しました（令和8年2月変更）』、期間R2〜R8（令和9年2月まで）。市は地域公共交通計画（マスタープラン）と利便増進実施計画（アクションプラン）を一体策定する方針。R7新規事業評価表（総合政策部総合政策課、事業期間R8〜R9）にR7データ分析・R8市全域の新計画策定・公表と記載（ https://www.city.miyazaki.miyazaki.jp/fs/8/7/6/4/6/3/_/01-03_______7_________.pdf ）→R8年度中に新計画策定予定。策定支援業務の委託公告は検索で未確認。担当：総合政策課（地域公共交通会議事務局 https://www.city.miyazaki.miyazaki.jp/city/policy/transportation/207006.html ）。旧網形成計画PDFらしきもの https://www.city.miyazaki.miyazaki.jp/fs/3/8/7/2/3/3/_/387233.pdf 。R8脱炭素先行地域づくり事業推進支援業務委託プロポあり。関連資料 https://www.city.miyazaki.miyazaki.jp/fs/8/3/4/6/2/1/_/834621.pdf 。環境：第三次計画（H30〜R9の予定をR5.3改訂でH30〜R6に短縮）の後継として第四次計画R7〜R16をR7.3策定。概要版 https://www.city.miyazaki.miyazaki.jp/fs/8/3/9/1/0/9/_/839109.pdf （どちらが本編か未確認）。</t>
+        </is>
+      </c>
+      <c r="S4" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T4" s="13" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="160" customHeight="1">
+      <c r="A5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>都城市</t>
+        </is>
+      </c>
+      <c r="C5" s="14">
+        <f>IF(OR(D5="◎",E5="◎"),"◎ 営業",IF(OR(D5="△",E5="△"),"△ 着手済・要確認",IF(OR(D5="？",E5="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D5" s="15">
+        <f>IF(J5="計画なし","－",IF(J5="策定済","✕",IF(H5="","？",IF(AND(H5&gt;=TGT_MIN,H5&lt;=TGT_MAX),IF(J5="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E5" s="15">
+        <f>IF(P5="計画なし","－",IF(P5="策定済","✕",IF(N5="","？",IF(AND(N5&gt;=TGT_MIN,N5&lt;=TGT_MAX),IF(P5="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>都城市地域公共交通計画</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>R4頃〜（終期不明）</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="n"/>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K5" s="16" t="inlineStr">
+        <is>
+          <t>https://www.city.miyakonojo.miyazaki.jp/soshiki/78/63199.html</t>
+        </is>
+      </c>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>第2次都城市環境基本計画</t>
+        </is>
+      </c>
+      <c r="M5" s="13" t="inlineStr">
+        <is>
+          <t>R5〜R14</t>
+        </is>
+      </c>
+      <c r="N5" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="O5" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="P5" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="Q5" s="16" t="inlineStr">
+        <is>
+          <t>https://www.city.miyakonojo.miyazaki.jp/uploaded/attachment/26663.pdf</t>
+        </is>
+      </c>
+      <c r="R5" s="13" t="inlineStr">
+        <is>
+          <t>交通：担当は総合政策課。前計画の網形成計画はH29〜R3（https://www.city.miyakonojo.miyazaki.jp/soshiki/78/3994.html ）。後継の地域公共交通計画ページあり、R6.10（山之口地区デマンドタクシー見直し）・R8.4（実施主体変更）に変更。期間は検索で確認できず（網形成計画の後継としてR4開始なら5年でR8終期の可能性＝推測、要確認）。次期計画の策定支援業務プロポ等は検索で未確認。環境：2023年4月策定、R5〜R14の10年、カーボンニュートラル推進計画と一体。R6年度実績報告R8.2公表。ゼロカーボン宣言済（https://www.city.miyakonojo.miyazaki.jp/soshiki/9/54776.html ）。</t>
+        </is>
+      </c>
+      <c r="S5" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T5" s="13" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="108" customHeight="1">
+      <c r="A6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>延岡市</t>
+        </is>
+      </c>
+      <c r="C6" s="14">
+        <f>IF(OR(D6="◎",E6="◎"),"◎ 営業",IF(OR(D6="△",E6="△"),"△ 着手済・要確認",IF(OR(D6="？",E6="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D6" s="15">
+        <f>IF(J6="計画なし","－",IF(J6="策定済","✕",IF(H6="","？",IF(AND(H6&gt;=TGT_MIN,H6&lt;=TGT_MAX),IF(J6="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E6" s="15">
+        <f>IF(P6="計画なし","－",IF(P6="策定済","✕",IF(N6="","？",IF(AND(N6&gt;=TGT_MIN,N6&lt;=TGT_MAX),IF(P6="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>延岡市地域公共交通計画（R7.12変更版）</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>R6〜R11</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="inlineStr">
+        <is>
+          <t>https://www.city.nobeoka.miyazaki.jp/soshiki/4/33676.html</t>
+        </is>
+      </c>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>第3次延岡市環境基本計画（後期計画 R8〜R12）</t>
+        </is>
+      </c>
+      <c r="M6" s="13" t="inlineStr">
+        <is>
+          <t>R3〜R12（後期R8〜R12）</t>
+        </is>
+      </c>
+      <c r="N6" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="O6" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="P6" s="15" t="inlineStr">
+        <is>
+          <t>策定済</t>
+        </is>
+      </c>
+      <c r="Q6" s="16" t="inlineStr">
+        <is>
+          <t>https://www.city.nobeoka.miyazaki.jp/soshiki/24/33838.html</t>
+        </is>
+      </c>
+      <c r="R6" s="13" t="inlineStr">
+        <is>
+          <t>交通：R6.3.27策定、当初R6〜R10を利便増進実施計画（R7〜R11、https://www.city.nobeoka.miyazaki.jp/uploaded/attachment/24594.pdf ）に合わせR11まで延長。R7.2・R7.12改定（北浦町乗合タクシー2路線廃止）。利便増進実施計画はR8.4一部変更。環境：第3次計画（R3〜R12）、後期計画（R8〜R12）をR7年度策定、パブコメ結果R8.2.24公表。</t>
+        </is>
+      </c>
+      <c r="S6" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T6" s="13" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="264" customHeight="1">
+      <c r="A7" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>日南市</t>
+        </is>
+      </c>
+      <c r="C7" s="14">
+        <f>IF(OR(D7="◎",E7="◎"),"◎ 営業",IF(OR(D7="△",E7="△"),"△ 着手済・要確認",IF(OR(D7="？",E7="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D7" s="15">
+        <f>IF(J7="計画なし","－",IF(J7="策定済","✕",IF(H7="","？",IF(AND(H7&gt;=TGT_MIN,H7&lt;=TGT_MAX),IF(J7="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E7" s="15">
+        <f>IF(P7="計画なし","－",IF(P7="策定済","✕",IF(N7="","？",IF(AND(N7&gt;=TGT_MIN,N7&lt;=TGT_MAX),IF(P7="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>日南市地域公共交通網形成計画（H31.3策定）</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>R1頃〜（終期不明）</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K7" s="16" t="inlineStr">
+        <is>
+          <t>https://www.city.nichinan.lg.jp/soshikikarasagasu/miraisoseika/2/2/1125.html</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>第二次日南市環境基本計画</t>
+        </is>
+      </c>
+      <c r="M7" s="13" t="inlineStr">
+        <is>
+          <t>R4頃〜（終期不明、10年ならR13＝推定）</t>
+        </is>
+      </c>
+      <c r="N7" s="15" t="n"/>
+      <c r="O7" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="P7" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="Q7" s="13" t="n"/>
+      <c r="R7" s="13" t="inlineStr">
+        <is>
+          <t>交通：網形成計画（H31.3、本文PDF https://www.city.nichinan.lg.jp/material/files/group/8/cdb416195e8da0535facafa68c59737a.pdf ）が最新として掲載。期間・後継の地域公共交通計画は検索で確認できず（期間満了・延長の可能性、要確認）。担当：未来創生課（0987-31-1128）。JR日南線活用検討会あり。環境：第一次計画H23〜H32（R2）の後継として第二次計画を策定、R4.3.2に同計画策定に伴いゼロカーボンシティ宣言（https://www.city.nichinan.lg.jp/soshikikarasagasu/chiikijichika/2/2/1/1108.html ）。計画書URL・期間は検索で確認できず（https://www.city.nichinan.lg.jp/material/files/group/34/33098224.pdf が環境基本計画の可能性あるが文字化けで未確認）。 【追加検索 2026-10-21】第一次環境基本計画はH23〜H32（R2）の10年（https://www.city.nichinan.lg.jp/material/files/group/34/33098224.pdf の要約より）。第二次計画の期間は依然未確認。</t>
+        </is>
+      </c>
+      <c r="S7" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T7" s="19" t="inlineStr">
+        <is>
+          <t>掲載／期間満了</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="186" customHeight="1">
+      <c r="A8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>小林市</t>
+        </is>
+      </c>
+      <c r="C8" s="14">
+        <f>IF(OR(D8="◎",E8="◎"),"◎ 営業",IF(OR(D8="△",E8="△"),"△ 着手済・要確認",IF(OR(D8="？",E8="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D8" s="15">
+        <f>IF(J8="計画なし","－",IF(J8="策定済","✕",IF(H8="","？",IF(AND(H8&gt;=TGT_MIN,H8&lt;=TGT_MAX),IF(J8="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E8" s="15">
+        <f>IF(P8="計画なし","－",IF(P8="策定済","✕",IF(N8="","？",IF(AND(N8&gt;=TGT_MIN,N8&lt;=TGT_MAX),IF(P8="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>小林市地域公共交通計画（R6.5改正）</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>R4〜R8</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>着手済</t>
+        </is>
+      </c>
+      <c r="K8" s="16" t="inlineStr">
+        <is>
+          <t>https://www.city.kobayashi.lg.jp/material/files/group/6/20240531koutuukeikaku.pdf</t>
+        </is>
+      </c>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>小林市環境基本計画</t>
+        </is>
+      </c>
+      <c r="M8" s="13" t="inlineStr">
+        <is>
+          <t>R5〜R14</t>
+        </is>
+      </c>
+      <c r="N8" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="O8" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="P8" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="Q8" s="16" t="inlineStr">
+        <is>
+          <t>https://www.city.kobayashi.lg.jp/material/files/group/14/R5-R14kobayasisikankyoukihonkeikaku.pdf</t>
+        </is>
+      </c>
+      <c r="R8" s="13" t="inlineStr">
+        <is>
+          <t>交通：計画ページ https://www.city.kobayashi.lg.jp/soshikikarasagasu/sogoseisakubukikakuseisakuka/oshirase/2290.html 。担当：総合政策部企画政策課。次期計画：『小林市地域公共交通計画策定支援業務委託』公募型プロポーザルをR8.5開始（契約R8.7上旬予定、履行期限R9.3.19）https://www.city.kobayashi.lg.jp/soshikikarasagasu/sogoseisakubukikakuseisakuka/oshirase/11204.html →着手済（受託者は検索で未確認）。西諸県（小林市・えびの市・高原町）の共同交通計画は検索で確認できず、小林市は単独計画。環境：R5.3策定R5〜R14、R9年度目安に中間見直し予定、区域施策編を兼ねる、ゼロカーボンシティこばやし。</t>
+        </is>
+      </c>
+      <c r="S8" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T8" s="13" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="329" customHeight="1">
+      <c r="A9" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>日向市</t>
+        </is>
+      </c>
+      <c r="C9" s="14">
+        <f>IF(OR(D9="◎",E9="◎"),"◎ 営業",IF(OR(D9="△",E9="△"),"△ 着手済・要確認",IF(OR(D9="？",E9="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D9" s="15">
+        <f>IF(J9="計画なし","－",IF(J9="策定済","✕",IF(H9="","？",IF(AND(H9&gt;=TGT_MIN,H9&lt;=TGT_MAX),IF(J9="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E9" s="15">
+        <f>IF(P9="計画なし","－",IF(P9="策定済","✕",IF(N9="","？",IF(AND(N9&gt;=TGT_MIN,N9&lt;=TGT_MAX),IF(P9="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>日向市地域公共交通計画（R6.1改定）</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>R5〜R9</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J9" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K9" s="16" t="inlineStr">
+        <is>
+          <t>https://www.hyugacity.jp/sp/tempimg/20240124090032.pdf</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>第3次日向市環境基本計画</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="inlineStr">
+        <is>
+          <t>R7〜（終期不明）</t>
+        </is>
+      </c>
+      <c r="N9" s="15" t="n"/>
+      <c r="O9" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="P9" s="15" t="inlineStr">
+        <is>
+          <t>策定済</t>
+        </is>
+      </c>
+      <c r="Q9" s="16" t="inlineStr">
+        <is>
+          <t>https://www.hyugacity.jp/sp/display.php?slist=0012</t>
+        </is>
+      </c>
+      <c r="R9" s="13" t="inlineStr">
+        <is>
+          <t>交通：R5.3.16策定。作成業務仕様書に計画期間R5〜R9と明記（https://www.hyugacity.jp/sp/tempimg/20220623085655.pdf ）。ただしR8.6.2の計画別紙（https://www.hyugacity.jp/sp/tempimg/20260630130356.pdf ）に『計画期間最終年度（令和10年）』との記述あり→R9年度末＝R10.3の意味か延長かは未確認。前回策定業務：公募型プロポーザル（R4.6）でランドブレイン株式会社が特定（461/500点、履行R5.3.17まで、金額不明）https://www.hyugacity.jp/sp/display.php?cont=220622140143 。担当：建設部都市政策課（総務・交通係）。関連：AIオンデマンドバス『のるーと日向』実証運行（R7.10計画）、東郷地域公共ライドシェアR8.4本格運行。R8.6.26に令和8年度日向市地域公共交通会議掲載、次期計画策定（プロポ等）は検索で未確認＝R9終期の有望案件。日向圏域（日向市・門川町・美郷町・諸塚村・椎葉村）の共同地域公共交通計画は確認できず（定住自立圏で過去に再編実施計画の事例あり、九州運輸局資料 https://wwwtb.mlit.go.jp/kyushu/content/000246814.pdf ＝要確認）。第4次日向圏域定住自立圏共生ビジョン（R7〜R11）https://www.hyugacity.jp/sp/tempimg/20260414083901.pdf 。環境：第3次計画をR7.3策定（期間は検索で未確認、e_urlは環境政策課ページ）。ごみ処理基本計画R8〜R17。</t>
+        </is>
+      </c>
+      <c r="S9" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T9" s="13" t="inlineStr">
+        <is>
+          <t>掲載（広域：日向・東臼杵）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="264" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>串間市</t>
+        </is>
+      </c>
+      <c r="C10" s="14">
+        <f>IF(OR(D10="◎",E10="◎"),"◎ 営業",IF(OR(D10="△",E10="△"),"△ 着手済・要確認",IF(OR(D10="？",E10="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D10" s="15">
+        <f>IF(J10="計画なし","－",IF(J10="策定済","✕",IF(H10="","？",IF(AND(H10&gt;=TGT_MIN,H10&lt;=TGT_MAX),IF(J10="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="15">
+        <f>IF(P10="計画なし","－",IF(P10="策定済","✕",IF(N10="","？",IF(AND(N10&gt;=TGT_MIN,N10&lt;=TGT_MAX),IF(P10="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>串間市地域公共交通計画</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>R6.4〜R11.9</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>推定</t>
+        </is>
+      </c>
+      <c r="J10" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
+          <t>https://www.city.kushima.lg.jp/main/city/tiitki/cat3051/post-658.html</t>
+        </is>
+      </c>
+      <c r="L10" s="13" t="n"/>
+      <c r="M10" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="N10" s="15" t="n"/>
+      <c r="O10" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="P10" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="Q10" s="13" t="n"/>
+      <c r="R10" s="13" t="inlineStr">
+        <is>
+          <t>交通：市公式の策定告知でR6.4〜R11.9（要約1回のみのため推定）。前計画は網形成計画＋利便増進実施計画（R3〜R5）https://www.city.kushima.lg.jp/main/city/upload/3dd9a5128660c7ce73e6f69ec07ed9568cdd6fdf.pdf 。環境：環境基本計画は検索で見つからず（計画なしの可能性、未確定）。代替として串間市地球温暖化対策実行計画（区域施策編・事務事業編、R5〜R12、R5.3）https://www.city.kushima.lg.jp/main/info/upload/%E3%80%90%E6%9C%AC%E7%B7%A8%E3%80%91%E4%B8%B2%E9%96%93%E5%B8%82%E5%9C%B0%E7%90%83%E6%B8%A9%E6%9A%96%E5%8C%96%E5%AF%BE%E7%AD%96%E5%AE%9F%E8%A1%8C%E8%A8%88%E7%94%BB%EF%BC%88%E5%8C%BA%E5%9F%9F%E6%96%BD%E7%AD%96%E7%B7%A8%E3%83%BB%E4%BA%8B%E5%8B%99%E4%BA%8B%E6%A5%AD%E7%B7%A8%EF%BC%89.pdf 。R2.12ゼロカーボンシティ宣言。</t>
+        </is>
+      </c>
+      <c r="S10" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T10" s="13" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="225" customHeight="1">
+      <c r="A11" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>西都市</t>
+        </is>
+      </c>
+      <c r="C11" s="14">
+        <f>IF(OR(D11="◎",E11="◎"),"◎ 営業",IF(OR(D11="△",E11="△"),"△ 着手済・要確認",IF(OR(D11="？",E11="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D11" s="15">
+        <f>IF(J11="計画なし","－",IF(J11="策定済","✕",IF(H11="","？",IF(AND(H11&gt;=TGT_MIN,H11&lt;=TGT_MAX),IF(J11="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="15">
+        <f>IF(P11="計画なし","－",IF(P11="策定済","✕",IF(N11="","？",IF(AND(N11&gt;=TGT_MIN,N11&lt;=TGT_MAX),IF(P11="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>西都市地域公共交通計画（R7.3改訂）</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>R5〜R11</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J11" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>https://www.city.saito.lg.jp/kurashi/kokyokotsu/post_1473.html</t>
+        </is>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>第三次西都市環境基本計画</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="inlineStr">
+        <is>
+          <t>R4〜R10</t>
+        </is>
+      </c>
+      <c r="N11" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="O11" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="P11" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="Q11" s="16" t="inlineStr">
+        <is>
+          <t>https://www.city.saito.lg.jp/%E6%A6%82%E8%A6%81%E7%89%88.pdf</t>
+        </is>
+      </c>
+      <c r="R11" s="13" t="inlineStr">
+        <is>
+          <t>交通：R5〜R11の7年計画、R7.3に変更（変更案パブコメR7.2.27〜3.26、意見なし https://www.city.saito.lg.jp/shiseigyosei/public_comment/post_1438.html ）。担当は総合政策課。デマンド型乗合タクシー・コミュニティバス運行、西都バスセンターを交通拠点化。環境：R4〜R10（第五次総合計画と整合、R7中間見直し予定）。素案PDF https://www.city.saito.lg.jp/%E7%AC%AC%E4%B8%89%E6%AC%A1%E8%A5%BF%E9%83%BD%E5%B8%82%E7%92%B0%E5%A2%83%E5%9F%BA%E6%9C%AC%E8%A8%88%E7%94%BB%EF%BC%88%E7%B4%A0%E6%A1%88%EF%BC%89.pdf 。担当は生活環境課。地球温暖化対策実行計画（区域施策編）2025.3策定 https://www.city.saito.lg.jp/b55189322065669ea41edbf8443fde72.pdf 。終期R9の計画なし。</t>
+        </is>
+      </c>
+      <c r="S11" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T11" s="13" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="277" customHeight="1">
+      <c r="A12" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>えびの市</t>
+        </is>
+      </c>
+      <c r="C12" s="14">
+        <f>IF(OR(D12="◎",E12="◎"),"◎ 営業",IF(OR(D12="△",E12="△"),"△ 着手済・要確認",IF(OR(D12="？",E12="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D12" s="15">
+        <f>IF(J12="計画なし","－",IF(J12="策定済","✕",IF(H12="","？",IF(AND(H12&gt;=TGT_MIN,H12&lt;=TGT_MAX),IF(J12="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="15">
+        <f>IF(P12="計画なし","－",IF(P12="策定済","✕",IF(N12="","？",IF(AND(N12&gt;=TGT_MIN,N12&lt;=TGT_MAX),IF(P12="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>えびの市地域公共交通網形成計画（H27.3策定、期間満了）</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>H27〜H29（期間満了・後継計画未確認）</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="n"/>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
+        <is>
+          <t>https://www.city.ebino.lg.jp/soshiki/kikaku/6/866.html</t>
+        </is>
+      </c>
+      <c r="L12" s="13" t="inlineStr">
+        <is>
+          <t>第二次えびの市環境基本計画（R5.3見直し版）</t>
+        </is>
+      </c>
+      <c r="M12" s="13" t="inlineStr">
+        <is>
+          <t>H30〜R9</t>
+        </is>
+      </c>
+      <c r="N12" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="O12" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="P12" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="Q12" s="16" t="inlineStr">
+        <is>
+          <t>https://www.city.ebino.lg.jp/soshiki/shiminkankyo/2/1343.html</t>
+        </is>
+      </c>
+      <c r="R12" s="13" t="inlineStr">
+        <is>
+          <t>交通：市単独の網形成計画（H27〜H29、担当 企画課）は期間満了。令和の地域公共交通計画や小林市・高原町との西諸県共同計画は検索で確認できず（宮崎県地域公共交通計画でカバーの可能性）。はまゆう号R3.3休止、R6.9から鹿児島空港行つばめエアポートライナー運行。概要版PDF https://www.city.ebino.lg.jp/material/files/group/3/120402133407201504101608451f.pdf 。環境：H30〜R9の10年計画（ページタイトル「平成30年度～平成39年度」）、R5.3中間見直し版 https://www.city.ebino.lg.jp/material/files/group/9/daiinizikankyokihonkeikakuminaosiban.pdf 。担当 市民環境課。R9終期のため第三次計画はR8〜R9策定見込みだが、プロポーザル・審議会等の着手は検索で未確認（有望）。関連：えびの市・高原町の循環型社会形成推進地域計画（R6〜R10）、えびの市地域再生可能エネルギービジョンあり。 広域：宮崎県地域公共交通計画（R6〜R10、広域的バス・地域間幹線バス対象）https://www.pref.miyazaki.lg.jp/sogokotsu/shigoto/butsuryu/20240221101503.html が広域バス部分をカバー（市単独計画ではない）。</t>
+        </is>
+      </c>
+      <c r="S12" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T12" s="19" t="inlineStr">
+        <is>
+          <t>掲載／期間満了</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="342" customHeight="1">
+      <c r="A13" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>三股町</t>
+        </is>
+      </c>
+      <c r="C13" s="14">
+        <f>IF(OR(D13="◎",E13="◎"),"◎ 営業",IF(OR(D13="△",E13="△"),"△ 着手済・要確認",IF(OR(D13="？",E13="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D13" s="15">
+        <f>IF(J13="計画なし","－",IF(J13="策定済","✕",IF(H13="","？",IF(AND(H13&gt;=TGT_MIN,H13&lt;=TGT_MAX),IF(J13="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="15">
+        <f>IF(P13="計画なし","－",IF(P13="策定済","✕",IF(N13="","？",IF(AND(N13&gt;=TGT_MIN,N13&lt;=TGT_MAX),IF(P13="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>三股町地域公共交通計画（R5.3策定、R6.6一部改定）</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>R5〜R9</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>推定</t>
+        </is>
+      </c>
+      <c r="J13" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K13" s="16" t="inlineStr">
+        <is>
+          <t>https://www.town.mimata.lg.jp/upload/file/01soumu/03gyosei/%E5%85%AC%E5%85%B1%E4%BA%A4%E9%80%9A%E8%A8%88%E7%94%BB/%E3%80%90%E5%AE%8C%E6%88%90%E7%89%88%E3%80%91%E2%98%85%E4%B8%89%E8%82%A1%E7%94%BA%E5%9C%B0%E5%9F%9F%E5%85%AC%E5%85%B1%E4%BA%A4%E9%80%9A%E8%A8%88%E7%94%BB.pdf</t>
+        </is>
+      </c>
+      <c r="L13" s="13" t="n"/>
+      <c r="M13" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="N13" s="15" t="n"/>
+      <c r="O13" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="P13" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="Q13" s="13" t="n"/>
+      <c r="R13" s="13" t="inlineStr">
+        <is>
+          <t>交通：R5.3策定（R4年度策定）、R6.6.3地域公共交通会議で一部改定承認。策定ページ https://www.town.mimata.lg.jp/contents/1699.html 。計画期間は町サイト限定検索の要約で「令和5年度〜令和9年度の5年間、対象区域は町全域」（1回のみのため推定、R9終期・有望）。改定ページ https://www.town.mimata.lg.jp/contents/1909.html 。担当は総務課（行政係、計画PDFの格納パス01soumu/03gyoseiより）。次期計画の策定業務・協議会審議は検索で見つからず（未確認）。前回の策定受託者・金額は不明。コミュニティバス「くいまーる」をR6.4再編（三股駅結節）、R8.1〜2にオンデマンドバス無料実証実験 https://www.town.mimata.lg.jp/contents/2100.html 、バス予報導入。WebFetchは不可。環境：三股町環境基本条例（第8条に計画規定）はあるが、環境基本計画本体は検索で見つからず（計画なしと判断、要確認）。代替：地球温暖化対策実行計画（区域施策編）、重点対策加速化事業計画（R6〜R10）https://www.town.mimata.lg.jp/upload/file/08kansui/01kankyou/%E5%9C%B0%E7%90%83%E6%B8%A9%E6%9A%96%E5%8C%96/%E4%BA%8B%E6%A5%AD%E8%A8%88%E7%94%BB%EF%BC%88%E6%9C%AC%E4%BD%93%EF%BC%89.pdf 、第2次事務事業編（R4〜R12）https://www.town.mimata.lg.jp/contents/828.html 。担当 環境水道課。</t>
+        </is>
+      </c>
+      <c r="S13" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T13" s="13" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="225" customHeight="1">
+      <c r="A14" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>高原町</t>
+        </is>
+      </c>
+      <c r="C14" s="14">
+        <f>IF(OR(D14="◎",E14="◎"),"◎ 営業",IF(OR(D14="△",E14="△"),"△ 着手済・要確認",IF(OR(D14="？",E14="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D14" s="15">
+        <f>IF(J14="計画なし","－",IF(J14="策定済","✕",IF(H14="","？",IF(AND(H14&gt;=TGT_MIN,H14&lt;=TGT_MAX),IF(J14="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E14" s="15">
+        <f>IF(P14="計画なし","－",IF(P14="策定済","✕",IF(N14="","？",IF(AND(N14&gt;=TGT_MIN,N14&lt;=TGT_MAX),IF(P14="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>高原町地域公共交通計画（R7.4改定）</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>R6〜R10</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J14" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K14" s="16" t="inlineStr">
+        <is>
+          <t>https://www.town.takaharu.lg.jp/uploaded/life/303843_13457119_misc.pdf</t>
+        </is>
+      </c>
+      <c r="L14" s="13" t="n"/>
+      <c r="M14" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="N14" s="15" t="n"/>
+      <c r="O14" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="P14" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="Q14" s="13" t="n"/>
+      <c r="R14" s="13" t="inlineStr">
+        <is>
+          <t>宮崎県西諸県郡高原町（神石高原町・久万高原町とは別）。交通：R6.3策定、R6.4〜R11.3の5か年。R7.4改定で乗合タクシーを町内全域デマンド化、小林祓川線を小林駅〜並木区間に短縮。改定ページ https://www.town.takaharu.lg.jp/soshiki/18/238554.html 。R8.7に「バス小林並木線と乗合タクシーの変更計画」パブコメ（小林並木線をR9.3末廃止予定、乗合タクシーを小林市内まで延伸）https://www.town.takaharu.lg.jp/soshiki/31/305198.html （計画の一部変更であり次期計画策定ではない）。小林市・えびの市との共同計画は確認できず（町単独計画）。環境：環境基本計画・温暖化対策実行計画とも町サイト検索で見つからず。えびの市と共同の循環型社会形成推進地域計画（R6〜R10）はあり https://www.env.go.jp/recycle/waste/3r_network/5_region/project_list/45_miyazaki/10_ebino_r6.pdf 。</t>
+        </is>
+      </c>
+      <c r="S14" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T14" s="13" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="251" customHeight="1">
+      <c r="A15" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>国富町</t>
+        </is>
+      </c>
+      <c r="C15" s="14">
+        <f>IF(OR(D15="◎",E15="◎"),"◎ 営業",IF(OR(D15="△",E15="△"),"△ 着手済・要確認",IF(OR(D15="？",E15="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D15" s="15">
+        <f>IF(J15="計画なし","－",IF(J15="策定済","✕",IF(H15="","？",IF(AND(H15&gt;=TGT_MIN,H15&lt;=TGT_MAX),IF(J15="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E15" s="15">
+        <f>IF(P15="計画なし","－",IF(P15="策定済","✕",IF(N15="","？",IF(AND(N15&gt;=TGT_MIN,N15&lt;=TGT_MAX),IF(P15="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>国富町地域公共交通網形成計画</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="n"/>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="J15" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n"/>
+      <c r="L15" s="13" t="n"/>
+      <c r="M15" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="N15" s="15" t="n"/>
+      <c r="O15" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="P15" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="Q15" s="13" t="n"/>
+      <c r="R15" s="13" t="inlineStr">
+        <is>
+          <t>交通：立地適正化計画 http://www.town.kunitomi.miyazaki.jp/main/administration/1aea1a1faa8ec122ae91ac27aa78c6c3.pdf に関連計画として「国富町地域公共交通網形成計画」の記載があるが、本文・期間・URLは検索で確認できず。地域公共交通会議設置あり https://www.town.kunitomi.miyazaki.jp/main/administration/page000891.html 。R2.9末に宮崎交通 法ケ岳線・馬渡線廃止→町コミュニティバスで代替、デマンド型乗合タクシー「よつば号」運行。担当 企画政策課。環境：環境基本計画は見つからず。代替：国富町地球温暖化対策実行計画（区域施策編）R7.1策定、R7〜R12 http://www.town.kunitomi.miyazaki.jp/main/living/e89a1ade96220e0eba3a859198aef55e.pdf 。R7.2.28ゼロカーボンシティ宣言 https://www.town.kunitomi.miyazaki.jp/main/living/trash/page002177.html 。事務事業編R2.5策定。</t>
+        </is>
+      </c>
+      <c r="S15" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T15" s="19" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="277" customHeight="1">
+      <c r="A16" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>綾町</t>
+        </is>
+      </c>
+      <c r="C16" s="14">
+        <f>IF(OR(D16="◎",E16="◎"),"◎ 営業",IF(OR(D16="△",E16="△"),"△ 着手済・要確認",IF(OR(D16="？",E16="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D16" s="15">
+        <f>IF(J16="計画なし","－",IF(J16="策定済","✕",IF(H16="","？",IF(AND(H16&gt;=TGT_MIN,H16&lt;=TGT_MAX),IF(J16="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="15">
+        <f>IF(P16="計画なし","－",IF(P16="策定済","✕",IF(N16="","？",IF(AND(N16&gt;=TGT_MIN,N16&lt;=TGT_MAX),IF(P16="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="n"/>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="J16" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n"/>
+      <c r="L16" s="13" t="n"/>
+      <c r="M16" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="N16" s="15" t="n"/>
+      <c r="O16" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="P16" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="Q16" s="13" t="n"/>
+      <c r="R16" s="13" t="inlineStr">
+        <is>
+          <t>宮崎県東諸県郡綾町（香川県綾川町とは別）。交通：町単独の地域公共交通計画は検索で確認できず（計画なしと判断、要確認）。広域バスは宮崎県地域公共交通計画（R6〜R10、広域的バス・地域間幹線バス対象）https://www.pref.miyazaki.lg.jp/sogokotsu/shigoto/butsuryu/20240221101503.html。R7年度実証運行→R8.4からオンデマンド交通「ぐるっとあや」本格運行（担当 福祉保健課）https://www.town.aya.miyazaki.jp/soshiki/hukusihokenka/9031.html 、高齢者向け「おでかけバスカ」（宮崎交通路線バス）。R8年度「日本のひなた宮崎国スポ綾町輸送計画等策定業務委託」入札公告あり https://www.town.aya.miyazaki.jp/site/kokusupo2027/10906.html （国スポ輸送計画で公共交通計画ではない）。環境：環境基本計画・温暖化対策実行計画（区域施策編）・ゼロカーボン宣言とも検索で見つからず。関連：ユネスコエコパーク推進室、オーガニックビレッジ宣言、綾町バイオガスプラント建設計画（R7 FS、R8基本設計予定）https://www.town.aya.miyazaki.jp/soshiki/nourinsinkou/10881.html 。</t>
+        </is>
+      </c>
+      <c r="S16" s="20" t="inlineStr">
+        <is>
+          <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T16" s="13" t="inlineStr">
+        <is>
+          <t>未掲載</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="316" customHeight="1">
+      <c r="A17" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>高鍋町</t>
+        </is>
+      </c>
+      <c r="C17" s="14">
+        <f>IF(OR(D17="◎",E17="◎"),"◎ 営業",IF(OR(D17="△",E17="△"),"△ 着手済・要確認",IF(OR(D17="？",E17="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D17" s="15">
+        <f>IF(J17="計画なし","－",IF(J17="策定済","✕",IF(H17="","？",IF(AND(H17&gt;=TGT_MIN,H17&lt;=TGT_MAX),IF(J17="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="15">
+        <f>IF(P17="計画なし","－",IF(P17="策定済","✕",IF(N17="","？",IF(AND(N17&gt;=TGT_MIN,N17&lt;=TGT_MAX),IF(P17="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="J17" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n"/>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>第2次高鍋町環境基本計画</t>
+        </is>
+      </c>
+      <c r="M17" s="13" t="inlineStr">
+        <is>
+          <t>R8〜R17</t>
+        </is>
+      </c>
+      <c r="N17" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="O17" s="15" t="inlineStr">
+        <is>
+          <t>推定</t>
+        </is>
+      </c>
+      <c r="P17" s="15" t="inlineStr">
+        <is>
+          <t>着手済</t>
+        </is>
+      </c>
+      <c r="Q17" s="13" t="n"/>
+      <c r="R17" s="13" t="inlineStr">
+        <is>
+          <t>交通：町単独の地域公共交通計画は検索で確認できず（計画なしと判断、要確認）。広域：宮崎県地域公共交通計画（R6〜R10、広域的バス・地域間幹線バス対象）https://www.pref.miyazaki.lg.jp/sogokotsu/shigoto/butsuryu/20240221101503.html。西都市・新富町と広域コミュニティバス「三納代線」「一丁田線」運行（R7.10から三和交通に事業者変更）https://www.town.takanabe.lg.jp/soshiki/chiikiseisaku/1/1/4613.html 、町デマンド交通あり（R8.10.9乗降所変更）https://www.town.takanabe.lg.jp/soshiki/chiikiseisaku/1/1/3730.html 。担当 地域政策課。環境：第7次高鍋町総合計画前期基本計画（R8.3）の関連計画表に「第2次高鍋町環境基本計画」「高鍋町地球温暖化対策実行計画」「気候変動適応計画」がいずれもR8〜R17として記載 https://www.town.takanabe.lg.jp/material/files/group/4/03_28-33.pdf 。計画書本体・策定済か否かは検索で確認できず（R8年度策定作業中の可能性→着手済扱い、要確認）。第1次計画の期間も未確認。SDGs未来都市計画（2025〜2027）https://www.town.takanabe.lg.jp/material/files/group/4/miraitoshikeikaku.pdf 。</t>
+        </is>
+      </c>
+      <c r="S17" s="20" t="inlineStr">
+        <is>
+          <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T17" s="13" t="inlineStr">
+        <is>
+          <t>未掲載</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="108" customHeight="1">
+      <c r="A18" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>新富町</t>
+        </is>
+      </c>
+      <c r="C18" s="14">
+        <f>IF(OR(D18="◎",E18="◎"),"◎ 営業",IF(OR(D18="△",E18="△"),"△ 着手済・要確認",IF(OR(D18="？",E18="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D18" s="15">
+        <f>IF(J18="計画なし","－",IF(J18="策定済","✕",IF(H18="","？",IF(AND(H18&gt;=TGT_MIN,H18&lt;=TGT_MAX),IF(J18="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="15">
+        <f>IF(P18="計画なし","－",IF(P18="策定済","✕",IF(N18="","？",IF(AND(N18&gt;=TGT_MIN,N18&lt;=TGT_MAX),IF(P18="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>新富町地域公共交通計画</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>R6〜（終期不明）</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="n"/>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K18" s="16" t="inlineStr">
+        <is>
+          <t>https://www.town.shintomi.lg.jp/item/20459.htm</t>
+        </is>
+      </c>
+      <c r="L18" s="13" t="n"/>
+      <c r="M18" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="N18" s="15" t="n"/>
+      <c r="O18" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="P18" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="Q18" s="13" t="n"/>
+      <c r="R18" s="13" t="inlineStr">
+        <is>
+          <t>交通：R6.3策定（新富町地域公共交通活性化協議会と連携、担当 総合政策課）。期間は検索で確認できず（5年なら R6〜R10 だが未確認）。コミュニティバス運行、R6.4県内初のEVバス導入。県の宮崎県地域公共交通計画（R6〜R10）も広域でカバー。環境：環境基本計画・区域施策編は検索で見つからず。代替：新富町ゼロカーボンシティ宣言（R5.12.15） https://www.town.shintomi.lg.jp/item/20470.htm 。</t>
+        </is>
+      </c>
+      <c r="S18" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T18" s="13" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="66" customHeight="1">
+      <c r="A19" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>西米良村</t>
+        </is>
+      </c>
+      <c r="C19" s="14">
+        <f>IF(OR(D19="◎",E19="◎"),"◎ 営業",IF(OR(D19="△",E19="△"),"△ 着手済・要確認",IF(OR(D19="？",E19="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D19" s="15">
+        <f>IF(J19="計画なし","－",IF(J19="策定済","✕",IF(H19="","？",IF(AND(H19&gt;=TGT_MIN,H19&lt;=TGT_MAX),IF(J19="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="15">
+        <f>IF(P19="計画なし","－",IF(P19="策定済","✕",IF(N19="","？",IF(AND(N19&gt;=TGT_MIN,N19&lt;=TGT_MAX),IF(P19="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="n"/>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="J19" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n"/>
+      <c r="L19" s="13" t="n"/>
+      <c r="M19" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="N19" s="15" t="n"/>
+      <c r="O19" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="P19" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="Q19" s="13" t="n"/>
+      <c r="R19" s="13" t="inlineStr">
+        <is>
+          <t>交通：村単独の地域公共交通計画は検索で見つからず（村営バス・デマンド対応あり）。県の宮崎県地域公共交通計画（R6〜R10）が広域カバー。環境：環境基本計画・区域施策編とも見つからず。</t>
+        </is>
+      </c>
+      <c r="S19" s="20" t="inlineStr">
+        <is>
+          <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T19" s="13" t="inlineStr">
+        <is>
+          <t>未掲載</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="69" customHeight="1">
+      <c r="A20" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>木城町</t>
+        </is>
+      </c>
+      <c r="C20" s="14">
+        <f>IF(OR(D20="◎",E20="◎"),"◎ 営業",IF(OR(D20="△",E20="△"),"△ 着手済・要確認",IF(OR(D20="？",E20="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D20" s="15">
+        <f>IF(J20="計画なし","－",IF(J20="策定済","✕",IF(H20="","？",IF(AND(H20&gt;=TGT_MIN,H20&lt;=TGT_MAX),IF(J20="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E20" s="15">
+        <f>IF(P20="計画なし","－",IF(P20="策定済","✕",IF(N20="","？",IF(AND(N20&gt;=TGT_MIN,N20&lt;=TGT_MAX),IF(P20="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>木城町地域公共交通計画</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>R6〜R10</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K20" s="16" t="inlineStr">
+        <is>
+          <t>https://www.town.kijo.lg.jp/sosikikarasagasu/tiikiseisakuka/7/1/2433.html</t>
+        </is>
+      </c>
+      <c r="L20" s="13" t="n"/>
+      <c r="M20" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="N20" s="15" t="n"/>
+      <c r="O20" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="P20" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="Q20" s="13" t="n"/>
+      <c r="R20" s="13" t="inlineStr">
+        <is>
+          <t>交通：対象期間R6〜R10（担当 地域政策課）。環境：環境基本計画は見つからず。代替として木城町カーボンニュートラル計画（R5.2） https://www.town.kijo.lg.jp/material/files/group/8/carbonneutralkeikaku.pdf 。</t>
+        </is>
+      </c>
+      <c r="S20" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T20" s="13" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="160" customHeight="1">
+      <c r="A21" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>川南町</t>
+        </is>
+      </c>
+      <c r="C21" s="14">
+        <f>IF(OR(D21="◎",E21="◎"),"◎ 営業",IF(OR(D21="△",E21="△"),"△ 着手済・要確認",IF(OR(D21="？",E21="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D21" s="15">
+        <f>IF(J21="計画なし","－",IF(J21="策定済","✕",IF(H21="","？",IF(AND(H21&gt;=TGT_MIN,H21&lt;=TGT_MAX),IF(J21="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E21" s="15">
+        <f>IF(P21="計画なし","－",IF(P21="策定済","✕",IF(N21="","？",IF(AND(N21&gt;=TGT_MIN,N21&lt;=TGT_MAX),IF(P21="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="J21" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n"/>
+      <c r="L21" s="13" t="n"/>
+      <c r="M21" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="N21" s="15" t="n"/>
+      <c r="O21" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="P21" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="Q21" s="13" t="n"/>
+      <c r="R21" s="13" t="inlineStr">
+        <is>
+          <t>交通：町単独の地域公共交通計画は検索で見つからず（トロントロンバス＝定時路線＋オンデマンド、川南町地域公共交通会議あり）。R7.12議会で乗合タクシー導入が議論、R8.10からタクシー撤退を受け町内常駐タクシー体制 https://www.town.kawaminami.miyazaki.jp/soshiki/2/16936.html 。県計画（R6〜R10）が広域カバー。環境：環境基本計画は見つからず。代替として川南町再生可能エネルギー導入計画及び地球温暖化対策実行計画（区域施策編・事務事業編）R6.1、ゼロカーボンシティ宣言済 https://www.town.kawaminami.miyazaki.jp/uploaded/attachment/5648.pdf 。</t>
+        </is>
+      </c>
+      <c r="S21" s="20" t="inlineStr">
+        <is>
+          <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T21" s="13" t="inlineStr">
+        <is>
+          <t>未掲載</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="121" customHeight="1">
+      <c r="A22" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>都農町</t>
+        </is>
+      </c>
+      <c r="C22" s="14">
+        <f>IF(OR(D22="◎",E22="◎"),"◎ 営業",IF(OR(D22="△",E22="△"),"△ 着手済・要確認",IF(OR(D22="？",E22="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D22" s="15">
+        <f>IF(J22="計画なし","－",IF(J22="策定済","✕",IF(H22="","？",IF(AND(H22&gt;=TGT_MIN,H22&lt;=TGT_MAX),IF(J22="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="15">
+        <f>IF(P22="計画なし","－",IF(P22="策定済","✕",IF(N22="","？",IF(AND(N22&gt;=TGT_MIN,N22&lt;=TGT_MAX),IF(P22="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="n"/>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="J22" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n"/>
+      <c r="L22" s="13" t="n"/>
+      <c r="M22" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="N22" s="15" t="n"/>
+      <c r="O22" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="P22" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="Q22" s="13" t="n"/>
+      <c r="R22" s="13" t="inlineStr">
+        <is>
+          <t>交通：町単独の地域公共交通計画は検索で見つからず（町公式サイト内検索でも出ず）。コミュニティバスはR8.4から一部定時路線を除き事前予約制へ移行 https://www.town.tsuno.lg.jp/article?articleId=604ec335889ebd12ec684b26 。県計画（R6〜R10）が広域カバー。第6次長期総合計画がH29〜R8で今年度終期（次期総合計画策定中と推定）。環境：環境基本計画・区域施策編は見つからず（木質バイオマス発電の整備計画あり）。</t>
+        </is>
+      </c>
+      <c r="S22" s="20" t="inlineStr">
+        <is>
+          <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T22" s="13" t="inlineStr">
+        <is>
+          <t>未掲載</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="121" customHeight="1">
+      <c r="A23" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>門川町</t>
+        </is>
+      </c>
+      <c r="C23" s="14">
+        <f>IF(OR(D23="◎",E23="◎"),"◎ 営業",IF(OR(D23="△",E23="△"),"△ 着手済・要確認",IF(OR(D23="？",E23="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D23" s="15">
+        <f>IF(J23="計画なし","－",IF(J23="策定済","✕",IF(H23="","？",IF(AND(H23&gt;=TGT_MIN,H23&lt;=TGT_MAX),IF(J23="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="15">
+        <f>IF(P23="計画なし","－",IF(P23="策定済","✕",IF(N23="","？",IF(AND(N23&gt;=TGT_MIN,N23&lt;=TGT_MAX),IF(P23="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>門川町地域公共交通計画（R6.1改訂）</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>R5〜R9</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J23" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K23" s="16" t="inlineStr">
+        <is>
+          <t>https://www.town.kadogawa.lg.jp/live/data/772474da5c2da6f187648a7d061279dd.pdf</t>
+        </is>
+      </c>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>第2次門川町環境基本計画</t>
+        </is>
+      </c>
+      <c r="M23" s="13" t="inlineStr">
+        <is>
+          <t>R5〜R14</t>
+        </is>
+      </c>
+      <c r="N23" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="O23" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="P23" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="Q23" s="16" t="inlineStr">
+        <is>
+          <t>https://www.town.kadogawa.lg.jp/news/data/730a8477ba8ab68d33388d679ee484d0.pdf</t>
+        </is>
+      </c>
+      <c r="R23" s="13" t="inlineStr">
+        <is>
+          <t>交通：町単独計画（日向市との共同計画ではない）。前計画の門川町地域公共交通網形成計画（H28〜R1）を評価して策定、R6.1改訂。R9終期のため次期計画はR8〜R9策定見込みだが、着手（委託・会議）は検索で未確認（有望）。路線バス維持・乗合タクシー（かどっぴータクシー）https://www.town.kadogawa.lg.jp/live/traffic/page003600.html 、公共交通ガイドブックR8.4改定。担当課・前回受託者は未確認。環境：R5〜R14の10年、中間目標年度R9（中間見直しの可能性）。</t>
+        </is>
+      </c>
+      <c r="S23" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T23" s="13" t="inlineStr">
+        <is>
+          <t>掲載（広域：日向・東臼杵）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="264" customHeight="1">
+      <c r="A24" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>諸塚村</t>
+        </is>
+      </c>
+      <c r="C24" s="14">
+        <f>IF(OR(D24="◎",E24="◎"),"◎ 営業",IF(OR(D24="△",E24="△"),"△ 着手済・要確認",IF(OR(D24="？",E24="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D24" s="15">
+        <f>IF(J24="計画なし","－",IF(J24="策定済","✕",IF(H24="","？",IF(AND(H24&gt;=TGT_MIN,H24&lt;=TGT_MAX),IF(J24="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="15">
+        <f>IF(P24="計画なし","－",IF(P24="策定済","✕",IF(N24="","？",IF(AND(N24&gt;=TGT_MIN,N24&lt;=TGT_MAX),IF(P24="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>宮崎県地域公共交通計画（県全域の広域計画。町村単独計画は未確認）</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>R6〜R10</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J24" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K24" s="16" t="inlineStr">
+        <is>
+          <t>https://www.pref.miyazaki.lg.jp/sogokotsu/shigoto/butsuryu/20240221101503.html</t>
+        </is>
+      </c>
+      <c r="L24" s="13" t="n"/>
+      <c r="M24" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="N24" s="15" t="n"/>
+      <c r="O24" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="P24" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="Q24" s="13" t="n"/>
+      <c r="R24" s="13" t="inlineStr">
+        <is>
+          <t>交通：村単独の地域公共交通計画は検索で確認できず。県計画（R6〜R10、県全域・広域バス路線中心）がカバー。旧『日向・東臼杵地域公共交通網形成計画』（日向市・門川町・美郷町・諸塚村・椎葉村、H28.4〜R4.9）は期間満了、協議会はR4年度で解散（日向市地域公共交通計画R5.3 https://www.hyugacity.jp/sp/tempimg/20240124090032.pdf に記載）。村は地域バスを諸塚交通に委託運行（国交省事例 https://www.mlit.go.jp/sogoseisaku/transport/pdf/100_morotsuka.pdf ）。第6次総合長期計画後期基本計画（R7.3）で公共交通維持を掲げる https://www.vill.morotsuka.miyazaki.jp/material/files/group/3/1114.pdf 。R8.10.1から宮崎交通×ヤマト運輸の路線バス型公共ライドシェア『ねこみやバス』実証運行（日向市・美郷町・諸塚村・椎葉村、〜R9.3、R9.4本格運行目標） https://www.miyakoh.co.jp/news/mediafile/8163cd6c3a9036e3cb1cb968d1444335eae2ee44.pdf 。環境：環境基本計画・区域施策編・ゼロカーボン宣言とも検索で確認できず。</t>
+        </is>
+      </c>
+      <c r="S24" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T24" s="19" t="inlineStr">
+        <is>
+          <t>掲載（広域：日向・東臼杵）／期間満了</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="303" customHeight="1">
+      <c r="A25" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>椎葉村</t>
+        </is>
+      </c>
+      <c r="C25" s="14">
+        <f>IF(OR(D25="◎",E25="◎"),"◎ 営業",IF(OR(D25="△",E25="△"),"△ 着手済・要確認",IF(OR(D25="？",E25="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D25" s="15">
+        <f>IF(J25="計画なし","－",IF(J25="策定済","✕",IF(H25="","？",IF(AND(H25&gt;=TGT_MIN,H25&lt;=TGT_MAX),IF(J25="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="15">
+        <f>IF(P25="計画なし","－",IF(P25="策定済","✕",IF(N25="","？",IF(AND(N25&gt;=TGT_MIN,N25&lt;=TGT_MAX),IF(P25="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>宮崎県地域公共交通計画（県全域の広域計画。町村単独計画は未確認）</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>R6〜R10</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J25" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K25" s="16" t="inlineStr">
+        <is>
+          <t>https://www.pref.miyazaki.lg.jp/sogokotsu/shigoto/butsuryu/20240221101503.html</t>
+        </is>
+      </c>
+      <c r="L25" s="13" t="n"/>
+      <c r="M25" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="N25" s="15" t="n"/>
+      <c r="O25" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="P25" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="Q25" s="13" t="n"/>
+      <c r="R25" s="13" t="inlineStr">
+        <is>
+          <t>交通：村単独の地域公共交通計画は検索で確認できず。県計画（R6〜R10）がカバー。旧『日向・東臼杵地域公共交通網形成計画』（日向市・門川町・美郷町・諸塚村・椎葉村、H28.4〜R4.9）は期間満了、協議会はR4年度で解散（日向市地域公共交通計画R5.3 https://www.hyugacity.jp/sp/tempimg/20240124090032.pdf に記載）。村営バス・予約型タクシー（担当：地域振興課 https://www.vill.shiiba.miyazaki.jp/promote/bus.php ）、過疎計画（R3〜R7）でオンデマンドバス運行事業、総合計画の個別施策で自家用有償旅客運送の検討 https://www.vill.shiiba.miyazaki.jp/promote/008_20_%E9%81%93%E8%B7%AF%E3%83%BB%E5%9C%B0%E5%9F%9F%E4%BA%A4%E9%80%9A%E7%B6%B2%E3%81%AE%E6%95%B4%E5%82%99.pdf 。R8.10.1から宮崎交通×ヤマト運輸の路線バス型公共ライドシェア『ねこみやバス』実証運行（日向市・美郷町・諸塚村・椎葉村、〜R9.3、R9.4本格運行目標） https://www.miyakoh.co.jp/news/mediafile/8163cd6c3a9036e3cb1cb968d1444335eae2ee44.pdf 。環境：環境基本計画・区域施策編・ゼロカーボン宣言とも検索で確認できず。</t>
+        </is>
+      </c>
+      <c r="S25" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T25" s="19" t="inlineStr">
+        <is>
+          <t>掲載（広域：日向・東臼杵）／期間満了</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="342" customHeight="1">
+      <c r="A26" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>美郷町</t>
+        </is>
+      </c>
+      <c r="C26" s="14">
+        <f>IF(OR(D26="◎",E26="◎"),"◎ 営業",IF(OR(D26="△",E26="△"),"△ 着手済・要確認",IF(OR(D26="？",E26="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D26" s="15">
+        <f>IF(J26="計画なし","－",IF(J26="策定済","✕",IF(H26="","？",IF(AND(H26&gt;=TGT_MIN,H26&lt;=TGT_MAX),IF(J26="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E26" s="15">
+        <f>IF(P26="計画なし","－",IF(P26="策定済","✕",IF(N26="","？",IF(AND(N26&gt;=TGT_MIN,N26&lt;=TGT_MAX),IF(P26="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>宮崎県地域公共交通計画（県全域の広域計画。町村単独計画は未確認）</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>R6〜R10</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J26" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K26" s="16" t="inlineStr">
+        <is>
+          <t>https://www.pref.miyazaki.lg.jp/sogokotsu/shigoto/butsuryu/20240221101503.html</t>
+        </is>
+      </c>
+      <c r="L26" s="13" t="n"/>
+      <c r="M26" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="N26" s="15" t="n"/>
+      <c r="O26" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="P26" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="Q26" s="13" t="n"/>
+      <c r="R26" s="13" t="inlineStr">
+        <is>
+          <t>宮崎県東臼杵郡美郷町（town.miyazaki-misato.lg.jp）。交通：町議会会議録（R3第1回定例会 https://www.town.miyazaki-misato.lg.jp/gikai/kiji003494/3_494_476_up_e03hoou3.pdf ）で『美郷町地域公共交通計画及び日向・東臼杵地域公共交通再編実施計画』に基づく施策と答弁があるが、町計画の本文・期間は検索で確認できず（旧網形成計画期の計画の可能性）。現行は県計画（R6〜R10）がカバー。旧『日向・東臼杵地域公共交通網形成計画』（日向市・門川町・美郷町・諸塚村・椎葉村、H28.4〜R4.9）は期間満了、協議会はR4年度で解散（日向市地域公共交通計画R5.3 https://www.hyugacity.jp/sp/tempimg/20240124090032.pdf に記載）。通院目的のコミュニティバスを運行。R8.10.1から宮崎交通×ヤマト運輸の路線バス型公共ライドシェア『ねこみやバス』実証運行（日向市・美郷町・諸塚村・椎葉村、〜R9.3、R9.4本格運行目標） https://www.miyakoh.co.jp/news/mediafile/8163cd6c3a9036e3cb1cb968d1444335eae2ee44.pdf 。環境：環境基本計画は確認できず。地球温暖化対策実行計画（事務事業編）は作成済、『地球温暖化防止の里宣言』あり（R3議会答弁 https://www.town.miyazaki-misato.lg.jp/gikai/kiji003494/3_494_472_up_64q42zzx.pdf ）。区域施策編は未確認。※秋田県美郷町の交通計画（R4.3）・温暖化計画とは別。</t>
+        </is>
+      </c>
+      <c r="S26" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T26" s="19" t="inlineStr">
+        <is>
+          <t>掲載（広域：日向・東臼杵）／期間満了</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="173" customHeight="1">
+      <c r="A27" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>高千穂町</t>
+        </is>
+      </c>
+      <c r="C27" s="14">
+        <f>IF(OR(D27="◎",E27="◎"),"◎ 営業",IF(OR(D27="△",E27="△"),"△ 着手済・要確認",IF(OR(D27="？",E27="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D27" s="15">
+        <f>IF(J27="計画なし","－",IF(J27="策定済","✕",IF(H27="","？",IF(AND(H27&gt;=TGT_MIN,H27&lt;=TGT_MAX),IF(J27="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E27" s="15">
+        <f>IF(P27="計画なし","－",IF(P27="策定済","✕",IF(N27="","？",IF(AND(N27&gt;=TGT_MIN,N27&lt;=TGT_MAX),IF(P27="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>高千穂町地域公共交通計画（策定準備中）</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n"/>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="J27" s="15" t="inlineStr">
+        <is>
+          <t>着手済</t>
+        </is>
+      </c>
+      <c r="K27" s="16" t="inlineStr">
+        <is>
+          <t>https://www.town-takachiho.jp/top/soshiki/kikakukanko/2881.html</t>
+        </is>
+      </c>
+      <c r="L27" s="13" t="n"/>
+      <c r="M27" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="N27" s="15" t="n"/>
+      <c r="O27" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="P27" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="Q27" s="13" t="n"/>
+      <c r="R27" s="13" t="inlineStr">
+        <is>
+          <t>交通：現行の町単独計画は確認できず（県計画R6〜R10が広域カバー。西臼杵3町の共同計画はH20年代の『西臼杵地域公共交通総合連携計画』のみで現行の共同計画は確認できず）。【着手済】企画観光課が『地域公共交通計画策定事前調査業務』を公募型プロポーザル（R8.5.20公募、7.3プレゼン、7.10結果通知、上限5,922,000円税込）→第一優先交渉者ランドブレイン㈱福岡事務所、契約期間〜R9.3.31。本計画策定はR9年度以降の見込み（営業機会：本策定業務）。コミュニティバス『ふれあいバス』運行 https://www.town-takachiho.jp/top/soshiki/kikakukanko/fureaibasu/index.html 。環境：環境基本計画・区域施策編・ゼロカーボン宣言とも検索で確認できず。</t>
+        </is>
+      </c>
+      <c r="S27" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T27" s="19" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="238" customHeight="1">
+      <c r="A28" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>日之影町</t>
+        </is>
+      </c>
+      <c r="C28" s="14">
+        <f>IF(OR(D28="◎",E28="◎"),"◎ 営業",IF(OR(D28="△",E28="△"),"△ 着手済・要確認",IF(OR(D28="？",E28="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D28" s="15">
+        <f>IF(J28="計画なし","－",IF(J28="策定済","✕",IF(H28="","？",IF(AND(H28&gt;=TGT_MIN,H28&lt;=TGT_MAX),IF(J28="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="15">
+        <f>IF(P28="計画なし","－",IF(P28="策定済","✕",IF(N28="","？",IF(AND(N28&gt;=TGT_MIN,N28&lt;=TGT_MAX),IF(P28="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>日之影町地域公共交通計画</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>R5〜R9</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J28" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K28" s="16" t="inlineStr">
+        <is>
+          <t>https://www.town.hinokage.lg.jp/docs/2023032900016/file_contents/keikaku_.pdf</t>
+        </is>
+      </c>
+      <c r="L28" s="13" t="n"/>
+      <c r="M28" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="N28" s="15" t="n"/>
+      <c r="O28" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="P28" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="Q28" s="13" t="n"/>
+      <c r="R28" s="13" t="inlineStr">
+        <is>
+          <t>交通：R5.3策定、R5〜R9の5か年（町単独。西臼杵共同計画ではない）。計画本文に最終年度R9に効果検証し次期計画を策定と明記。R4.4に地域公共交通会議を活性化再生法に基づく会議へ改組。R8.6.1に令和8年度第1回地域公共交通会議開催（議事録あり https://www.town.hinokage.lg.jp/docs/2022042900023/ 、議題は未確認）→次期計画（R10〜）策定はR8〜R9着手見込み（有望、委託公告は未確認）。前回策定業務の受託者・金額は検索で確認できず。関連：宮崎交通延岡〜高千穂線の一部（県道北方高千穂線旧道区間）廃止を補完しすまいるバス八戸線を本格運行、町内全域の予約型乗合交通を本格運行（R6.10） https://www.town.hinokage.lg.jp/docs/2016020200106/ 、R8.7〜八戸線迂回運行。環境：環境基本計画は確認できず。代替として『日之影町地球温暖化対策実行計画（区域施策編）』策定済（期間未確認）、ゼロカーボンシティ宣言（R6.3頃） https://www.town.hinokage.lg.jp/docs/2024030700011/ 。</t>
+        </is>
+      </c>
+      <c r="S28" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T28" s="13" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="147" customHeight="1">
+      <c r="A29" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>五ヶ瀬町</t>
+        </is>
+      </c>
+      <c r="C29" s="14">
+        <f>IF(OR(D29="◎",E29="◎"),"◎ 営業",IF(OR(D29="△",E29="△"),"△ 着手済・要確認",IF(OR(D29="？",E29="？"),"？ 期間要確認","✕ 対象外")))</f>
+        <v/>
+      </c>
+      <c r="D29" s="15">
+        <f>IF(J29="計画なし","－",IF(J29="策定済","✕",IF(H29="","？",IF(AND(H29&gt;=TGT_MIN,H29&lt;=TGT_MAX),IF(J29="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="15">
+        <f>IF(P29="計画なし","－",IF(P29="策定済","✕",IF(N29="","？",IF(AND(N29&gt;=TGT_MIN,N29&lt;=TGT_MAX),IF(P29="着手済","△","◎"),"✕"))))</f>
+        <v/>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>宮崎県地域公共交通計画（県全域の広域計画。町村単独計画は未確認）</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>R6〜R10</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J29" s="15" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K29" s="16" t="inlineStr">
+        <is>
+          <t>https://www.pref.miyazaki.lg.jp/sogokotsu/shigoto/butsuryu/20240221101503.html</t>
+        </is>
+      </c>
+      <c r="L29" s="13" t="n"/>
+      <c r="M29" s="13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="N29" s="15" t="n"/>
+      <c r="O29" s="15" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="P29" s="15" t="inlineStr">
+        <is>
+          <t>計画なし</t>
+        </is>
+      </c>
+      <c r="Q29" s="13" t="n"/>
+      <c r="R29" s="13" t="inlineStr">
+        <is>
+          <t>交通：町単独の地域公共交通計画は検索で確認できず。県計画（R6〜R10）が広域カバー、西臼杵3町の現行共同計画も確認できず。コミュニティバス『Gライン』（H19.10〜、担当：企画課、R6.8から一部区間・便でデマンド型運行導入） https://www.town.gokase.miyazaki.jp/kakuka/kikaku/110.html 。五ヶ瀬町総合交通対策運営委員会・地域公共交通会議あり。環境：環境基本計画・区域施策編は確認できず。ゼロカーボンシティ宣言を表明 https://www.town.gokase.miyazaki.jp/kakuka/kikaku/1233.html （区域施策編策定の可能性あり、要確認）。</t>
+        </is>
+      </c>
+      <c r="S29" s="17" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T29" s="19" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:T29"/>
+  <conditionalFormatting sqref="A4:T29">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>LEFT($C4,1)="◎"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="1">
+      <formula>LEFT($C4,1)="△"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="2">
+      <formula>LEFT($C4,1)="？"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="3">
+      <formula>LEFT($C4,1)="✕"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H29">
+    <cfRule type="expression" priority="1" dxfId="4" stopIfTrue="1">
+      <formula>AND(ISNUMBER(H4),H4&gt;=TGT_MIN,H4&lt;=TGT_MAX)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="5">
+      <formula>AND(ISNUMBER(H4),H4=TGT_MAX+1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N4:N29">
+    <cfRule type="expression" priority="3" dxfId="4" stopIfTrue="1">
+      <formula>AND(ISNUMBER(N4),N4&gt;=TGT_MIN,N4&lt;=TGT_MAX)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="5">
+      <formula>AND(ISNUMBER(N4),N4=TGT_MAX+1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="J4:J29 P4:P29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"未確認,着手済,策定済,計画なし"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId29"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N44"/>
@@ -18454,7 +21694,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
